--- a/Noticias_Calcario_20260714.xlsx
+++ b/Noticias_Calcario_20260714.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - avozdocampo.com</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNnBteWw0TE1HbHBPOFZNdXp1NmdOaWJYcXNyLUwtUUc5eW9GcUw2WU1jaUZuMjdsZHd1djBmd2JHRkVqdWhhVi1fM3pjdV9fX19zVnBJWUM4UTRHZlpabkFDd3kzWkd6QmJNd093TU53blZ0VWdJbkRmSWIyVEVycGNXRGQ2OU5LR1BkSEJBVU16c0pCMGs2SmRzNks4MmJMc0JYUFZwM2hMTl9oX0VibXZhQ084UkpSZmxvbTZfN21LZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - avozdocampo.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,95 +676,95 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNnBteWw0TE1HbHBPOFZNdXp1NmdOaWJYcXNyLUwtUUc5eW9GcUw2WU1jaUZuMjdsZHd1djBmd2JHRkVqdWhhVi1fM3pjdV9fX19zVnBJWUM4UTRHZlpabkFDd3kzWkd6QmJNd093TU53blZ0VWdJbkRmSWIyVEVycGNXRGQ2OU5LR1BkSEJBVU16c0pCMGs2SmRzNks4MmJMc0JYUFZwM2hMTl9oX0VibXZhQ084UkpSZmxvbTZfN21LZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes em sete unidades no Brasil e pressiona custos do agro - Economic News Brasil</t>
+          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14/07/2026 10:17</t>
+          <t>14/07/2026 11:33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdWlnLW42MkVwbEVHUUc2LXRpQUhhYjJCbzM5VzE4S0xxcDdrRlptQ1h1YkZDVFJ0SkxzOFN5WS05eVdiZ3FMR2VJdEIyeFpzckJvb1pHZnJRZV9fbEZwakdLTWdGS2Q1NVN3bWIwTmN3MUxJNXNvaWVjTHl1VGdqUWxYaVdpWFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORmJVVEVSd2xNTnQ1d1ZfQnFGalNqXy1XU3VyOGQyVmRpS19EM0RsZzBFbzFxQVVCQkRsbHFhN01od1AwVUE0M2xzaUVyaUNiQWhENXlZNE02N2pHNldySGRseFc0a184bW51YUlPV2o0YXBIdnBzRHMzS3lnM2NOdEhzTTFMN1pEQzdfTlhWMUs4c0xhalNOalM2cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caminhão sai com fertilizante e chega com calcário; caso é investigado pela Polícia Civil - JM Online</t>
+          <t>Mosaic reduz produção de fertilizantes em sete unidades no Brasil e pressiona custos do agro - Economic News Brasil</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14/07/2026 10:13</t>
+          <t>14/07/2026 10:17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdzREdE1BVFdYdHRvbk5kOG05ams1aHR5R1hEX0xkckRCMVJyNm5ucG9ZcjRwS2prTllwdzdLcnU2WmFFQU05QmgyS09Fbzh1VFptZFgzcjBHOFBOemNfR3doUDBmTHJtaFdydzJISHpHM0NueTNjRDRwcDhRNEliX0M4QVBKaDlyaDZaYnRJOERXelpLRzdVTklQWVgwaVlZODFPcmFlRnJpdjRBWk9NRkhSZmZudHI3eGpqS0ZxS3o2cjl6Z1FER2FLLW9FcThM0gHQAUFVX3lxTE93NER0TUFUV1h0dG9uTmQ4bTlqazVodHlHWERfTGRyREIxUnI2bm5wb1lyNHBLamtOWXB3N0tydTZaYUVBTTlCaDJLT0VvOHVUWm1kWDNyMEc4UE56Y19Hd2hQMGZMcm1oV3J3MkhIekczQ255M2NENHBwOFE0SWJfQzhBUEpoOXJoNlpidEk4RFd6WktHN1VOSVBZWDBpWVk4MU9yYWVGcml2NEFaT01GSFJmZm50cjd4ampLRnFLejZyOXpnUURHYUstb0VxOEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdWlnLW42MkVwbEVHUUc2LXRpQUhhYjJCbzM5VzE4S0xxcDdrRlptQ1h1YkZDVFJ0SkxzOFN5WS05eVdiZ3FMR2VJdEIyeFpzckJvb1pHZnJRZV9fbEZwakdLTWdGS2Q1NVN3bWIwTmN3MUxJNXNvaWVjTHl1VGdqUWxYaVdpWFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tecnologia de veículos autônomos MOSAIC: um novo passo em frente na logística militar na Ucrânia. - Vietnam.vn</t>
+          <t>Caminhão sai com fertilizante e chega com calcário; caso é investigado pela Polícia Civil - JM Online</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14/07/2026 08:33</t>
+          <t>14/07/2026 10:13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPQlRFMVhpVkU0T3A1VW9hZVp5aXMzQUF6bnFCYTFXMVhfZVpFeV8zZmZRc1JwaE9lT0RpZV9yYmVIY1BBRnhmamQydnlpRWI1SE5xdGZSVGlneUxOR19fMzdBdjVncmhWVlNQSnBiMHFtUERxMUxwUXdxeWw5cG9pSGxTbXM1QXo0MlBfaE9KeHd6ZXpTeXBzUy0wYnJXU3ZXR1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdzREdE1BVFdYdHRvbk5kOG05ams1aHR5R1hEX0xkckRCMVJyNm5ucG9ZcjRwS2prTllwdzdLcnU2WmFFQU05QmgyS09Fbzh1VFptZFgzcjBHOFBOemNfR3doUDBmTHJtaFdydzJISHpHM0NueTNjRDRwcDhRNEliX0M4QVBKaDlyaDZaYnRJOERXelpLRzdVTklQWVgwaVlZODFPcmFlRnJpdjRBWk9NRkhSZmZudHI3eGpqS0ZxS3o2cjl6Z1FER2FLLW9FcThM0gHQAUFVX3lxTE93NER0TUFUV1h0dG9uTmQ4bTlqazVodHlHWERfTGRyREIxUnI2bm5wb1lyNHBLamtOWXB3N0tydTZaYUVBTTlCaDJLT0VvOHVUWm1kWDNyMEc4UE56Y19Hd2hQMGZMcm1oV3J3MkhIekczQ255M2NENHBwOFE0SWJfQzhBUEpoOXJoNlpidEk4RFd6WktHN1VOSVBZWDBpWVk4MU9yYWVGcml2NEFaT01GSFJmZm50cjd4ampLRnFLejZyOXpnUURHYUstb0VxOEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dependência externa amplia riscos para fertilizantes - Agrolink</t>
+          <t>Tecnologia de veículos autônomos MOSAIC: um novo passo em frente na logística militar na Ucrânia. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14/07/2026 05:15</t>
+          <t>14/07/2026 08:33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNbUZXX19wUkttRGhrbG1nekhhaW5UTWlhUUM1RzNZOGdSZ2tDYlJNNGlKVGRTRFRFVlpwUFpMNnNEUGh2di00N1RFbHFONWNqajJwOFBrMHlSZWFSTFpQYmxMVEdRTGVsWHBlOEI0RzlGYmxYOFRPSXB0MlhmdHZSUVp4c1BkdTVnaWs1QjdlUDZMT0JBNFVVeXZFYmpaY0VlT213?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPQlRFMVhpVkU0T3A1VW9hZVp5aXMzQUF6bnFCYTFXMVhfZVpFeV8zZmZRc1JwaE9lT0RpZV9yYmVIY1BBRnhmamQydnlpRWI1SE5xdGZSVGlneUxOR19fMzdBdjVncmhWVlNQSnBiMHFtUERxMUxwUXdxeWw5cG9pSGxTbXM1QXo0MlBfaE9KeHd6ZXpTeXBzUy0wYnJXU3ZXR1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -793,132 +793,132 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
+          <t>A queda nos preços da ureia alivia o fardo dos agricultores para a safra de verão-outono. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14/07/2026 02:00</t>
+          <t>14/07/2026 04:24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBvc29iQWxFa2d6al8zOU15R1M0VGd3VGtzLWE5bTVTaDcxOWZYa0phT0JCWUxtSDZ4bEZodHpNOTNoNnZIS1hBczNaV2o1Y1VRN0J5RWNqbHA2SUl5WEtaS0RiaUNITkZxbzBya1hSWnhJV0wtcnM0NWtGUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Previsão do tempo Limestone VIC. 14 dias - Meteored Brasil</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14/07/2026 00:47</t>
+          <t>14/07/2026 02:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5uWS1sR2lPOGZ6UmtZa1l5ZF9uaVJPSXBBa21UcnNsLUFIYkI5VHdfSWdTQW0tNkhRVmxZY1BlNllNN1ZjdUU3eFFCZkRqeFY1VHQwWjdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NASA revela imagens inéditas de enxofre puro em Marte: um “tesouro amarelo” descoberto pelo rover Curiosity - Noticias Ambientales</t>
+          <t>Previsão do tempo Limestone VIC. 14 dias - Meteored Brasil</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13/07/2026 21:56</t>
+          <t>14/07/2026 00:47</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNOGpMbFZtUjdFd1JDQXp4WkVlc0FaLUxYVGU2WHNXRmRkUzVVb0hFcHFrSy1CYTFVUG5GdVZoVDdKQ0tkTC02ZkdSMUNhMS1TalRncjBKTldzUk54MDNHQl9OcE5MS0dkQ1c1LUJtWWQyX05vSGlKUFpnTGJjd2ptMUdjY2JpNEZpem5xOXNDMmo0M2l5R0JtZFcyR3lyTW1tQ2tvaVU3VkpOamdrdldSWTk0SWRMXzlJdDRpMHZ6WUwzVWNkc2ZhTDUtcmVsNXIzOW9VZHVnVVF6UEd4ZTRvcHpn0gHnAUFVX3lxTE9VR2NueC1oS2MzbzFWa3otdmJyS3dlQUV0M2dWQXZ3Q1NrSW9GR21TUTQ5YVZ6LTVrOFpqVkFudmdSTDBzMTlsLWlOTHdoWGJMT093cHpVODVrNHpyME9jUEdMTlNTOVh6Qm41eG13UnhQZ1FUZ1pNZkpTQjZXbXYtVm9aUlptODgzWGstZUJ6bk9BNkhtVld6WEtBODk1bkN3ZjR3WnF0NnhtX25rTkhfajgzSG40MEMzNmVlQnBTTWNCRU1IeDE4VmZwZzY3bjVsc1BBWGpZLWthNTc5b3RzLXhaOFRPUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5uWS1sR2lPOGZ6UmtZa1l5ZF9uaVJPSXBBa21UcnNsLUFIYkI5VHdfSWdTQW0tNkhRVmxZY1BlNllNN1ZjdUU3eFFCZkRqeFY1VHQwWjdB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 4 - ArchDaily</t>
+          <t>NASA revela imagens inéditas de enxofre puro em Marte: um “tesouro amarelo” descoberto pelo rover Curiosity - Noticias Ambientales</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13/07/2026 20:59</t>
+          <t>13/07/2026 21:56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPWUJ1VEZxajJHbVRUdm5YQnpJakE4WXlZRTVUQURmYkZRZUJWOG9jQnVVMENoc29FRV94SHlRTC1PUHV5dGtoMXVJTERVZnc5OE5GdFRlNFpvZml2VlZmc0RZRkt4S2JmdjVuMTUxUGxVSnI4c1VxZXdOYzdBQjNRZVVVTU5jSVZOeTJ3QkF0RTR2QWJab3hNTTRWS0lpWkZxd1ZuZ3VYV180ZjRKTjBPSmVQdkVzRkllRWdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNOGpMbFZtUjdFd1JDQXp4WkVlc0FaLUxYVGU2WHNXRmRkUzVVb0hFcHFrSy1CYTFVUG5GdVZoVDdKQ0tkTC02ZkdSMUNhMS1TalRncjBKTldzUk54MDNHQl9OcE5MS0dkQ1c1LUJtWWQyX05vSGlKUFpnTGJjd2ptMUdjY2JpNEZpem5xOXNDMmo0M2l5R0JtZFcyR3lyTW1tQ2tvaVU3VkpOamdrdldSWTk0SWRMXzlJdDRpMHZ6WUwzVWNkc2ZhTDUtcmVsNXIzOW9VZHVnVVF6UEd4ZTRvcHpn0gHnAUFVX3lxTE9VR2NueC1oS2MzbzFWa3otdmJyS3dlQUV0M2dWQXZ3Q1NrSW9GR21TUTQ5YVZ6LTVrOFpqVkFudmdSTDBzMTlsLWlOTHdoWGJMT093cHpVODVrNHpyME9jUEdMTlNTOVh6Qm41eG13UnhQZ1FUZ1pNZkpTQjZXbXYtVm9aUlptODgzWGstZUJ6bk9BNkhtVld6WEtBODk1bkN3ZjR3WnF0NnhtX25rTkhfajgzSG40MEMzNmVlQnBTTWNCRU1IeDE4VmZwZzY3bjVsc1BBWGpZLWthNTc5b3RzLXhaOFRPUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uberaba propõe reduzir ISS para tentar preservar empregos após hibernação da Mosaic - Regionalzão</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13/07/2026 20:54</t>
+          <t>13/07/2026 20:59</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xbkloamZJdlJQX1V6US13ZkFvei1CRk9vVDBVSElYMm1qUVZiMWY4Ynk1UlhEVlQ3bm5Ha1RmNXNrMjl5NEdwQ3pwMFBXNk9GUGppSm13aTdja1U1TzlaR1JQNEtSQzVXNFlXZ1FNbTZJWlRDbHhvRjQzb1BRNDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPWUJ1VEZxajJHbVRUdm5YQnpJakE4WXlZRTVUQURmYkZRZUJWOG9jQnVVMENoc29FRV94SHlRTC1PUHV5dGtoMXVJTERVZnc5OE5GdFRlNFpvZml2VlZmc0RZRkt4S2JmdjVuMTUxUGxVSnI4c1VxZXdOYzdBQjNRZVVVTU5jSVZOeTJ3QkF0RTR2QWJab3hNTTRWS0lpWkZxd1ZuZ3VYV180ZjRKTjBPSmVQdkVzRkllRWdZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Galeria de Kalesinterflex - Calcario Collection - 7 - ArchDaily</t>
+          <t>Uberaba propõe reduzir ISS para tentar preservar empregos após hibernação da Mosaic - Regionalzão</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13/07/2026 20:39</t>
+          <t>13/07/2026 20:54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNVDlHVXpVUFBMa0lkMnhaQllMbll2U2ZzTHNHVlM1Y3ZQQ2p2cl8yRG5ENTBCOHdQWjdFU1E0b3RtVWhhb1I4VEpYOHAxaEdnT3BYV0tYSEVJcHI1OVlKOU9xLTRsWm83Q2FJQlEtSEMtdUh6anp3ZlhZWjM3THpsaDNLUTU1bmRzNDI0R1FIZXpqRnk5ckQwX2NVcXpFNFdVcFhsS0U2anJyX09NUUt0VEY3QURicm1FTHp1SVhfSm1rZWZvV0NUdkExYW1kOFBIU2xLeEoxMzI2cHpPazNjRnlKd19BRkpMS0owdGY1VjU2Wjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xbkloamZJdlJQX1V6US13ZkFvei1CRk9vVDBVSElYMm1qUVZiMWY4Ynk1UlhEVlQ3bm5Ha1RmNXNrMjl5NEdwQ3pwMFBXNk9GUGppSm13aTdja1U1TzlaR1JQNEtSQzVXNFlXZ1FNbTZJWlRDbHhvRjQzb1BRNDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1013,88 +1013,88 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 4 - ArchDaily</t>
+          <t>Mosaic anuncia paralisação temporária de atividades em Catalão devido à escassez global de enxofre - zapcatalao.com.br</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13/07/2026 18:50</t>
+          <t>13/07/2026 18:45</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNRElabWZXNlRNTlJMTm1nckx6UnJ0cWJsNjZGYVVQbWNoN2JOQnZoUGFjMVpvQnVPNmFSOE12OGZmNkpiYVRUR1JDWWJEZ3NfU1U5amtkX01MUW5mdkdRWDJadFdWRHh0bFF3Z0ZHSk4zVHRZM3k5SHA4VXRTMFlEWXhsSU5rTllCVDhoU2VTcHFsT29WR1g1VmZQcTVrVVUxMUp0Ym1aclBDWV9GOW5vLWNwQUlTNm9v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUGhkU2hMOC1vX0l4SVdHbUszZFpoV1AwcmlqU3l6a0h0aWdUb2dVWExIQ01NSFZuLS1UTGpoa29PQXI5TWhkQnA4Q1d6MEZwcDQtNHRlRGNlU0NhUG5kNFMxb25zLU11OVdORDVmdUR0aXViZldld0ZxUXNITXBTUjR6c0JmUVU4SXo5aGlmY1JTQkZHUFdGNzlub19lc3ByTEhLREd3MHgzY0xwRHBXeUVCM1FOQnQtUElyVTdvT0JBZ3l5SFpSWjFYMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária de atividades em Catalão devido à escassez global de enxofre - zapcatalao.com.br</t>
+          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13/07/2026 18:45</t>
+          <t>13/07/2026 17:45</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUGhkU2hMOC1vX0l4SVdHbUszZFpoV1AwcmlqU3l6a0h0aWdUb2dVWExIQ01NSFZuLS1UTGpoa29PQXI5TWhkQnA4Q1d6MEZwcDQtNHRlRGNlU0NhUG5kNFMxb25zLU11OVdORDVmdUR0aXViZldld0ZxUXNITXBTUjR6c0JmUVU4SXo5aGlmY1JTQkZHUFdGNzlub19lc3ByTEhLREd3MHgzY0xwRHBXeUVCM1FOQnQtUElyVTdvT0JBZ3l5SFpSWjFYMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNclVqZS1lVldPbUIzS3JZeHhEbHNZeUE2U3ZJa1RvMEdydThWNnp1MGt6UkFaZExEVWo0Nk5JSjV2cFpOUUlyWVZaRUxXZ3VaaHNmckhBRndIR0NTX196OGpnbVEzZDItazdET2xZM0VPQ1NCZVdoM3R6S3J6elE5MXVEM3VFQkRKX1dyMVJ5WWtjTXJkcndOckJWRXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
+          <t>Uberaba propõe reduzir ISS após Mosaic anunciar hibernação da produção de fosfato - Diário do Comércio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13/07/2026 17:45</t>
+          <t>13/07/2026 14:50</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNclVqZS1lVldPbUIzS3JZeHhEbHNZeUE2U3ZJa1RvMEdydThWNnp1MGt6UkFaZExEVWo0Nk5JSjV2cFpOUUlyWVZaRUxXZ3VaaHNmckhBRndIR0NTX196OGpnbVEzZDItazdET2xZM0VPQ1NCZVdoM3R6S3J6elE5MXVEM3VFQkRKX1dyMVJ5WWtjTXJkcndOckJWRXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1xY1VPeFZZNUwzYUc5dWxRWXlSS3JudmpJTEloR09RVUpxMmtjY1hSLUpTbkU2eHNDaEgxZW8tQTZicGpWMlZHb1ZNb21fZFE2aENLTlpGUjB3b2hxMk1hNXNsSnp6TkMtUXZCRExYR1BCSEktUk1idDZJYw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Uberaba propõe reduzir ISS após Mosaic anunciar hibernação da produção de fosfato - Diário do Comércio</t>
+          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13/07/2026 14:50</t>
+          <t>13/07/2026 13:30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1xY1VPeFZZNUwzYUc5dWxRWXlSS3JudmpJTEloR09RVUpxMmtjY1hSLUpTbkU2eHNDaEgxZW8tQTZicGpWMlZHb1ZNb21fZFE2aENLTlpGUjB3b2hxMk1hNXNsSnp6TkMtUXZCRExYR1BCSEktUk1idDZJYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
         </is>
       </c>
     </row>
@@ -1106,215 +1106,215 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
+          <t>Transição energética pode reduzir oferta de enxofre e encarecer fertilizantes - CompreRural</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13/07/2026 13:30</t>
+          <t>13/07/2026 13:13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMVowY3hvZ3VyTlU3QkR6YlVZMVk3Y3paOW5UbUxqMV9pSDFydmV2NzU0QmcwZGtoajR1OGtfcC1QM291bXpSc29yRVAxS2k0OXJYSDM4UHJOMVNmcWVOTUJzdzBfNWhfUUJtZlpqYTRkRHR2dGlwMmV5SF83OTl4Nnp0RHhIbVVaY1Z4WmFLYjhuVWRDZXhTYm8xcTZIQ0pwbVNXZXN4OFNfdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Transição energética pode reduzir oferta de enxofre e encarecer fertilizantes - CompreRural</t>
+          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - Poder Goiás</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13/07/2026 13:13</t>
+          <t>13/07/2026 11:57</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMVowY3hvZ3VyTlU3QkR6YlVZMVk3Y3paOW5UbUxqMV9pSDFydmV2NzU0QmcwZGtoajR1OGtfcC1QM291bXpSc29yRVAxS2k0OXJYSDM4UHJOMVNmcWVOTUJzdzBfNWhfUUJtZlpqYTRkRHR2dGlwMmV5SF83OTl4Nnp0RHhIbVVaY1Z4WmFLYjhuVWRDZXhTYm8xcTZIQ0pwbVNXZXN4OFNfdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxObURQMTIzVUVEOUNoMzlHMGY0dl9rWmdjdnRJRTNiLWNkWnNrVFp2WWh3ZmR0dnV0Z2ZwZWpBNmctUGJLV1FadDh5TDF5dHRXX3BtVUtUTnBZUnhyRE9GVmw2Y2VBSlVHYVpMNlprNVBnZ0p6dzEzRF9UWmhxeEQtdkdyQkZuYm5OYmFCM2JGVGUyNEdPcDNnUm53Y0VQbmUyVVZPa2ZpR2o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - Poder Goiás</t>
+          <t>Rover Curiosity encontra cristais de enxofre puro em Marte após esmagar rocha por acidente - Nerdizmo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13/07/2026 11:57</t>
+          <t>13/07/2026 11:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxObURQMTIzVUVEOUNoMzlHMGY0dl9rWmdjdnRJRTNiLWNkWnNrVFp2WWh3ZmR0dnV0Z2ZwZWpBNmctUGJLV1FadDh5TDF5dHRXX3BtVUtUTnBZUnhyRE9GVmw2Y2VBSlVHYVpMNlprNVBnZ0p6dzEzRF9UWmhxeEQtdkdyQkZuYm5OYmFCM2JGVGUyNEdPcDNnUm53Y0VQbmUyVVZPa2ZpR2o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQU29hYlBaR21Yamp2VXpDekF6bHp6WnMxaGpaSDhEcEhpSGhsU0htSXg0VzQxMzc1Tjhqd1RFYlNiNmRqTWoyQVhUSFk5dkx4NjhGQjZqZVpaenlGZmRRdkdON3pEcm4ySzBKR2xnVlNKb2stQzhMaS1JQ0VicU1RUHFFUmZVeFZoRXhmbE9EZHljNjBfSXNMVG5LaUdTdmZBbzVCUUZxcGpyT2NXbHF1Y1NYYWxDeUJ0b2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rover Curiosity encontra cristais de enxofre puro em Marte após esmagar rocha por acidente - Nerdizmo</t>
+          <t>Fertiliza Turmalina amplia atendimento e beneficiará 147 produtores com Agrosilício - csastudiowebradio.com.br</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13/07/2026 11:00</t>
+          <t>13/07/2026 10:58</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQU29hYlBaR21Yamp2VXpDekF6bHp6WnMxaGpaSDhEcEhpSGhsU0htSXg0VzQxMzc1Tjhqd1RFYlNiNmRqTWoyQVhUSFk5dkx4NjhGQjZqZVpaenlGZmRRdkdON3pEcm4ySzBKR2xnVlNKb2stQzhMaS1JQ0VicU1RUHFFUmZVeFZoRXhmbE9EZHljNjBfSXNMVG5LaUdTdmZBbzVCUUZxcGpyT2NXbHF1Y1NYYWxDeUJ0b2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOc2xrV0ZHYzhPOUk2dWlmMXBmZGR3ck52dVRESjJTNmw3TU1razRzR0hobkVHaXA1YjBObk9MTmMyQ2VxVVo5S29EQnhxMXdYb3YtcWVsdzZZUWJIZV9QUjY5aS1uQjJIMENzLXg3SWdwcFVhR3RfVkF5MnVBUkRYdnBKSUpfcnVqS01FVVA0WU1KU29aVThSZ0M3YzcxaFluTmRuYWdVTXlrMjRhMlBzbTNpNkVqNFNWRHV3b3Nfc1dmcy02VnhYRGpR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fertiliza Turmalina amplia atendimento e beneficiará 147 produtores com Agrosilício - csastudiowebradio.com.br</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13/07/2026 10:58</t>
+          <t>13/07/2026 10:31</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOc2xrV0ZHYzhPOUk2dWlmMXBmZGR3ck52dVRESjJTNmw3TU1razRzR0hobkVHaXA1YjBObk9MTmMyQ2VxVVo5S29EQnhxMXdYb3YtcWVsdzZZUWJIZV9QUjY5aS1uQjJIMENzLXg3SWdwcFVhR3RfVkF5MnVBUkRYdnBKSUpfcnVqS01FVVA0WU1KU29aVThSZ0M3YzcxaFluTmRuYWdVTXlrMjRhMlBzbTNpNkVqNFNWRHV3b3Nfc1dmcy02VnhYRGpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13/07/2026 10:31</t>
+          <t>13/07/2026 10:14</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
+          <t>Galeria de Masonry Stone Walls - Dietfurt Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13/07/2026 10:14</t>
+          <t>13/07/2026 09:49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPcHRFajVmOVhoREJOaGxGWkdTTXlmVW9kWGFvaDl6dHByQmFTTzNyMEY1cHdTNE5zeWIzRERxSnNzZDdxMjdMOXBWSVdqaE16bUxFVmQwQW1nbGREWldkekNfOVJUZEo0dWRyTk9zLXotcS1ZT1dka3BOcWptMlZwVm9faVB6czAzcG5vUXc2Mnd3N3B0V2hmcnhkT3JORTJWS2pSeXZuVU9GbWFZempvNFQ4Wlg5VnhzYVY4VHN6Vk5taklscWdfelRxNzJtNURWcXJRM0pVVXdfbkZ0TWxWS0hTY01QTmJyRkJkZlNZcjhwSG5CbmxENEktT2E0YUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Galeria de Masonry Stone Walls - Dietfurt Limestone - 1 - ArchDaily</t>
+          <t>Cruzeiro perde dois pênaltis e é derrotado pelo Grêmio em amistoso em Brasília - Rádio Itatiaia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13/07/2026 09:49</t>
+          <t>12/07/2026 22:04</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPcHRFajVmOVhoREJOaGxGWkdTTXlmVW9kWGFvaDl6dHByQmFTTzNyMEY1cHdTNE5zeWIzRERxSnNzZDdxMjdMOXBWSVdqaE16bUxFVmQwQW1nbGREWldkekNfOVJUZEo0dWRyTk9zLXotcS1ZT1dka3BOcWptMlZwVm9faVB6czAzcG5vUXc2Mnd3N3B0V2hmcnhkT3JORTJWS2pSeXZuVU9GbWFZempvNFQ4Wlg5VnhzYVY4VHN6Vk5taklscWdfelRxNzJtNURWcXJRM0pVVXdfbkZ0TWxWS0hTY01QTmJyRkJkZlNZcjhwSG5CbmxENEktT2E0YUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxORWEtUDBwVjI2ajNHQjFLbHBzclRraGFrV29BXzZpVkVZMXNBNDhoR3dteFRqRUViNm5BN0VGbkQxMDVzc2liN3lCRkFqVGNtNnM3ekM3LVNvQXByTGZOaGZrTTVKNHgxc0dSOXVKZmhJWk16bHZQOGNpUjBaZWU0TlRScVcxOWY0NFczS0FEMkVjU0NKbjlPY1JjUjFaNWIyR2IyajFWUGVHQXE1SmhkVUlfblNrcEVDeTNLc0hvOVItMHk2Rm9CeWUweHpvRWgxN2VKTVhJc2k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cruzeiro perde dois pênaltis e é derrotado pelo Grêmio em amistoso em Brasília - Rádio Itatiaia</t>
+          <t>Guerra entre EUA e Irã ameaça fertilizantes e acende alerta para agricultores do Brasil - A Referência</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>12/07/2026 22:04</t>
+          <t>12/07/2026 21:58</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxORWEtUDBwVjI2ajNHQjFLbHBzclRraGFrV29BXzZpVkVZMXNBNDhoR3dteFRqRUViNm5BN0VGbkQxMDVzc2liN3lCRkFqVGNtNnM3ekM3LVNvQXByTGZOaGZrTTVKNHgxc0dSOXVKZmhJWk16bHZQOGNpUjBaZWU0TlRScVcxOWY0NFczS0FEMkVjU0NKbjlPY1JjUjFaNWIyR2IyajFWUGVHQXE1SmhkVUlfblNrcEVDeTNLc0hvOVItMHk2Rm9CeWUweHpvRWgxN2VKTVhJc2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOc0o3SzR2VWFVY3M3RVRIZ3dQUThlTmJpVXpQSnp2X28yMlFsNER4S3RYOFhoQy03YUZCdm9MOG1NRDVaMmR4cXNiVy1vQzNzaXlMdTFDek9kUVZiNWNpSmJxckFCZmJVMkpWY0Y5SURXZks4VG10M1l3dlNkTGlpV2lvMEtNaEpRam5sUUo4bmE2Qk1VSGl0VHY2UjV1M0hKZ0lCUG00ZENSVkFRVnFtY3UzNExaY3pQWkxmX0dR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Guerra entre EUA e Irã ameaça fertilizantes e acende alerta para agricultores do Brasil - A Referência</t>
+          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12/07/2026 21:58</t>
+          <t>12/07/2026 21:41</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOc0o3SzR2VWFVY3M3RVRIZ3dQUThlTmJpVXpQSnp2X28yMlFsNER4S3RYOFhoQy03YUZCdm9MOG1NRDVaMmR4cXNiVy1vQzNzaXlMdTFDek9kUVZiNWNpSmJxckFCZmJVMkpWY0Y5SURXZks4VG10M1l3dlNkTGlpV2lvMEtNaEpRam5sUUo4bmE2Qk1VSGl0VHY2UjV1M0hKZ0lCUG00ZENSVkFRVnFtY3UzNExaY3pQWkxmX0dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
+          <t>Desenvolvido ao longo de quase duas décadas num laboratório, o concreto "vivo" com bactérias que fabricam calcário e fecham sozinhas as próprias rachaduras já chegou a áreas do aeroporto de Schiphol e a um estacionamento de 12.000 m² na Holanda - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>12/07/2026 21:41</t>
+          <t>12/07/2026 20:45</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxONFI3b2x4REx2NFFYMm5rQTdWTl9YU1JsS1VGa0w0azdsczVXQzdaSHBWbHNXeXpNS1ZtUVlRU1VUUWtSR3ZLc2hhMWdjbklURTk4Q0JycEJpU1l6ZGtNVldqWUV0Q0lzd1pNdGZVNmlhUE84dmhtOTEyRHFLVFRoUnRmaHNYRHZMVzQySG1tQl9UaU1kOUFvS2N5NmZSU0lvNUdPNjBjanF1a2RQVE4wSUdRSVFUY0ZfbnZQT291R0xrX2ZtOWhHaVlNcnI1NVdWZ0JmM0huN0lMV0s2ZkZXLUJ3dnFHZTh1bXZTcVhzMDRFVldaQ3VSZmkyLWRXMGFiZ3p1dUh2by1uLWUyTGM4bXA2dmswVUVkazM5MGluSV9nYVhEUTYwRWF6T1JpSjhKbHFIYXpQVS1Sc0lDSWc5VVNKNjhIS0U?oc=5</t>
         </is>
       </c>
     </row>
@@ -1348,39 +1348,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Desenvolvido ao longo de quase duas décadas num laboratório, o concreto "vivo" com bactérias que fabricam calcário e fecham sozinhas as próprias rachaduras já chegou a áreas do aeroporto de Schiphol e a um estacionamento de 12.000 m² na Holanda - CPG Click Petróleo e Gás</t>
+          <t>Alta nos fosfatados: o desafio do produtor e o papel estratégico do calcário por Surama Geleilate - Conexao 085</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12/07/2026 20:45</t>
+          <t>12/07/2026 18:04</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxONFI3b2x4REx2NFFYMm5rQTdWTl9YU1JsS1VGa0w0azdsczVXQzdaSHBWbHNXeXpNS1ZtUVlRU1VUUWtSR3ZLc2hhMWdjbklURTk4Q0JycEJpU1l6ZGtNVldqWUV0Q0lzd1pNdGZVNmlhUE84dmhtOTEyRHFLVFRoUnRmaHNYRHZMVzQySG1tQl9UaU1kOUFvS2N5NmZSU0lvNUdPNjBjanF1a2RQVE4wSUdRSVFUY0ZfbnZQT291R0xrX2ZtOWhHaVlNcnI1NVdWZ0JmM0huN0lMV0s2ZkZXLUJ3dnFHZTh1bXZTcVhzMDRFVldaQ3VSZmkyLWRXMGFiZ3p1dUh2by1uLWUyTGM4bXA2dmswVUVkazM5MGluSV9nYVhEUTYwRWF6T1JpSjhKbHFIYXpQVS1Sc0lDSWc5VVNKNjhIS0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMWtCT3VtS2lJOWlkOW9RT0JCX29mUi1aTE1Vb0J2TFBIc3p1Z2x6VnhrelhEcHYyQlJfeTVxdndiWUN6Y3V0a2tMOEVnUXlWWFVmMS1uelRvc3ZjMXk3Mmp5NjRTV3lRX3pNUGJ4WkZobFBwSWVJLWh2dGxKUWtKUHluby1jRjhFM1ZFYmNKZEs3Tlk2Q3oxQ2s5eUoxRm9halFVeER3OUp2YWhMaUpCdWZLWUVCUVdfU29ZMWRDd3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alta nos fosfatados: o desafio do produtor e o papel estratégico do calcário por Surama Geleilate - Conexao 085</t>
+          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12/07/2026 18:04</t>
+          <t>12/07/2026 14:31</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMWtCT3VtS2lJOWlkOW9RT0JCX29mUi1aTE1Vb0J2TFBIc3p1Z2x6VnhrelhEcHYyQlJfeTVxdndiWUN6Y3V0a2tMOEVnUXlWWFVmMS1uelRvc3ZjMXk3Mmp5NjRTV3lRX3pNUGJ4WkZobFBwSWVJLWh2dGxKUWtKUHluby1jRjhFM1ZFYmNKZEs3Tlk2Q3oxQ2s5eUoxRm9halFVeER3OUp2YWhMaUpCdWZLWUVCUVdfU29ZMWRDd3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1392,61 +1392,61 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12/07/2026 14:31</t>
+          <t>12/07/2026 12:51</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12/07/2026 12:51</t>
+          <t>12/07/2026 10:11</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 4 - ArchDaily</t>
+          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/07/2026 12:38</t>
+          <t>12/07/2026 09:03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPYnpEazhULUNDcnlGY0ZKOXJrNTZiRTlBTFJab2pSSXZIOWtzU3lPTU1lUUI0TC1BdVd5MkdWS3pYT2syLWFhUGZMT0FHLUJaVXRjVll6UG50b2lEWmMwbmgtM2tsdjBJd0IxTmtscGtIbTEzbEg4dmwxTmxlSmI3NFRpb2htcnVMZXNNWkI1V2FWNUUxeXZKNVprbU11a2R0dlBwbzd5aXNyN2VyYU8zQUd5TmE5XzNNcERVTWo4U3lxNEtodmtpWGkzZk1lNE02OG8yVHh5SzdMRllKRzRsSVVta1pzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 12 - ArchDaily</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12/07/2026 10:11</t>
+          <t>11/07/2026 23:15</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSklsTFVWbjJRWGtvNWtSM2lpTFpVT1g0Um93ckxMR3o3RWZKNE5QMmpmWmVNS05QLWdaUFlvXzNmY3FFV0l6d1VDX0R1cWdaS1lqTm9vY1U5U1VEbXhhM2NQa0VKWnJneWsxTGNsb0lHTW1rekdmbUNtc1BoNDFJcUdURVFueWlnZGRrUTBWOW1UOTlhMExHSFcyNGdEVTZQaUZsWXFVVW9XaUoxYklCQWpqdGY0QzNLMFI5WWlZMDhZQlpNV0N6WVdENUhkWlBVeGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1480,39 +1480,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
+          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12/07/2026 09:03</t>
+          <t>11/07/2026 04:40</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 12 - ArchDaily</t>
+          <t>Importação de ureia em junho de 2026: preço sobe e volume cai - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>11/07/2026 23:15</t>
+          <t>11/07/2026 04:35</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSklsTFVWbjJRWGtvNWtSM2lpTFpVT1g0Um93ckxMR3o3RWZKNE5QMmpmWmVNS05QLWdaUFlvXzNmY3FFV0l6d1VDX0R1cWdaS1lqTm9vY1U5U1VEbXhhM2NQa0VKWnJneWsxTGNsb0lHTW1rekdmbUNtc1BoNDFJcUdURVFueWlnZGRrUTBWOW1UOTlhMExHSFcyNGdEVTZQaUZsWXFVVW9XaUoxYklCQWpqdGY0QzNLMFI5WWlZMDhZQlpNV0N6WVdENUhkWlBVeGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFB0ZGdwcy1Wb1F1M3dJbm50LTVDZndVVHRyUGp2NGRiN1BQVzdISGZaWWdqRjQxY3RyRTd4S3BQQ2o2ZnZNbFlwOWVNenpGcGl0aERvQzJyYUtZNUdpSVpoZFEwRzZjZFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -1524,39 +1524,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - MSN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>11/07/2026 04:40</t>
+          <t>11/07/2026 00:13</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOUmNxdWp0UlRQWmJiM3ZlY2FwZ0Nad2NUMzF0M2ZJSE43NXg5U29DT0wxSURtQTlLdnpYdlRUZXhSaFB6UUlpYmxfN09VeUs1X1B4MTd1ODVyb1hpT0w1THpjY0FTVGQwUXdJTkY4akpiVXAxYnFydnlVR0k2ckYtQW5Yckp5TUtBNTFpVDJkek85cnhsbnRYSnF3cjJQbV9zTW9US3lUN1EtVFdjSm5EcWRhRXdtR3d4WVRSZWxwR1NoRHZUTm0tZVhrMUNUMTVwa3N0LXJCREhEUEFJTVd6TUp1QzJ3Mm1kUWNjRVVtczVWWDFa?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Importação de ureia em junho de 2026: preço sobe e volume cai - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11/07/2026 04:35</t>
+          <t>10/07/2026 23:16</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFB0ZGdwcy1Wb1F1M3dJbm50LTVDZndVVHRyUGp2NGRiN1BQVzdISGZaWWdqRjQxY3RyRTd4S3BQQ2o2ZnZNbFlwOWVNenpGcGl0aERvQzJyYUtZNUdpSVpoZFEwRzZjZFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1568,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - MSN</t>
+          <t>Anderson articula frente em Brasília em defesa dos empregos e da indústria - JM Online</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11/07/2026 00:13</t>
+          <t>10/07/2026 23:02</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOUmNxdWp0UlRQWmJiM3ZlY2FwZ0Nad2NUMzF0M2ZJSE43NXg5U29DT0wxSURtQTlLdnpYdlRUZXhSaFB6UUlpYmxfN09VeUs1X1B4MTd1ODVyb1hpT0w1THpjY0FTVGQwUXdJTkY4akpiVXAxYnFydnlVR0k2ckYtQW5Yckp5TUtBNTFpVDJkek85cnhsbnRYSnF3cjJQbV9zTW9US3lUN1EtVFdjSm5EcWRhRXdtR3d4WVRSZWxwR1NoRHZUTm0tZVhrMUNUMTVwa3N0LXJCREhEUEFJTVd6TUp1QzJ3Mm1kUWNjRVVtczVWWDFa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTEZpWWZfRnhBMFNlTHVkck43ajB5eWM4ZG5Ia1BQRUFHMTdaLTZoZlluV0Zac243OTE4dUhocS1OWUdVMk10RFJHcmRVS29UNWVIX2VsQUdNeVQ3dndyUEEwUkRDSkxzc3VuN1VBVC1XdkFpRjhzRFh1elJzNlowcklvVHlUaEd5aWlOY0pIT2RLbi1FNnFVY2RKbDNWejF0NFJuVXBmNUJIendFWFJYOWVjUHF3S0nSAb8BQVVfeXFMTVo3Yml6b05zemlGcVJoYnlXUk1ER1dXSUpDMXJqbWJZb0l5U2xWbk1sVnF5NHNGUWd4OGdFQXE5YzNCdTZRWmZiblpXdGUza0hKaDVJRXFQa01vSzQxYmp0dTJoRUVYSGdjY0d1eGpPdW1JT1QwQ09RU3BsV0JRamY3ZUhvd2YxcWw5MEZidEN1NDlHZ0ZjMFp6blZWcEQ3R01iUGxiZmw3aDJyMElEX3JDX1dCU0xuS2o5amc0clk?oc=5</t>
         </is>
       </c>
     </row>
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10/07/2026 23:16</t>
+          <t>10/07/2026 21:55</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Anderson articula frente em Brasília em defesa dos empregos e da indústria - JM Online</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10/07/2026 23:02</t>
+          <t>10/07/2026 19:30</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTEZpWWZfRnhBMFNlTHVkck43ajB5eWM4ZG5Ia1BQRUFHMTdaLTZoZlluV0Zac243OTE4dUhocS1OWUdVMk10RFJHcmRVS29UNWVIX2VsQUdNeVQ3dndyUEEwUkRDSkxzc3VuN1VBVC1XdkFpRjhzRFh1elJzNlowcklvVHlUaEd5aWlOY0pIT2RLbi1FNnFVY2RKbDNWejF0NFJuVXBmNUJIendFWFJYOWVjUHF3S0nSAb8BQVVfeXFMTVo3Yml6b05zemlGcVJoYnlXUk1ER1dXSUpDMXJqbWJZb0l5U2xWbk1sVnF5NHNGUWd4OGdFQXE5YzNCdTZRWmZiblpXdGUza0hKaDVJRXFQa01vSzQxYmp0dTJoRUVYSGdjY0d1eGpPdW1JT1QwQ09RU3BsV0JRamY3ZUhvd2YxcWw5MEZidEN1NDlHZ0ZjMFp6blZWcEQ3R01iUGxiZmw3aDJyMElEX3JDX1dCU0xuS2o5amc0clk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1634,105 +1634,105 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
+          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10/07/2026 21:55</t>
+          <t>10/07/2026 17:18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10/07/2026 19:30</t>
+          <t>10/07/2026 17:16</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
+          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10/07/2026 17:18</t>
+          <t>10/07/2026 15:37</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPaG9iU21CY05aUGR1OExxRUNPbGtmTGZVOUtISUxJUTY5QThsM0tfNkQyVWNuckN0ckVral9IR05uVThNUDVYOXhvaTVvclhlMzhtQzkyTC1jQnlGbE9iSVVKcDNZM0FOT01nTXBRVWJuVWdLNHR3Xzhvd09QSHZmRU1TcFppeFA2dE9sZzEweHdVOURTZ1JHTlJBRnlybUNlcGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
+          <t>Mosaic amplia paralisações em Minas Gerais e anuncia hibernação da unidade de Uberaba - Portal Imbiara</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10/07/2026 17:16</t>
+          <t>10/07/2026 13:47</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQR0RFQVNmTDJGRnpaOEoydWZRVU1RLWlhUkRTYmRPaFExWDhrRWJpbDFfQVB6RXhMYkZKNThBUVB1cWwxRlFpZUJXdi1qNTdVenhZbVo4MmZGaUM1Rnl1MkVIY2c3M0ZnRHhCY3NROFJpZmMtRWVSNHNzZFFodS1iOEFULVJoTUw1eUVzc3ZRaEE3NHo4LWF3RUhKdTdPa0ZJVndxWWJTdlpBUVRZMnFPakVKcGtJZEt4aW1vbG84a3JsWEJfazRkMkJDSzR2Y0NkQjVnbUNyVGY0S2NDM3NoZ2ptd05iQ0JQUmM5WHVHYzV1Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Galeria de Facade Panels - Dietfurt Limestone - 9 - ArchDaily</t>
+          <t>Melhora dos preços da soja e recuo do Super Simples conferem relações de troca mais favoráveis ao produtor brasileiro - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>10/07/2026 16:51</t>
+          <t>10/07/2026 13:22</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPQmZoejM4a1I4S2tFa011djlVUGY4ZTY2aGlfTTIzWjBnaVRZVDY3MFQ0ZVl0R2NqeVhvclRjdjNuQUtmdmtKb2pUbXREY3p1aDNWdURBNlhJMnBqVjVqYjRNZWE1SENpaVVMbkZqNTRBTDZIcHBBRExmWUI1UXE0MlFQdnY0RDNpdnhaSlp0SDJINEh3Qy1EZklNNVRVMGpsRTFEU0xKeVhBUlpNUWpSQUN2MVRaY3JlYUp4QXRKaHhSaGxvTUFBaWVzMWoxNVJ1UHlFNkRhV3duelZqc3VKSkYyNUhUaHhkdVMtSUhKM0E0NExKaUxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOQ1BxcXlmR1RXMnRTWi05ZHpOLTZWNlBPRkRYaHZuOGJaTWtnTDVWWW9vUmZRd1RoaEt3SkVEMVlOSHZTdWowc3d1U0ZjQzZzazFNSEFJZE1MTzZxREgyaS1nZERJMVB1U0FhS0g4ckEzUkNUWEpydjdUS2dBemxRWHNpa180RnZuM3Zfa0pjT2NzNzJOOS1zTk9UZDRXSVdJOUp1VWkyb1VaY0lSOVJvNDRxOWlNeXB5S1ZiSFlpSEg1emtzeG9hWUNHMnBDdF9JazBOQ0dFdkZ6N0lmUzc5dEJQWkRqZlBSTENjQXNNalM4Z2gwOTVJUHNibGI0VFRQeW1tSHdQdjlOdEJ6ZmVQTll6bktwTDZBQXcybW5B0gGjAkFVX3lxTFBQVzY1NHBLeU5Tak81dmlTeml1ZFllWHk4aU9PUDIwaWJDaGpnTzNiZTJXekxWNmtkMW1TX0FLREFET01YVndNWDlyeVg1aElCQWs3Um5NaHNQMzlKOXRlM3JjVkxqNVJwaVVxdVdsSTZlaTdmdWVXcDRaU0FOTDZoZ1ByZE9Jc0RPWEhEMlhLTGpDY2pTb2NBdW00VmZZMlVjWGxaT3RlSEt0OFliRDJiVWJPOG9EczZmaHJsOUJmaTU2YzRJSHZoQnMtY2k1YS1iaEVybjBKTUJJdEpnY1ZHY2VNbF9xMnFXQVZNeVZBVDJkOUNxWmxaR1lrRl9pekxNemVfMzdDRjFBMWVySmZvbEcxYTA1OGlsWFByYzhKeXFzbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1744,105 +1744,105 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
+          <t>Tensões entre EUA e Irã ameaçam fornecimento de fertilizantes para o Brasil - Globo Rural</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10/07/2026 15:37</t>
+          <t>10/07/2026 13:15</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPaG9iU21CY05aUGR1OExxRUNPbGtmTGZVOUtISUxJUTY5QThsM0tfNkQyVWNuckN0ckVral9IR05uVThNUDVYOXhvaTVvclhlMzhtQzkyTC1jQnlGbE9iSVVKcDNZM0FOT01nTXBRVWJuVWdLNHR3Xzhvd09QSHZmRU1TcFppeFA2dE9sZzEweHdVOURTZ1JHTlJBRnlybUNlcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOai1tRmFORnVmWkZnVlNVbzJZcFlfdDFJeDRua0xvVnFZRUlZa05vbHlWMjY0Z1BncGpPVEVmdncwOWMzQWF0MjRqT0VaODllRWpBN0ZZam50TDdCaUxfcmFpVG9sZ282VTZqU1ZTYjItXzRfZUV4NHBrUUtCLVNQdER4VW5pVVhMRGlTa2VrTnhYdXRIaTVYNS12T1luazFTa2Q3Sm9tUXdHZnRsRWV4RTNPS0x6elhqT2xXVmZWblJYSTFRdUdXcmVKamtUeVHSAd4BQVVfeXFMTTJsTWZ0ZS1XM0hIcFpHX2J3d2ZqNmQ3dWllWVFHVEhhNWtNcU95a3loYnpJLVppZzlickRHMDV0YmZsb1ZjTWpubEpFQkQ2QVlEUnIyM3NEbmt2N1V1Tkt3NTgtYk9ybmJUSURNYnJsU3pzaTJlaTEzM19tR2xHTmE4aS1BMElVQ19VWmx6QXBiZklzei12QURCZ050YjhRS3Y3QTFmSEduZ0FCV0RhT3BHeVI5ZVgzQm0wUTZkaTRCaFZJOFBZTGRNd29DRlEyY3B3RXAzOEk5ZmtXalV3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mosaic amplia paralisações em Minas Gerais e anuncia hibernação da unidade de Uberaba - Portal Imbiara</t>
+          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>10/07/2026 13:47</t>
+          <t>10/07/2026 11:32</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQR0RFQVNmTDJGRnpaOEoydWZRVU1RLWlhUkRTYmRPaFExWDhrRWJpbDFfQVB6RXhMYkZKNThBUVB1cWwxRlFpZUJXdi1qNTdVenhZbVo4MmZGaUM1Rnl1MkVIY2c3M0ZnRHhCY3NROFJpZmMtRWVSNHNzZFFodS1iOEFULVJoTUw1eUVzc3ZRaEE3NHo4LWF3RUhKdTdPa0ZJVndxWWJTdlpBUVRZMnFPakVKcGtJZEt4aW1vbG84a3JsWEJfazRkMkJDSzR2Y0NkQjVnbUNyVGY0S2NDM3NoZ2ptd05iQ0JQUmM5WHVHYzV1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Melhora dos preços da soja e recuo do Super Simples conferem relações de troca mais favoráveis ao produtor brasileiro - Notícias Agrícolas</t>
+          <t>Após anúncio de paralisação da Mosaic, Prefeitura cria observatório de fertilizantes em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10/07/2026 13:22</t>
+          <t>10/07/2026 10:36</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOQ1BxcXlmR1RXMnRTWi05ZHpOLTZWNlBPRkRYaHZuOGJaTWtnTDVWWW9vUmZRd1RoaEt3SkVEMVlOSHZTdWowc3d1U0ZjQzZzazFNSEFJZE1MTzZxREgyaS1nZERJMVB1U0FhS0g4ckEzUkNUWEpydjdUS2dBemxRWHNpa180RnZuM3Zfa0pjT2NzNzJOOS1zTk9UZDRXSVdJOUp1VWkyb1VaY0lSOVJvNDRxOWlNeXB5S1ZiSFlpSEg1emtzeG9hWUNHMnBDdF9JazBOQ0dFdkZ6N0lmUzc5dEJQWkRqZlBSTENjQXNNalM4Z2gwOTVJUHNibGI0VFRQeW1tSHdQdjlOdEJ6ZmVQTll6bktwTDZBQXcybW5B0gGjAkFVX3lxTFBQVzY1NHBLeU5Tak81dmlTeml1ZFllWHk4aU9PUDIwaWJDaGpnTzNiZTJXekxWNmtkMW1TX0FLREFET01YVndNWDlyeVg1aElCQWs3Um5NaHNQMzlKOXRlM3JjVkxqNVJwaVVxdVdsSTZlaTdmdWVXcDRaU0FOTDZoZ1ByZE9Jc0RPWEhEMlhLTGpDY2pTb2NBdW00VmZZMlVjWGxaT3RlSEt0OFliRDJiVWJPOG9EczZmaHJsOUJmaTU2YzRJSHZoQnMtY2k1YS1iaEVybjBKTUJJdEpnY1ZHY2VNbF9xMnFXQVZNeVZBVDJkOUNxWmxaR1lrRl9pekxNemVfMzdDRjFBMWVySmZvbEcxYTA1OGlsWFByYzhKeXFzbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVWJ0ZEcyc3AyMDBZQ3BPNDVkYV9LdnJPZkNFeWZQSkVINjlqTm5TQUI5NDhWT2lrZ0s4ME52aDc5SnVYMkFieWZmeGthbndlQjRFeFM2NTVfX3I0bmJ4bVFTZmR5YXMteHVMT3NaMXpsYmdqZGVfVXU1YkptN243NnRiVlBxaHlOdEJpMGczcmdDLWppdzRlZ01XZFFxZVJIQ1R2Q05iTjh3N2lOcFM4bi1nd2VBeExEVklueDMzeWRIX1VubXhXVG5BcUl4amxPZmfSAdoBQVVfeXFMTjdGeU03cEdhN0NpRDNUMHozamhOZ3VKT3VjRzlaMnNNR0xaRjhaYUhZUGJOZkE1SEVOM3hhUnlyMm9zX3N1bjVCQ0RlVU9MX0o4RVZNOVlIQkhKRjY1bFlVd2l2aVZCSEhGaTgyVGh2V1Q5UUU1c1lETnY1QlNDT3lUa3Q0Z0FMUUktcENzYmdBTEVzdUtNakJudFRRTFo4UDhncEdDYXJROTd6eGdaUVNOSUVyRjhfeXp4eXlZSmx1ODZpZ1o4VEppc0VVT3laci1YeWE5QnhWTWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tensões entre EUA e Irã ameaçam fornecimento de fertilizantes para o Brasil - Globo Rural</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>10/07/2026 13:15</t>
+          <t>10/07/2026 10:16</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOai1tRmFORnVmWkZnVlNVbzJZcFlfdDFJeDRua0xvVnFZRUlZa05vbHlWMjY0Z1BncGpPVEVmdncwOWMzQWF0MjRqT0VaODllRWpBN0ZZam50TDdCaUxfcmFpVG9sZ282VTZqU1ZTYjItXzRfZUV4NHBrUUtCLVNQdER4VW5pVVhMRGlTa2VrTnhYdXRIaTVYNS12T1luazFTa2Q3Sm9tUXdHZnRsRWV4RTNPS0x6elhqT2xXVmZWblJYSTFRdUdXcmVKamtUeVHSAd4BQVVfeXFMTTJsTWZ0ZS1XM0hIcFpHX2J3d2ZqNmQ3dWllWVFHVEhhNWtNcU95a3loYnpJLVppZzlickRHMDV0YmZsb1ZjTWpubEpFQkQ2QVlEUnIyM3NEbmt2N1V1Tkt3NTgtYk9ybmJUSURNYnJsU3pzaTJlaTEzM19tR2xHTmE4aS1BMElVQ19VWmx6QXBiZklzei12QURCZ050YjhRS3Y3QTFmSEduZ0FCV0RhT3BHeVI5ZVgzQm0wUTZkaTRCaFZJOFBZTGRNd29DRlEyY3B3RXAzOEk5ZmtXalV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>10/07/2026 11:32</t>
+          <t>10/07/2026 08:34</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Após anúncio de paralisação da Mosaic, Prefeitura cria observatório de fertilizantes em Uberaba - JM Online</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10/07/2026 10:36</t>
+          <t>10/07/2026 07:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVWJ0ZEcyc3AyMDBZQ3BPNDVkYV9LdnJPZkNFeWZQSkVINjlqTm5TQUI5NDhWT2lrZ0s4ME52aDc5SnVYMkFieWZmeGthbndlQjRFeFM2NTVfX3I0bmJ4bVFTZmR5YXMteHVMT3NaMXpsYmdqZGVfVXU1YkptN243NnRiVlBxaHlOdEJpMGczcmdDLWppdzRlZ01XZFFxZVJIQ1R2Q05iTjh3N2lOcFM4bi1nd2VBeExEVklueDMzeWRIX1VubXhXVG5BcUl4amxPZmfSAdoBQVVfeXFMTjdGeU03cEdhN0NpRDNUMHozamhOZ3VKT3VjRzlaMnNNR0xaRjhaYUhZUGJOZkE1SEVOM3hhUnlyMm9zX3N1bjVCQ0RlVU9MX0o4RVZNOVlIQkhKRjY1bFlVd2l2aVZCSEhGaTgyVGh2V1Q5UUU1c1lETnY1QlNDT3lUa3Q0Z0FMUUktcENzYmdBTEVzdUtNakJudFRRTFo4UDhncEdDYXJROTd6eGdaUVNOSUVyRjhfeXp4eXlZSmx1ODZpZ1o4VEppc0VVT3laci1YeWE5QnhWTWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10/07/2026 10:16</t>
+          <t>09/07/2026 21:17</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1898,61 +1898,61 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10/07/2026 08:34</t>
+          <t>09/07/2026 20:05</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Importações de ureia recuam 32% no semestre, mas fosfatados exigem aceleração nas compras - MT Econômico</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10/07/2026 07:00</t>
+          <t>09/07/2026 18:35</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNc3RsNG8zMnZxOFBSY0J0UmxuTlA1MlNPbmotbGwwZEpxLXhiXzB0cnVqVFlrZGpqek5FY0c3LWxXWF9VYkZHem1KTEtlNHN0SDdNSDFNeUJEd3luVmp5VWhpMlBBVUpSbnVLWVF5NWFXMWpUWE4tb1ZqeURjTzF0bGZKclNPZGJoelJiQ3pwMlVJa2JJelV3c1p5RTNJY3NleWowTndvWlItZl9WX1lUd2U5SnNfU2gzc0pNb2JoUkxhV2dxWi1fOEJQRHg5NjVTWEZHT0lLM1o5RWlRNk85eg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
+          <t>Prefeitura de Chuvisca define distribuição de ureia para produtores de leite - Portal ClicR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>09/07/2026 21:17</t>
+          <t>09/07/2026 16:46</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdHRaa3pPRVdoSzFsWGJiZElFNEc3QTFhYmpEX1Z1bC1uNk1uQXhqM2Nld2kwTGtqNlBsVTdaZXpBbGdia2xqODlMNU52NlRNaTVsWDl6dG52ek9WQ3dPLVBMS0c2eTNsUUVHUmx1RERiRUVnTXk5dC15X2ttYmxIRmx2VXBjS20waGJJeWFUS1ZTdHJMcGJ0ZHB6M01GcGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1964,83 +1964,83 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>09/07/2026 20:05</t>
+          <t>09/07/2026 16:20</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Importações de ureia recuam 32% no semestre, mas fosfatados exigem aceleração nas compras - MT Econômico</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>09/07/2026 18:35</t>
+          <t>09/07/2026 14:52</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNc3RsNG8zMnZxOFBSY0J0UmxuTlA1MlNPbmotbGwwZEpxLXhiXzB0cnVqVFlrZGpqek5FY0c3LWxXWF9VYkZHem1KTEtlNHN0SDdNSDFNeUJEd3luVmp5VWhpMlBBVUpSbnVLWVF5NWFXMWpUWE4tb1ZqeURjTzF0bGZKclNPZGJoelJiQ3pwMlVJa2JJelV3c1p5RTNJY3NleWowTndvWlItZl9WX1lUd2U5SnNfU2gzc0pNb2JoUkxhV2dxWi1fOEJQRHg5NjVTWEZHT0lLM1o5RWlRNk85eg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Prefeitura de Chuvisca define distribuição de ureia para produtores de leite - Portal ClicR</t>
+          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>09/07/2026 16:46</t>
+          <t>09/07/2026 14:32</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdHRaa3pPRVdoSzFsWGJiZElFNEc3QTFhYmpEX1Z1bC1uNk1uQXhqM2Nld2kwTGtqNlBsVTdaZXpBbGdia2xqODlMNU52NlRNaTVsWDl6dG52ek9WQ3dPLVBMS0c2eTNsUUVHUmx1RERiRUVnTXk5dC15X2ttYmxIRmx2VXBjS20waGJJeWFUS1ZTdHJMcGJ0ZHB6M01GcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>09/07/2026 16:20</t>
+          <t>09/07/2026 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2052,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>09/07/2026 14:52</t>
+          <t>09/07/2026 14:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2074,61 +2074,61 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>09/07/2026 14:32</t>
+          <t>09/07/2026 13:56</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>09/07/2026 14:00</t>
+          <t>09/07/2026 13:50</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
+          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>09/07/2026 14:00</t>
+          <t>09/07/2026 12:28</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
+          <t>Misturadora da Mosaic no DIMIC encerra atividades e 22 trabalhadores são demitidos em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>09/07/2026 13:56</t>
+          <t>09/07/2026 12:27</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPc2dMOGg4WGRhNHZOZEt2NVNnRDdUT3RoN1o4UTZjeGR4bHJxRUxDazBtZzVtRW5JYzBta2tKb3A1WWtSMF9jMWx5c2RVRkkxU1FheFNFd2s2RkktNkNZeHFaeFhPWnhqbmNvRGRfTk1QRGFTckdBVW5RZ0t1UmdKYTFYMmRDdXNfd2g0ejFxanpYOE5kUDJ6aW5Ick0zby1ORVpndEdwUlM4Wi0yR3ppcU5DYko0MkpDa0dLWE5Ca3N2cFliWFR5bTVTWENCZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2162,39 +2162,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - negociosba.com.br</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>09/07/2026 13:50</t>
+          <t>09/07/2026 02:57</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZEZja1RxUjJDTWtwU2F1dEtha0RLamR6YXM4X3BnR0RUUkttaktoa1NzQXIyN29ack1Od2lWdFp1a1F6RjFFWlVmTDUtN3JTTmdRRWtMTHZlQ0xhd2NQUV8zT3NQRUZlanJQaTBieG4teG1wUFBSM3hLT1JWRGJ2cXFNWmRDX1V5MWljZWFHd1BfX09wSENFSDV5NEVGcTlMRjJMcml2WUpERkg3RVlv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>09/07/2026 12:28</t>
+          <t>08/07/2026 23:25</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
@@ -2206,39 +2206,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Misturadora da Mosaic no DIMIC encerra atividades e 22 trabalhadores são demitidos em Catalão - Diante do Fato Catalão</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - TradingView</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>09/07/2026 12:27</t>
+          <t>08/07/2026 23:25</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPc2dMOGg4WGRhNHZOZEt2NVNnRDdUT3RoN1o4UTZjeGR4bHJxRUxDazBtZzVtRW5JYzBta2tKb3A1WWtSMF9jMWx5c2RVRkkxU1FheFNFd2s2RkktNkNZeHFaeFhPWnhqbmNvRGRfTk1QRGFTckdBVW5RZ0t1UmdKYTFYMmRDdXNfd2g0ejFxanpYOE5kUDJ6aW5Ick0zby1ORVpndEdwUlM4Wi0yR3ppcU5DYko0MkpDa0dLWE5Ca3N2cFliWFR5bTVTWENCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5odGhpYmZGMWVBdmQzQ0JLajR0d3NCdmQxOUtrdDdGRWh4UnZTd21JS0Jua3c0eUtyUkVmVEVXVDVoWW5UZXhIcG05R0w2Y2lCcFpkLU5RcjczTHZmeS1ZUExlX3BHZVJFc1hOaEpmRTJ0MFplenpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - negociosba.com.br</t>
+          <t>Justiça homologa acordo de R$ 11 milhões para reparação ambiental em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>09/07/2026 02:57</t>
+          <t>08/07/2026 21:28</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZEZja1RxUjJDTWtwU2F1dEtha0RLamR6YXM4X3BnR0RUUkttaktoa1NzQXIyN29ack1Od2lWdFp1a1F6RjFFWlVmTDUtN3JTTmdRRWtMTHZlQ0xhd2NQUV8zT3NQRUZlanJQaTBieG4teG1wUFBSM3hLT1JWRGJ2cXFNWmRDX1V5MWljZWFHd1BfX09wSENFSDV5NEVGcTlMRjJMcml2WUpERkg3RVlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQN1d3cHVseUJvTWtEQTVYQUZNVGV0MGJ0MlNTS0VDaVFlNFlVNGxwNXpCcndCaHpDYm13OXFHOHppZF9kcHZhc1Zjd2F2VWhzOVIwalFRRjh5VE9kMmhPZXNCcnJKb1ctQmJta2VWV3NTVHZSaVJyTDN0YVlqWHhpV0JLT3dpbmpSVXpleW5RNlpFMGE3SWtxemplY0c1czJIcVAtbHlwWm5sREtSR1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -2250,127 +2250,127 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Mosaic reduz operações no Brasil com crise de enxofre - boca.com.br</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>08/07/2026 23:25</t>
+          <t>08/07/2026 21:15</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQU3dtd1pHdkVKMDlGNnhQM1RZa1FKU2NCMDBFZjJMSVhfbjBXT3M4NTUxWENhenJkdWRmdWxTdjZ5dlI1bDh5Qng1VEFweXRxRUsyWmNVQXNicGIyNnM2Q1JPMGFiMWl5ZllFV2dpQzQ0eG5zdThpVWo4R2V3eW82V18xcWt3OU5jZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - TradingView</t>
+          <t>Henrique Carballal recebe cúpula da multinacional CMOC para alinhar metas ESG na produção de ouro em Santaluz - Classe Politica</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>08/07/2026 23:25</t>
+          <t>08/07/2026 19:52</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5odGhpYmZGMWVBdmQzQ0JLajR0d3NCdmQxOUtrdDdGRWh4UnZTd21JS0Jua3c0eUtyUkVmVEVXVDVoWW5UZXhIcG05R0w2Y2lCcFpkLU5RcjczTHZmeS1ZUExlX3BHZVJFc1hOaEpmRTJ0MFplenpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOVGdidnBPSEhqUXZwenhwVXg1N0N3V0J4czZJZVJFUzhvR2lOY2g5YWszUHVTcjg5NnVNeF9kVExVb3FGQ0dHMGtqSnZ1QlZCWmMtbTVYTGZkZG1RSFlzVHd2SE5mQ25wSHFWZ2FwLVB3bDFCc1VmVUNveEJ4cDFlMFNNeXdqRmJ1OTBpRkEzdWRiUzNzMG0tM1NBSFREQWZKek5Yelh6WEZxUnRYTW4wUEl1MnZ3WnV5dFV2UjlkSThoa0Zta3dCSk5ZVFFKWFlyZUxhUnpvaVF1d3RJak5ZOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Justiça homologa acordo de R$ 11 milhões para reparação ambiental em Catalão - Tribuna do Planalto</t>
+          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>08/07/2026 21:28</t>
+          <t>08/07/2026 17:55</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQN1d3cHVseUJvTWtEQTVYQUZNVGV0MGJ0MlNTS0VDaVFlNFlVNGxwNXpCcndCaHpDYm13OXFHOHppZF9kcHZhc1Zjd2F2VWhzOVIwalFRRjh5VE9kMmhPZXNCcnJKb1ctQmJta2VWV3NTVHZSaVJyTDN0YVlqWHhpV0JLT3dpbmpSVXpleW5RNlpFMGE3SWtxemplY0c1czJIcVAtbHlwWm5sREtSR1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil com crise de enxofre - boca.com.br</t>
+          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>08/07/2026 21:15</t>
+          <t>08/07/2026 17:33</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQU3dtd1pHdkVKMDlGNnhQM1RZa1FKU2NCMDBFZjJMSVhfbjBXT3M4NTUxWENhenJkdWRmdWxTdjZ5dlI1bDh5Qng1VEFweXRxRUsyWmNVQXNicGIyNnM2Q1JPMGFiMWl5ZllFV2dpQzQ0eG5zdThpVWo4R2V3eW82V18xcWt3OU5jZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Henrique Carballal recebe cúpula da multinacional CMOC para alinhar metas ESG na produção de ouro em Santaluz - Classe Politica</t>
+          <t>Cidades | Prefeitura de Palmas inicia distribuição de calcário para agricultores familiares - T1 Notícias</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>08/07/2026 19:52</t>
+          <t>08/07/2026 17:12</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOVGdidnBPSEhqUXZwenhwVXg1N0N3V0J4czZJZVJFUzhvR2lOY2g5YWszUHVTcjg5NnVNeF9kVExVb3FGQ0dHMGtqSnZ1QlZCWmMtbTVYTGZkZG1RSFlzVHd2SE5mQ25wSHFWZ2FwLVB3bDFCc1VmVUNveEJ4cDFlMFNNeXdqRmJ1OTBpRkEzdWRiUzNzMG0tM1NBSFREQWZKek5Yelh6WEZxUnRYTW4wUEl1MnZ3WnV5dFV2UjlkSThoa0Zta3dCSk5ZVFFKWFlyZUxhUnpvaVF1d3RJak5ZOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPTGVpZUZOWEtDQ21kSGdYRUdqcmFGR1U2MEFwWVI2R1haWTFIOWllVnJfN2xVVWN1aFlneUVhdGlzS3p1NVNicWdfeDVScVkyWVlCYUlKZVhGenBmQTdreVBaQWZoQ1BIMXpMNEpOejI3UEdUSmxwb3Q0QUF5ZGVCX1lwd2RiZUhTQUxta0tZMkV1MXRzb3F6Tnc5QjBhTnoyMUVySEVxT0JoUDNyZzU1QWs5MnRhS09SUlFVck93SVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
+          <t>Produtores rurais já podem aderir à compra coletiva de calcário e gesso em Itabira; saiba mais - DeFato Online</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>08/07/2026 17:55</t>
+          <t>08/07/2026 15:01</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOEgxejNHdTFianBzUHZpWXlzNm5OS1hQazhhZE9mcjhKX1hkMk1PeWhQcHM3MGhoWThpUWJZdENPNms1c0praVl0ZFBxNUNobk9iTzZSMUF3SXQzb0dqRnZSUVJZckN1Nk5UZUZybXQ2VXJYNTYwcm9lcGpXQ2ZyU0dwd3BlaUpSUHJSaGlTY1J3Q2cxWEdwVWd1cmNwVUhnQldka3NTMXhxMFlNdVhYaHROamNmSnh0dnZBN2hvWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2382,17 +2382,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
+          <t>Programa de distribuição de calcário chega a Palmas e deve fortalecer a produção de mais de 500 agricultores familiares - Sou de Palmas</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>08/07/2026 17:33</t>
+          <t>08/07/2026 14:33</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOLTIxSVZ3LVJMUFNpZ0U0UlBkanNMekh6blBXRDUydklHbG5QVTFVX2Nha21GT010cm5BOGJBX3BrVU43UEdqT2YycUxMVGRsSDNnWFBVS0kwTVNRWDlyQ0J1NW5PazRKak9MblpMSkRYSEowZVd1RjhEUFRmWmpjMXdoeTRUeEdGTUl2UVlBdm5keWF0RG1vTXVTMXlSYkJMSmtYd2NNOW1VTTVCNC1NcGllSnlhakZkZVZNVTUzRTV3dWIzNy1QLVNSaGNtR0NNYWRhY0d1d0hoNEZiaTFuVXNrTVlqenR2?oc=5</t>
         </is>
       </c>
     </row>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cidades | Prefeitura de Palmas inicia distribuição de calcário para agricultores familiares - T1 Notícias</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Prefeitura de Palmas.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>08/07/2026 17:12</t>
+          <t>08/07/2026 14:17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPTGVpZUZOWEtDQ21kSGdYRUdqcmFGR1U2MEFwWVI2R1haWTFIOWllVnJfN2xVVWN1aFlneUVhdGlzS3p1NVNicWdfeDVScVkyWVlCYUlKZVhGenBmQTdreVBaQWZoQ1BIMXpMNEpOejI3UEdUSmxwb3Q0QUF5ZGVCX1lwd2RiZUhTQUxta0tZMkV1MXRzb3F6Tnc5QjBhTnoyMUVySEVxT0JoUDNyZzU1QWs5MnRhS09SUlFVck93SVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS3BUcG5OdUxkY0tHNFpTWTdHYkhwaWxVSjJKSVJiTVQzUkw4ZXQ0dTJ3UlhETGVFeDNlOVBlM20xdlVaMnMyZU1zS2VxUndPanFwYVJPc0psRENuVTlhOUh3RmxTZXFtTFVMUjMxWWRpUUF5b20yTUVYRVdpYlh4UkRGQUdIbVk1ZjVBc0VtWk51TE11d3VYQkpfVWxXWWtxS2g2c3JWNThsaHcwSFJ4aVpPMG9QcTRXVlpSLXJxWjJYNzh1NXFpTHFUcE5oOXFsQmU3bFE2RlVBc0NBLS1CMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Produtores rurais já podem aderir à compra coletiva de calcário e gesso em Itabira; saiba mais - DeFato Online</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>08/07/2026 15:01</t>
+          <t>08/07/2026 13:03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOEgxejNHdTFianBzUHZpWXlzNm5OS1hQazhhZE9mcjhKX1hkMk1PeWhQcHM3MGhoWThpUWJZdENPNms1c0praVl0ZFBxNUNobk9iTzZSMUF3SXQzb0dqRnZSUVJZckN1Nk5UZUZybXQ2VXJYNTYwcm9lcGpXQ2ZyU0dwd3BlaUpSUHJSaGlTY1J3Q2cxWEdwVWd1cmNwVUhnQldka3NTMXhxMFlNdVhYaHROamNmSnh0dnZBN2hvWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
@@ -2448,347 +2448,347 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Programa de distribuição de calcário chega a Palmas e deve fortalecer a produção de mais de 500 agricultores familiares - Sou de Palmas</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura de Sorriso</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>08/07/2026 14:33</t>
+          <t>08/07/2026 12:54</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOLTIxSVZ3LVJMUFNpZ0U0UlBkanNMekh6blBXRDUydklHbG5QVTFVX2Nha21GT010cm5BOGJBX3BrVU43UEdqT2YycUxMVGRsSDNnWFBVS0kwTVNRWDlyQ0J1NW5PazRKak9MblpMSkRYSEowZVd1RjhEUFRmWmpjMXdoeTRUeEdGTUl2UVlBdm5keWF0RG1vTXVTMXlSYkJMSmtYd2NNOW1VTTVCNC1NcGllSnlhakZkZVZNVTUzRTV3dWIzNy1QLVNSaGNtR0NNYWRhY0d1d0hoNEZiaTFuVXNrTVlqenR2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Prefeitura de Palmas.</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>08/07/2026 14:17</t>
+          <t>08/07/2026 10:32</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS3BUcG5OdUxkY0tHNFpTWTdHYkhwaWxVSjJKSVJiTVQzUkw4ZXQ0dTJ3UlhETGVFeDNlOVBlM20xdlVaMnMyZU1zS2VxUndPanFwYVJPc0psRENuVTlhOUh3RmxTZXFtTFVMUjMxWWRpUUF5b20yTUVYRVdpYlh4UkRGQUdIbVk1ZjVBc0VtWk51TE11d3VYQkpfVWxXWWtxS2g2c3JWNThsaHcwSFJ4aVpPMG9QcTRXVlpSLXJxWjJYNzh1NXFpTHFUcE5oOXFsQmU3bFE2RlVBc0NBLS1CMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>08/07/2026 13:03</t>
+          <t>07/07/2026 18:35</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura de Sorriso</t>
+          <t>Fertilizantes subiram mais que a inflação com ureia disparada: 149% - MT Econômico</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>08/07/2026 12:54</t>
+          <t>07/07/2026 18:33</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOTlXdllBd0RsRTMwRmZuckFDamxwbDdTVlBYUk01bnVoZHAtOGJEa2lOdmtfMmtCRFBZWFFQOEQ4SnpKSGlJbl9fTFQzdnY3Vlc1M1FnYV9hcFNPVDJMQ0VLY2Y2ZFFFYnBqNDhjSVhRQzhDNi1nLWZiR3BRYnppRDhtMEhoMmxnel85VTJDMFJZS19paFB6WGJ5QmRSWjl6M2ZNYVVSanVZNEF6S2VFUnVHNGZqajJKc0NzREZOQ05BeDA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Carreta carregada com calcário tomba após GPS indicar estrada rural em Jandaia do Sul - Canal 38</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>08/07/2026 10:32</t>
+          <t>07/07/2026 12:48</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPbjhYdVBoUk5sOTNMN2p4VlEtVzQwM29sU1JlNktjV1B2RkU2UHA3UndrajVhTHhmS3VZdWRGRmprbHRTQjdRSW1GN0pLN05sMnAxcGR1MVAwZkRRTlZuNmt1RE1ndjdYU0JtQjk3OFRaUmhWN2RKck4tSGJlZXJfT3JiQlhzclpWMVpLX3pGcW03anY0NTE2Y25rdDAwZ014bDZneUNyY1NqeV9MSlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>Vídeo: Caminhão com calcário tomba e interdita rodovia BR-376 - Diário dos Campos</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>07/07/2026 18:35</t>
+          <t>07/07/2026 12:25</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMjBYMUlrTk44Q051SjdWdk5BQWhmV0tZUG1VaV9PSm82NGFLQ3B3RnMtbGVmR2xhYmxTYUpyUnQ4WVVmQXdiVFE0TnBUUUZ0M3I2R2NjS1k2R0NmckF2NG5OMzNVQmtLUU5VbHVLbkdoT1ZfYmdMSE44U0J1b0dtV3RxWm4zM19ZckZSWU54VWpYQnF1M0k40gGcAUFVX3lxTE1OSmhaeUw4dG0tZUl1N1B4RTRORmZpeEtfaHlTc1pMQ183YWpzYWh1Zng0MlBEUGIydDJKeVFHZjNZNzdDVS1xLTdMbU0yVWJ1RUFuOXR6aVpHNUtMZElhWDVuQXlVVEVBWHYwaVVVSVFKRE1sVHdJWHFGdHgzampVSFV3OXd2VHF3X0VDOEVONlJLdEk2QXhiYVdlcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação com ureia disparada: 149% - MT Econômico</t>
+          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>07/07/2026 18:33</t>
+          <t>07/07/2026 11:15</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOTlXdllBd0RsRTMwRmZuckFDamxwbDdTVlBYUk01bnVoZHAtOGJEa2lOdmtfMmtCRFBZWFFQOEQ4SnpKSGlJbl9fTFQzdnY3Vlc1M1FnYV9hcFNPVDJMQ0VLY2Y2ZFFFYnBqNDhjSVhRQzhDNi1nLWZiR3BRYnppRDhtMEhoMmxnel85VTJDMFJZS19paFB6WGJ5QmRSWjl6M2ZNYVVSanVZNEF6S2VFUnVHNGZqajJKc0NzREZOQ05BeDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Carreta carregada com calcário tomba após GPS indicar estrada rural em Jandaia do Sul - Canal 38</t>
+          <t>ANM notifica CODEMIG e Mosaic Fertilizantes sobre dívida de R$ 55 mi de CFEM - atlaspublico.com.br</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>07/07/2026 12:48</t>
+          <t>07/07/2026 09:59</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPbjhYdVBoUk5sOTNMN2p4VlEtVzQwM29sU1JlNktjV1B2RkU2UHA3UndrajVhTHhmS3VZdWRGRmprbHRTQjdRSW1GN0pLN05sMnAxcGR1MVAwZkRRTlZuNmt1RE1ndjdYU0JtQjk3OFRaUmhWN2RKck4tSGJlZXJfT3JiQlhzclpWMVpLX3pGcW03anY0NTE2Y25rdDAwZ014bDZneUNyY1NqeV9MSlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOM1dxN01qNjc0ZDR6UXlRX2FsWUt0ZWxhcHExOGVoWDhTazJOdzBTUkpuandqc2szc2dhdzhhTUJlV0p6NGl4Z3MyanMtS0Y3czIwcUFFOXI5Q0U3NlQ4NWRRRW5Bb0NiMlF0aGhqRW13ZE5TbU9xcS02cmVwX1p6Z0hIWDRIQVNQRy1hcWktdXZUZ1psdWlYaFQ1ZFJGS013dERKUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vídeo: Caminhão com calcário tomba e interdita rodovia BR-376 - Diário dos Campos</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - MINUTO MT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>07/07/2026 12:25</t>
+          <t>07/07/2026 09:08</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMjBYMUlrTk44Q051SjdWdk5BQWhmV0tZUG1VaV9PSm82NGFLQ3B3RnMtbGVmR2xhYmxTYUpyUnQ4WVVmQXdiVFE0TnBUUUZ0M3I2R2NjS1k2R0NmckF2NG5OMzNVQmtLUU5VbHVLbkdoT1ZfYmdMSE44U0J1b0dtV3RxWm4zM19ZckZSWU54VWpYQnF1M0k40gGcAUFVX3lxTE1OSmhaeUw4dG0tZUl1N1B4RTRORmZpeEtfaHlTc1pMQ183YWpzYWh1Zng0MlBEUGIydDJKeVFHZjNZNzdDVS1xLTdMbU0yVWJ1RUFuOXR6aVpHNUtMZElhWDVuQXlVVEVBWHYwaVVVSVFKRE1sVHdJWHFGdHgzampVSFV3OXd2VHF3X0VDOEVONlJLdEk2QXhiYVdlcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNm9yRHRTbXM3bWkzai03Qjh6eUh5bm5XSmcyZFA0Ymx1Zl82dThtOEFaUF9ieDRLbHNCT0VtbmJ2S2UyTDZLb2pFZllibWstOWM0VHZHR3V3eFRiVU5vdWgxMUoyaEQ4NDVwd2oteDBGdWNfMGVpUnRleFYzV3BRcnZ5R0xHbzNJV2pqRmxlWXgwZnB1UFBKd2F2NkwwV0p3QUw1YWZKSDFBTUQ4djJZNkVBMWp2NE9JdUEtMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>07/07/2026 11:15</t>
+          <t>07/07/2026 01:32</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOd0ZxY1VnNE5vV1ZDUW41MHU1MGpadk82Y0lUaU1LQk5xdkM0SmJESmpRWWpmM0VPcC1SdWJaNS1DcFVTYzk5UVF5dm5KdHhqSDNQWFZhUUt2RVExLWxJUUdaQUpId3JncThlMHZKWE12Z3VPRHFzN2J1OUJnWG5JUlBfaEZiUWVOZjZwMTR1ZXBWZzdMTkw2MWxQMXBic0xEeE1DTkJsbHdHLTZESlRweERMSXd5VDBnZU9tLWdDNnFObjU3NmVCUTlsbVFYNmtyWWJQWlJ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ANM notifica CODEMIG e Mosaic Fertilizantes sobre dívida de R$ 55 mi de CFEM - atlaspublico.com.br</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - BRASIL NOTÍCIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>07/07/2026 09:59</t>
+          <t>07/07/2026 00:31</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOM1dxN01qNjc0ZDR6UXlRX2FsWUt0ZWxhcHExOGVoWDhTazJOdzBTUkpuandqc2szc2dhdzhhTUJlV0p6NGl4Z3MyanMtS0Y3czIwcUFFOXI5Q0U3NlQ4NWRRRW5Bb0NiMlF0aGhqRW13ZE5TbU9xcS02cmVwX1p6Z0hIWDRIQVNQRy1hcWktdXZUZ1psdWlYaFQ1ZFJGS013dERKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDN6N25ybWpZZE9iX3JvejZSc29pWXVXczdzazFkNzlqMDZaTWVtcmJsQ1BLMTc0cmlQQWxsM3J4bURTMWJlOExWWDJxUkd5U1A4cUxTSGdWSzVQSG5VWkFIOHYxa2VOaXJBcVp6OHp6SmNWdldaaWhwajZ2Nk1mVnBCMm91OS10VEstR2Y4SFo4aDhvck1yNWV5Q08tMEFETmxrMEptMHVDQ1VWVFhySklFaUJ2NXNtM3dsTURCbEJxTjJRRlViNGd1c1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - MINUTO MT</t>
+          <t>Enxofre se torna essencial na agricultura devido a baixa eficiência - boca.com.br</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>07/07/2026 09:08</t>
+          <t>06/07/2026 14:15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNm9yRHRTbXM3bWkzai03Qjh6eUh5bm5XSmcyZFA0Ymx1Zl82dThtOEFaUF9ieDRLbHNCT0VtbmJ2S2UyTDZLb2pFZllibWstOWM0VHZHR3V3eFRiVU5vdWgxMUoyaEQ4NDVwd2oteDBGdWNfMGVpUnRleFYzV3BRcnZ5R0xHbzNJV2pqRmxlWXgwZnB1UFBKd2F2NkwwV0p3QUw1YWZKSDFBTUQ4djJZNkVBMWp2NE9JdUEtMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWVY4VzhicjNjWXdaS0VKLXZpcTE3Z3B6VURpQlIzNFlUUE01QVNxdjBuXzZsSmlLZXV5YzlIVXI1QmQ0Z3BETGFFZWFoUlBPeG5WMlZTX3E3RDlMc3lSU1BsTWJDazZmRTBHUHZhRzdESE5BUkxJczB5bkNFRHhKaGctakVrSndvSWE4QlhQTWNjalZoN01SR1Vra2tkY1hM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - RADAR DIGITAL BRASÍLIA</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>07/07/2026 01:32</t>
+          <t>06/07/2026 13:47</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOd0ZxY1VnNE5vV1ZDUW41MHU1MGpadk82Y0lUaU1LQk5xdkM0SmJESmpRWWpmM0VPcC1SdWJaNS1DcFVTYzk5UVF5dm5KdHhqSDNQWFZhUUt2RVExLWxJUUdaQUpId3JncThlMHZKWE12Z3VPRHFzN2J1OUJnWG5JUlBfaEZiUWVOZjZwMTR1ZXBWZzdMTkw2MWxQMXBic0xEeE1DTkJsbHdHLTZESlRweERMSXd5VDBnZU9tLWdDNnFObjU3NmVCUTlsbVFYNmtyWWJQWlJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - BRASIL NOTÍCIA</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>07/07/2026 00:31</t>
+          <t>06/07/2026 09:03</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDN6N25ybWpZZE9iX3JvejZSc29pWXVXczdzazFkNzlqMDZaTWVtcmJsQ1BLMTc0cmlQQWxsM3J4bURTMWJlOExWWDJxUkd5U1A4cUxTSGdWSzVQSG5VWkFIOHYxa2VOaXJBcVp6OHp6SmNWdldaaWhwajZ2Nk1mVnBCMm91OS10VEstR2Y4SFo4aDhvck1yNWV5Q08tMEFETmxrMEptMHVDQ1VWVFhySklFaUJ2NXNtM3dsTURCbEJxTjJRRlViNGd1c1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Enxofre se torna essencial na agricultura devido a baixa eficiência - boca.com.br</t>
+          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>06/07/2026 14:15</t>
+          <t>05/07/2026 19:45</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWVY4VzhicjNjWXdaS0VKLXZpcTE3Z3B6VURpQlIzNFlUUE01QVNxdjBuXzZsSmlLZXV5YzlIVXI1QmQ0Z3BETGFFZWFoUlBPeG5WMlZTX3E3RDlMc3lSU1BsTWJDazZmRTBHUHZhRzdESE5BUkxJczB5bkNFRHhKaGctakVrSndvSWE4QlhQTWNjalZoN01SR1Vra2tkY1hM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Alta da ureia preocupa produtores e eleva custos da próxima safra - capitalnews.com.br</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>06/07/2026 13:47</t>
+          <t>04/07/2026 21:22</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZHVhcUh1QnEzbldNX2ZwU0FnWTJiTVFLTkpRRkpoemJYbEVMVkJCNV9zR0tJc3otWkhRdEs4M0JxTE5tOWdfY01pWjFveG4yNThjbmdnOE8xTTJPRl8xY25oYlFYR2JGbGd1SzNyVEV0d1haUEhHR0oxdGJNc05ZYTNHcEt6QzBvVmNpbWg2SEFiT2Z1OEpFT3B1bDZ0UmNRUjRadktMU2kzODkzS2w5bFU5UkJVNGJTSndzZzQ0b0llaTZyTjZXaVd6MExkRjBkSkJ6SQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2800,61 +2800,61 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>06/07/2026 09:03</t>
+          <t>04/07/2026 07:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
+          <t>Rússia prorroga proibição das exportações de enxofre - GlobalFert</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>05/07/2026 19:45</t>
+          <t>03/07/2026 18:37</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPSDYtNVczb3hScWJXUzkxcVZLMzV1dTRic3hNZ0V5RDJrM3dQalVBaHN3azdoSG5rM2laeVMzUTlVV1poeDl6N2ZCd1pETUsyVktHOHlFcjJsNmFwMXVqSFgza2hMOHZhM3hYbEMweTZYUXhRVkRDVG1jRGV4UngyY2luRXVnRGM1eDlncHhPenNsYUJUX1Q0dmVNNlI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Alta da ureia preocupa produtores e eleva custos da próxima safra - capitalnews.com.br</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>04/07/2026 21:22</t>
+          <t>03/07/2026 13:20</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZHVhcUh1QnEzbldNX2ZwU0FnWTJiTVFLTkpRRkpoemJYbEVMVkJCNV9zR0tJc3otWkhRdEs4M0JxTE5tOWdfY01pWjFveG4yNThjbmdnOE8xTTJPRl8xY25oYlFYR2JGbGd1SzNyVEV0d1haUEhHR0oxdGJNc05ZYTNHcEt6QzBvVmNpbWg2SEFiT2Z1OEpFT3B1bDZ0UmNRUjRadktMU2kzODkzS2w5bFU5UkJVNGJTSndzZzQ0b0llaTZyTjZXaVd6MExkRjBkSkJ6SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2866,17 +2866,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>04/07/2026 07:00</t>
+          <t>03/07/2026 07:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2888,83 +2888,83 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rússia prorroga proibição das exportações de enxofre - GlobalFert</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>03/07/2026 18:37</t>
+          <t>03/07/2026 07:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPSDYtNVczb3hScWJXUzkxcVZLMzV1dTRic3hNZ0V5RDJrM3dQalVBaHN3azdoSG5rM2laeVMzUTlVV1poeDl6N2ZCd1pETUsyVktHOHlFcjJsNmFwMXVqSFgza2hMOHZhM3hYbEMweTZYUXhRVkRDVG1jRGV4UngyY2luRXVnRGM1eDlncHhPenNsYUJUX1Q0dmVNNlI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>03/07/2026 13:20</t>
+          <t>03/07/2026 07:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
+          <t>O Amado Batista. As 84 Toneladas de Calcário. A Dívida de R4 9 Mil Reais e a Cobrança na Justiça - O Antagônico</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>03/07/2026 07:00</t>
+          <t>03/07/2026 01:28</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxON0w1Z1ZmVjZtdTR4dUlMYkFtdXVNXzByY3EtTlRabUxBUE1WYkZtRGpJbEVpNUNiS0s1NE50cnJ1SVJMUzNaX04wZUJhclV6Z3JYQWs1cm4xN0ljRUlyRHVTUGRyMG1teDVPRHBJZWM4X1hseEY0T0ZkNWxnUFF1aWZ4UURBYzN3VEJtZmM5NDhSYl9sei1qeGhQak1tS2dPcEtETkNjN2JlbUZsR0R6NlJ5YzNFeHVKU2ZrN0dwRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>03/07/2026 07:00</t>
+          <t>02/07/2026 20:01</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
         </is>
       </c>
     </row>
@@ -2976,127 +2976,127 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Nova técnica de pirólise por plasma transforma borra de café em biocarvão de alto desempenho em apenas 90 segundos, sem secagem prévia, triplica o carbono fixo, remove totalmente o enxofre e ainda cria um material altamente poroso para aplicações e - Folha BV</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>03/07/2026 07:00</t>
+          <t>02/07/2026 10:59</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOb0hhdlk1Y09OQVdsSVFqYW5oMDUtMkFqOVlnbTlSSDlSWUNIME12ekVCYTQwNjBQRmh6YUdtdGFRUkNMQnYxdkxGVlNuUlpiamd6aGl1bHdPbnlBcV82NWx0RGVKaXM2dU9pQTNTUlQzS3lKa3pQalRkUThjV2Q1d3kyV3JINHNvRldNbDFSVlhycVYwaWJaVDZGdTNOZXJPcWJ0dDVlb0hGcUxkbWwydWUyZlpDY3ltT0F2Z1ZXUnZFUVgzcldjc01DN09GbFAyR2dlSmZTU25aU1lkQWh6ZG5LMXNYODRWc1g5YkhUWDBLbmEyLVdHWFBzSE5EVmxmSncwOFI4a2dJUllZTVJ4bnZzZlBXeXYyUFpJSkgwXzBveVJzSmwzTGxpMW5TN191VGs3X1ZFTlYwdVBKRGpGY0lvd3J5N1Zsc0NwRnE4bjRBbkN2SmlKQmRrUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>O Amado Batista. As 84 Toneladas de Calcário. A Dívida de R4 9 Mil Reais e a Cobrança na Justiça - O Antagônico</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>03/07/2026 01:28</t>
+          <t>02/07/2026 07:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxON0w1Z1ZmVjZtdTR4dUlMYkFtdXVNXzByY3EtTlRabUxBUE1WYkZtRGpJbEVpNUNiS0s1NE50cnJ1SVJMUzNaX04wZUJhclV6Z3JYQWs1cm4xN0ljRUlyRHVTUGRyMG1teDVPRHBJZWM4X1hseEY0T0ZkNWxnUFF1aWZ4UURBYzN3VEJtZmM5NDhSYl9sei1qeGhQak1tS2dPcEtETkNjN2JlbUZsR0R6NlJ5YzNFeHVKU2ZrN0dwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>02/07/2026 20:01</t>
+          <t>01/07/2026 13:48</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nova técnica de pirólise por plasma transforma borra de café em biocarvão de alto desempenho em apenas 90 segundos, sem secagem prévia, triplica o carbono fixo, remove totalmente o enxofre e ainda cria um material altamente poroso para aplicações e - Folha BV</t>
+          <t>Destaques da Edição 363 - JornalCana</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>02/07/2026 10:59</t>
+          <t>01/07/2026 10:37</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOb0hhdlk1Y09OQVdsSVFqYW5oMDUtMkFqOVlnbTlSSDlSWUNIME12ekVCYTQwNjBQRmh6YUdtdGFRUkNMQnYxdkxGVlNuUlpiamd6aGl1bHdPbnlBcV82NWx0RGVKaXM2dU9pQTNTUlQzS3lKa3pQalRkUThjV2Q1d3kyV3JINHNvRldNbDFSVlhycVYwaWJaVDZGdTNOZXJPcWJ0dDVlb0hGcUxkbWwydWUyZlpDY3ltT0F2Z1ZXUnZFUVgzcldjc01DN09GbFAyR2dlSmZTU25aU1lkQWh6ZG5LMXNYODRWc1g5YkhUWDBLbmEyLVdHWFBzSE5EVmxmSncwOFI4a2dJUllZTVJ4bnZzZlBXeXYyUFpJSkgwXzBveVJzSmwzTGxpMW5TN191VGs3X1ZFTlYwdVBKRGpGY0lvd3J5N1Zsc0NwRnE4bjRBbkN2SmlKQmRrUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOZS15WnBLcU9obFdvQ3RBQmU1OURPZlhCenRTS08xNmdmTm5CUUVpd0ZVZHJJeDBTWXlGdVFuLXVXRjhxV0VGNG5IcjlEdUluR3JjdmNlczdWT3NaeENEOHk3dGw2X0FnOHpOcGhxWlNERkhQMDVWSm5hMFlpeVNLMEI2ZGVmT3FBSmozM3JqUVNRa19McFdKZ3JmWGtNeHFHZWdJTw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Mosaico romano de 84 m² e 1.700 anos é desenterrado por acaso por um agricultor que plantava mudas de cerejeira na Turquia, a menos de 50 cm do chão - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>02/07/2026 07:00</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxNcDNIeVBkYVFQVDZOTUVuS1R3WXlvcXFsbUZ0cm5XQUliVXEtZ0p0TGFzZEk5OV9kV3N1LXFhQXJfdEU3V2g3Ukl5d1ZxTGRVZm92WUFFVzhCZmx2WUpSY0RWYUY4NVJKdW5sSUlDS1Q3b1NaNWoybDVhYzJtb0ttT1hjNWdDUGlQYjViRm1IV1JZZEZzSzI0Q1dlcExyd1VoXzJCaXpnRVpXMUN3WTV4cDJJV1dJMHJqa0dOazFTUWRFOWIwU0VMTEVoLThGQlI4eE5GWU1OM0ZDTDFHSEtKU3l4MzBCSi1oVF9rSk44cGtGQlhTWnJoZThuREJsdDhROGlabDE5dVUzTERUVURsSG91UmJhdTVtODRWVjdB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>01/07/2026 13:48</t>
+          <t>30/06/2026 21:22</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3108,51 +3108,51 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mosaico romano de 84 m² e 1.700 anos é desenterrado por acaso por um agricultor que plantava mudas de cerejeira na Turquia, a menos de 50 cm do chão - CPG Click Petróleo e Gás</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>30/06/2026 07:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxNcDNIeVBkYVFQVDZOTUVuS1R3WXlvcXFsbUZ0cm5XQUliVXEtZ0p0TGFzZEk5OV9kV3N1LXFhQXJfdEU3V2g3Ukl5d1ZxTGRVZm92WUFFVzhCZmx2WUpSY0RWYUY4NVJKdW5sSUlDS1Q3b1NaNWoybDVhYzJtb0ttT1hjNWdDUGlQYjViRm1IV1JZZEZzSzI0Q1dlcExyd1VoXzJCaXpnRVpXMUN3WTV4cDJJV1dJMHJqa0dOazFTUWRFOWIwU0VMTEVoLThGQlI4eE5GWU1OM0ZDTDFHSEtKU3l4MzBCSi1oVF9rSk44cGtGQlhTWnJoZThuREJsdDhROGlabDE5dVUzTERUVURsSG91UmJhdTVtODRWVjdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>30/06/2026 21:22</t>
+          <t>30/06/2026 07:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3162,51 +3162,51 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>30/06/2026 07:00</t>
+          <t>29/06/2026 11:22</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>30/06/2026 07:00</t>
+          <t>29/06/2026 11:22</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3218,39 +3218,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>29/06/2026 11:22</t>
+          <t>29/06/2026 07:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>29/06/2026 11:22</t>
+          <t>29/06/2026 07:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Segundo o WSJ, a Martin Marietta e a Lhoist North America vão se fundir em um negócio de US$ 13,5 bilhões - TradingView</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85QWpvMXdqUXlsdVlyQ1pRXzUxUWZIY24yVlhHOXpONU5hQjdGM3ZNU1QwMGxBWWxiRGN2UVA2aGFBNHJ3bVQyYVR0T1JzNjI3SWltcmQ1c3BpY25CMC1Pa3BhaXRCTk9QMzFuSzUyNWFZRnNJVFFyYQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3306,61 +3306,61 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>29/06/2026 07:00</t>
+          <t>26/06/2026 16:47</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Segundo o WSJ, a Martin Marietta e a Lhoist North America vão se fundir em um negócio de US$ 13,5 bilhões - TradingView</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>29/06/2026 07:00</t>
+          <t>26/06/2026 07:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85QWpvMXdqUXlsdVlyQ1pRXzUxUWZIY24yVlhHOXpONU5hQjdGM3ZNU1QwMGxBWWxiRGN2UVA2aGFBNHJ3bVQyYVR0T1JzNjI3SWltcmQ1c3BpY25CMC1Pa3BhaXRCTk9QMzFuSzUyNWFZRnNJVFFyYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>26/06/2026 16:47</t>
+          <t>26/06/2026 07:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3382,129 +3382,129 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Brazilian Farmers Delay Input Purchases as They Await Debt Relief Bill, Mosaic Says - The AgriBiz</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>26/06/2026 07:00</t>
+          <t>25/06/2026 07:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQN2xNaUxQMDVWZl9tOVF1UFA3SG9QaHdTVndkU2Z3ci1Dazl6cElWRmV1NjVDMzVyY1Z1ckh1S2kydnFleVQ0YXpnOExKdlpBVkFPMk1xUWJodkpjODgyMzB3Q1lSdmN1Rm04SG1yb3hLbnhjb21fdUFoeFFoN0d6d3YzSHVfMmZWcF9WMHBKV2RRTUR6Z1VuRTRKM21CdTctOGh6VDdQSHhaQ0xhZV9xd1c0dU9wVkZIQ2U3c21weWtCdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>26/06/2026 07:00</t>
+          <t>25/06/2026 07:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>25/06/2026 07:00</t>
+          <t>24/06/2026 18:03</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Brazilian Farmers Delay Input Purchases as They Await Debt Relief Bill, Mosaic Says - The AgriBiz</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>25/06/2026 07:00</t>
+          <t>24/06/2026 07:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQN2xNaUxQMDVWZl9tOVF1UFA3SG9QaHdTVndkU2Z3ci1Dazl6cElWRmV1NjVDMzVyY1Z1ckh1S2kydnFleVQ0YXpnOExKdlpBVkFPMk1xUWJodkpjODgyMzB3Q1lSdmN1Rm04SG1yb3hLbnhjb21fdUFoeFFoN0d6d3YzSHVfMmZWcF9WMHBKV2RRTUR6Z1VuRTRKM21CdTctOGh6VDdQSHhaQ0xhZV9xd1c0dU9wVkZIQ2U3c21weWtCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>24/06/2026 18:03</t>
+          <t>24/06/2026 07:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Arqueólogos encontram mosaico de deus do rio na Turquia - Aventuras na História</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3514,19 +3514,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdFM4Yk1jUU5RMURVMTViQklhT2I4SW1jWUxTRVI0azJDM2lmMGtrWThNNGNKTE5HcWFabEV5MUVNU2lSc2NIYkhmbm5xcWZieXAxRmRpN1BPWXlscGtIZmZyZHREWkhQc21scEQ0d3ZobjB6eER4TVNMMHpfVUNMUGRVY3lFNnRRRGVhLUxVd0l0OXBRT3RKWjdtMENVcm5RRURBZ2EyVlNXTkc2UlpjdWozMVRXMWdyVW5j?oc=5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3536,19 +3536,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,95 +3558,95 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>Secretaria de Agricultura mantém transporte de calcário para fortalecer a produção rural em Sentinela do Sul - Portal ClicR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>24/06/2026 07:00</t>
+          <t>23/06/2026 18:47</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPSklWeDZHUDl4T0FyeFZqY3RPdkptcGdkaG04MjB6SVA5QkYxcWxHQm9qS0ZzSTBGbGtsTXVHbFRRUFVrd194V1JDQVdpdVNJXzVCRXFuQ1JXU2ZydUltajNoRE52QUZWNVYxZmJBaXdLM29QeVdnUTFiejRieEhwOGNfSmtNdUFnSVMwYlZxeGJlX3pJY2VnNW5jbkNmMGcyYjVuN0RBbGl1dWhDY0Y5dzhkMF9wWW1pZHN2SVVTZFZZaENCVmdtWmtB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Arqueólogos encontram mosaico de deus do rio na Turquia - Aventuras na História</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>24/06/2026 07:00</t>
+          <t>23/06/2026 10:31</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdFM4Yk1jUU5RMURVMTViQklhT2I4SW1jWUxTRVI0azJDM2lmMGtrWThNNGNKTE5HcWFabEV5MUVNU2lSc2NIYkhmbm5xcWZieXAxRmRpN1BPWXlscGtIZmZyZHREWkhQc21scEQ0d3ZobjB6eER4TVNMMHpfVUNMUGRVY3lFNnRRRGVhLUxVd0l0OXBRT3RKWjdtMENVcm5RRURBZ2EyVlNXTkc2UlpjdWozMVRXMWdyVW5j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura mantém transporte de calcário para fortalecer a produção rural em Sentinela do Sul - Portal ClicR</t>
+          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>23/06/2026 18:47</t>
+          <t>23/06/2026 07:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPSklWeDZHUDl4T0FyeFZqY3RPdkptcGdkaG04MjB6SVA5QkYxcWxHQm9qS0ZzSTBGbGtsTXVHbFRRUFVrd194V1JDQVdpdVNJXzVCRXFuQ1JXU2ZydUltajNoRE52QUZWNVYxZmJBaXdLM29QeVdnUTFiejRieEhwOGNfSmtNdUFnSVMwYlZxeGJlX3pJY2VnNW5jbkNmMGcyYjVuN0RBbGl1dWhDY0Y5dzhkMF9wWW1pZHN2SVVTZFZZaENCVmdtWmtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>23/06/2026 10:31</t>
+          <t>23/06/2026 07:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3675,44 +3675,44 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
+          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>23/06/2026 07:00</t>
+          <t>22/06/2026 22:10</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>23/06/2026 07:00</t>
+          <t>22/06/2026 12:06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3724,73 +3724,73 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>22/06/2026 22:10</t>
+          <t>22/06/2026 11:41</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>22/06/2026 12:06</t>
+          <t>22/06/2026 07:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>22/06/2026 11:41</t>
+          <t>22/06/2026 07:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -3812,51 +3812,51 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>22/06/2026 07:00</t>
+          <t>21/06/2026 07:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Mosaico de antigo 'deus do rio' é encontrado na Turquia - Globo</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>22/06/2026 07:00</t>
+          <t>21/06/2026 07:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOLTdXYW1GZW4ybGRZM2Q1OU5WWFNYNEVENXNhVDZBTG9LanM0YnM2NGlZQnAxbThZeWs0a0lOdVgyVkRfN3JQaEI4RHY1Y3BLa1lobmFuN1VvTGg5SUFiT2VvMkNxMHJDdjdyRTJGWm1HZWxpRlZNajdmQmg0WERVTGlyeW80U2g0WDctOGY0X0Vsblg5RVVLdmtFanU2bkVaaWNEQjhCdE1MWlg1cmpOZ05RQXZMcXPSAcYBQVVfeXFMUGFBczRwMXpFN0tOdm1GWWlid0hBYjV4bEFQbWRMeUEzS0hFTzZiNTdvVUI2QW5SaGg1OUY2cXV2Q1ltellaSEk1V3BHUHBzeTMwSmZJZTUxZ2FEN1UxNTVQWjY1eVBaOHFkblBqTWc3VDJWdXpzRGo0QUI1TVdYYk9MdE1uSGwxSHFnQktpX2VZYzlwT1FWT2Jub1U5dWdHWHlWRlhDZHU0ck51SmZKVjBqREhaa0JVcnFsN2tMN0dlLU0welJ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mosaico de antigo 'deus do rio' é encontrado na Turquia - Globo</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,51 +3866,51 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOLTdXYW1GZW4ybGRZM2Q1OU5WWFNYNEVENXNhVDZBTG9LanM0YnM2NGlZQnAxbThZeWs0a0lOdVgyVkRfN3JQaEI4RHY1Y3BLa1lobmFuN1VvTGg5SUFiT2VvMkNxMHJDdjdyRTJGWm1HZWxpRlZNajdmQmg0WERVTGlyeW80U2g0WDctOGY0X0Vsblg5RVVLdmtFanU2bkVaaWNEQjhCdE1MWlg1cmpOZ05RQXZMcXPSAcYBQVVfeXFMUGFBczRwMXpFN0tOdm1GWWlid0hBYjV4bEFQbWRMeUEzS0hFTzZiNTdvVUI2QW5SaGg1OUY2cXV2Q1ltellaSEk1V3BHUHBzeTMwSmZJZTUxZ2FEN1UxNTVQWjY1eVBaOHFkblBqTWc3VDJWdXpzRGo0QUI1TVdYYk9MdE1uSGwxSHFnQktpX2VZYzlwT1FWT2Jub1U5dWdHWHlWRlhDZHU0ck51SmZKVjBqREhaa0JVcnFsN2tMN0dlLU0welJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Itamaraty faz varredura emergencial atrás de fertilizantes para o Brasil - Jornal do Comércio</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>21/06/2026 07:00</t>
+          <t>20/06/2026 20:42</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxONEFWVzJtWFhfVnFJdkpadjFtWXJaRTdYT0lUc0djdktrOEw2M0ltdnlGOFFOcWZCQ08zcXdNQU1uMkJpSV9DTnh5ajJWZDJ2NmxFaFdNMGk0VmdMbjdsWUdiNTYtSVhqNUpvWUNBbmRKNlRoTTFEOUpoQlNGX2lDUkFhQXhPVE40WldxUzhBVkhVWGdJZ2pnNk1HYVZLUXZfX1lDUnNTZndiU19rdzlTN0lOX1F2Q3EzU0JPY0h5bzBfajkycDFKOG10Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>21/06/2026 07:00</t>
+          <t>20/06/2026 07:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3922,29 +3922,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Itamaraty faz varredura emergencial atrás de fertilizantes para o Brasil - Jornal do Comércio</t>
+          <t>Um pedido de socorro para os fertilizantes | Radar Econômico - VEJA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>20/06/2026 20:42</t>
+          <t>20/06/2026 07:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxONEFWVzJtWFhfVnFJdkpadjFtWXJaRTdYT0lUc0djdktrOEw2M0ltdnlGOFFOcWZCQ08zcXdNQU1uMkJpSV9DTnh5ajJWZDJ2NmxFaFdNMGk0VmdMbjdsWUdiNTYtSVhqNUpvWUNBbmRKNlRoTTFEOUpoQlNGX2lDUkFhQXhPVE40WldxUzhBVkhVWGdJZ2pnNk1HYVZLUXZfX1lDUnNTZndiU19rdzlTN0lOX1F2Q3EzU0JPY0h5bzBfajkycDFKOG10Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNXzNyRkc3R1RCQVRpMzZlZGRtN1J6bkJtZl9YRzBFN2JkdElMc01CN2lyaWVOanRNekgybzJrNnhwMHdZV3pDTUZEY2lkMno5dHNPZ3pCSlM2QTROUlJuSFo3cWpxQzR3cGhLUzJYRmY2SXFobEdOTGpfdEhVTS1Jc0IxMGJ0TllQMFNrVnNFa0QwZlRfTGw4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Um pedido de socorro para os fertilizantes | Radar Econômico - VEJA</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,161 +3954,161 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNXzNyRkc3R1RCQVRpMzZlZGRtN1J6bkJtZl9YRzBFN2JkdElMc01CN2lyaWVOanRNekgybzJrNnhwMHdZV3pDTUZEY2lkMno5dHNPZ3pCSlM2QTROUlJuSFo3cWpxQzR3cGhLUzJYRmY2SXFobEdOTGpfdEhVTS1Jc0IxMGJ0TllQMFNrVnNFa0QwZlRfTGw4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
+          <t>ProSolos: Capão Bonito do Sul distribui calcário para 25 produtores rurais - Tua Rádio</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>20/06/2026 07:00</t>
+          <t>19/06/2026 07:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPczJPU19lVkVaMG8wVGZGVEpQbjQyb3pYbmY2VGhUNW1GVW9lazlCaEtONGlDR3ZpSHFxVWMwaGoyNXhzcTRBLXREWkVKZUQtNF9TRXFWY1pnYXIwS3RfNVBkaTJIbFh5blVtaEZuRWhDRzU3dW5ETDZ5RXBEZU5KZzR5NW9OMTluT0dHaGU5OC0taUI5Y2FzXzZLdlZkb2tjdnMwS2ZXTXZDMnBJT05xTEFXNFl0VXBpRTlFWVA5ZFFja2xCdGpPSExFNDJsdGVjbUVaYnNhYmFsSGZkbVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20/06/2026 07:00</t>
+          <t>19/06/2026 07:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ProSolos: Capão Bonito do Sul distribui calcário para 25 produtores rurais - Tua Rádio</t>
+          <t>Compra de ativos existentes pode antecipar em dois anos o início da operação da St George em Araxá - Diário do Comércio</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>19/06/2026 07:00</t>
+          <t>18/06/2026 07:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPczJPU19lVkVaMG8wVGZGVEpQbjQyb3pYbmY2VGhUNW1GVW9lazlCaEtONGlDR3ZpSHFxVWMwaGoyNXhzcTRBLXREWkVKZUQtNF9TRXFWY1pnYXIwS3RfNVBkaTJIbFh5blVtaEZuRWhDRzU3dW5ETDZ5RXBEZU5KZzR5NW9OMTluT0dHaGU5OC0taUI5Y2FzXzZLdlZkb2tjdnMwS2ZXTXZDMnBJT05xTEFXNFl0VXBpRTlFWVA5ZFFja2xCdGpPSExFNDJsdGVjbUVaYnNhYmFsSGZkbVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE90MzZRdUdobThNWk13akRvUnVnWno1c1Q5cEU3a3EyUnExQzA2LW5MRlRPNXZIYml3dXJFYVBPRzYyeUhuMjVZTGJDWDNIYkZjRVF2XzdQank4TmMtUmdmYmhreWZfTTZQbUZaWFowNF9vNHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>19/06/2026 07:00</t>
+          <t>18/06/2026 07:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Compra de ativos existentes pode antecipar em dois anos o início da operação da St George em Araxá - Diário do Comércio</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>18/06/2026 07:00</t>
+          <t>17/06/2026 07:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE90MzZRdUdobThNWk13akRvUnVnWno1c1Q5cEU3a3EyUnExQzA2LW5MRlRPNXZIYml3dXJFYVBPRzYyeUhuMjVZTGJDWDNIYkZjRVF2XzdQank4TmMtUmdmYmhreWZfTTZQbUZaWFowNF9vNHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
+          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>18/06/2026 07:00</t>
+          <t>17/06/2026 07:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>17/06/2026 07:00</t>
+          <t>16/06/2026 17:20</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4120,39 +4120,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>17/06/2026 07:00</t>
+          <t>16/06/2026 07:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>16/06/2026 17:20</t>
+          <t>16/06/2026 07:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4164,39 +4164,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>16/06/2026 07:00</t>
+          <t>15/06/2026 07:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>16/06/2026 07:00</t>
+          <t>15/06/2026 07:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Rio Maior organizou Gala Empresarial do concelho - O Mirante</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYmIwcks0U205THc0UF80M2tqOTBpZWY1VWhZMFZzUUE2UEt2bmFLcTBsQ1g4YjRBRjBmRUZiN25XQVdCNDdldTdiZC10VTdBSzY3YjJiTFo5TXdaNjVVNkZUMTZSQ1g4MU1XX2s0azMwd0hNTFlDTktFVktWSWtrWUpPTjFQZEhoUzU3M3NzaXpQMVVaajZoYWhPRHNtLUhf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,51 +4262,51 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Cruzeiro conquista o título em Imigrante - Grupo A Hora</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>15/06/2026 07:00</t>
+          <t>14/06/2026 07:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdk1rcDcyUzh6UTl2c1R0LU9JMDA0T2ozQ3h6VExIbFhUVWUzWnlWY3pnWXJmNkp1SEp2ZUtCUDNqU0FlN3NpODZtbkNramhWR2ZQaE53M1FfZFk1SnpxMTlIQjEwaUxtVTJhSGhXVWFHRkFUOHBGaS1MMDZnd2pUM2NFcnNRYWNva3JOd1VZRWxadw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cruzeiro conquista o título em Imigrante - Grupo A Hora</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>14/06/2026 07:00</t>
+          <t>12/06/2026 07:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdk1rcDcyUzh6UTl2c1R0LU9JMDA0T2ozQ3h6VExIbFhUVWUzWnlWY3pnWXJmNkp1SEp2ZUtCUDNqU0FlN3NpODZtbkNramhWR2ZQaE53M1FfZFk1SnpxMTlIQjEwaUxtVTJhSGhXVWFHRkFUOHBGaS1MMDZnd2pUM2NFcnNRYWNva3JOd1VZRWxadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4318,61 +4318,61 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>12/06/2026 07:00</t>
+          <t>11/06/2026 07:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11/06/2026 07:00</t>
+          <t>10/06/2026 07:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>10/06/2026 07:00</t>
+          <t>09/06/2026 07:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4445,44 +4445,44 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>09/06/2026 07:00</t>
+          <t>08/06/2026 17:33</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>08/06/2026 17:33</t>
+          <t>08/06/2026 07:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4577,44 +4577,44 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>08/06/2026 07:00</t>
+          <t>08/06/2026 02:34</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>08/06/2026 02:34</t>
+          <t>04/06/2026 07:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -4626,73 +4626,73 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>04/06/2026 07:00</t>
+          <t>03/06/2026 07:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>03/06/2026 07:00</t>
+          <t>02/06/2026 15:15</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>02/06/2026 15:15</t>
+          <t>02/06/2026 07:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,41 +4702,41 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>02/06/2026 07:00</t>
+          <t>01/06/2026 07:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,19 +4746,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Mosaic suspende mineração em Tapira por 30 dias e acende alerta em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,29 +4834,29 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMU1lSmhaSEJPbE5tbmdCU3ozeXVFcUdfX2dGZ2k3c3hGUzNaX2NCTUlfMlZiZjBLa2xXSHpFUURHbFBwLWRVZFdKOXJFVjBhb2t5SnZjVGJYcS1zRGlPNVN3dFRuVHF3WEtXeFkxelM2dUV4S0tLME41WVBFV1lZZWJSbFNZVzQwSEZNUk9teEtQM1M5eV90cnBpeWpCSW5kVDFNZl96aFd4TEd6aEV0OUMyMTLSAbwBQVVfeXFMTjl1UzR0Q2dTWHFEN0FqdktmQ0Nlc2p3YXBYLVpNTnlGVUFXOGNwUXNuMTZRdWZoQ2ttSHFzNEZsY2ltWjdqT05uUVpPSjdaUkR2YTFXYXV6RVZERU5rRk52ZGU1d2Vac2ptRDFTVXFVWGgzZTFCNzMyZ0VpZ1o4RWpLa044YUVEX2lMWEJYVDAta1RWRnhrV1BKYmZpSVpKSm56N2wzU3dCQldWV3R0VEJLNTJGbHdxY0VRdVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mosaic suspende mineração em Tapira por 30 dias e acende alerta em Uberaba - JM Online</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>01/06/2026 07:00</t>
+          <t>31/05/2026 07:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMU1lSmhaSEJPbE5tbmdCU3ozeXVFcUdfX2dGZ2k3c3hGUzNaX2NCTUlfMlZiZjBLa2xXSHpFUURHbFBwLWRVZFdKOXJFVjBhb2t5SnZjVGJYcS1zRGlPNVN3dFRuVHF3WEtXeFkxelM2dUV4S0tLME41WVBFV1lZZWJSbFNZVzQwSEZNUk9teEtQM1M5eV90cnBpeWpCSW5kVDFNZl96aFd4TEd6aEV0OUMyMTLSAbwBQVVfeXFMTjl1UzR0Q2dTWHFEN0FqdktmQ0Nlc2p3YXBYLVpNTnlGVUFXOGNwUXNuMTZRdWZoQ2ttSHFzNEZsY2ltWjdqT05uUVpPSjdaUkR2YTFXYXV6RVZERU5rRk52ZGU1d2Vac2ptRDFTVXFVWGgzZTFCNzMyZ0VpZ1o4RWpLa044YUVEX2lMWEJYVDAta1RWRnhrV1BKYmZpSVpKSm56N2wzU3dCQldWV3R0VEJLNTJGbHdxY0VRdVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4922,51 +4922,51 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>31/05/2026 07:00</t>
+          <t>30/05/2026 07:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Anvisa recolhe coco ralado por excesso de dióxido de enxofre; saiba quais são os riscos à saúde - Notícias ao Minuto Brasil</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>30/05/2026 07:00</t>
+          <t>29/05/2026 07:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVlFOZlF1ZGhHU1NNYjlNdm1kVzNDT0IwX0pRZUVzaFkwUTVhRnFvdU1xcnhnNl9PYllWVmdnVDVkXzlFcVJhYVoydXo5TURlVHlnR3Y1bjNrRGtGMTg0SkFoODdPblU4Qy1fbW9IcGFVN1BZVWloSVlWemNpM19KVlE3OVRiV1MwZmt4UXdlUmR4ZzdqU09RNmgwdWpjVDBtcVRkNWZseF92SnZySUN4VXlCMzdxa0JIU1FDd2FkZlNBbmhUNHBLdDNEVFlfQ3gwblpPbk9qcHNheHkyb1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Com excesso de enxofre, Anvisa ordena recolhimento de coco ralado da marca ‘Casa de Mãe’ - Grafitti News</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMlJWRTAxYnh2aVNNS3N6QkQwZkMxU2lCN19hMW5FNVNPYTBZRWpPU1VVQVk3blQyMnUyNkV4X0FjcDhnNE5vMkR3dzhwSHR6ek44M2E4V3hWU0FmM3NDLUVYV0s1N1dJTlYyazF4U196cGp2Ym1EWTc4amtOSDZDODhkbC1tM201cWZFY0luUXc2UkpSM0M2RDRPYlFBZy1TSVVUVHY3YUxXX3lhN09ManZmRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Anvisa recolhe coco ralado por excesso de dióxido de enxofre; saiba quais são os riscos à saúde - Notícias ao Minuto Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVlFOZlF1ZGhHU1NNYjlNdm1kVzNDT0IwX0pRZUVzaFkwUTVhRnFvdU1xcnhnNl9PYllWVmdnVDVkXzlFcVJhYVoydXo5TURlVHlnR3Y1bjNrRGtGMTg0SkFoODdPblU4Qy1fbW9IcGFVN1BZVWloSVlWemNpM19KVlE3OVRiV1MwZmt4UXdlUmR4ZzdqU09RNmgwdWpjVDBtcVRkNWZseF92SnZySUN4VXlCMzdxa0JIU1FDd2FkZlNBbmhUNHBLdDNEVFlfQ3gwblpPbk9qcHNheHkyb1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQYzh2cjdEME1NdHBVU0EwUEp4emJrSVMwWERxTW5FeFduT2prV3lyZ3lGbkFkOUtzcG01WV9sQUtObUl0N3FhbzhOVXI5eG1wWEwyN0ZrcDdSczdCa2plUFZTSWtGS21TODBYNGpWSDZpbTR0d0hwYWhJU29vbUlnaG5zcThDV2liYURCdHE3VDV4WWNVMlM5Um8yTUItMWI3ZFdEa0ZTZEFfa08yZHFOVksxdXo3SktXeGVrd2liNlU0b24yS0JWT2M5eHZnYU3SAdQBQVVfeXFMTmthZ3daS3ZoN1NrVzN0RXFfdXZJcHRkQTBwaVFmdmpfZGJlQVFaY0MwSmNYSDMydWZVeUN5NnVlWXZhQkNWX3BUSUpyQzQ3aUZKTk1yemJyNmhCTkNfSmM0V3NXc2t0eDEzcEQ2eHZxZkM3V3RZRlNjYkVaUmVmT2JvQ1lweDAySEZYem80MlE4TVItVGZaTi1yQ1paTktMQzhaTWNoWktGMGtiMXFjYnJLZFBocnBNbV9oYXJIWWNyaUwxSWlVNlpYR2VjS0pXZ0F3ZDk?oc=5</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
+          <t>Com excesso de enxofre, Anvisa ordena recolhimento de coco ralado da marca ‘Casa de Mãe’ - Grafitti News</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,29 +5032,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQYzh2cjdEME1NdHBVU0EwUEp4emJrSVMwWERxTW5FeFduT2prV3lyZ3lGbkFkOUtzcG01WV9sQUtObUl0N3FhbzhOVXI5eG1wWEwyN0ZrcDdSczdCa2plUFZTSWtGS21TODBYNGpWSDZpbTR0d0hwYWhJU29vbUlnaG5zcThDV2liYURCdHE3VDV4WWNVMlM5Um8yTUItMWI3ZFdEa0ZTZEFfa08yZHFOVksxdXo3SktXeGVrd2liNlU0b24yS0JWT2M5eHZnYU3SAdQBQVVfeXFMTmthZ3daS3ZoN1NrVzN0RXFfdXZJcHRkQTBwaVFmdmpfZGJlQVFaY0MwSmNYSDMydWZVeUN5NnVlWXZhQkNWX3BUSUpyQzQ3aUZKTk1yemJyNmhCTkNfSmM0V3NXc2t0eDEzcEQ2eHZxZkM3V3RZRlNjYkVaUmVmT2JvQ1lweDAySEZYem80MlE4TVItVGZaTi1yQ1paTktMQzhaTWNoWktGMGtiMXFjYnJLZFBocnBNbV9oYXJIWWNyaUwxSWlVNlpYR2VjS0pXZ0F3ZDk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMlJWRTAxYnh2aVNNS3N6QkQwZkMxU2lCN19hMW5FNVNPYTBZRWpPU1VVQVk3blQyMnUyNkV4X0FjcDhnNE5vMkR3dzhwSHR6ek44M2E4V3hWU0FmM3NDLUVYV0s1N1dJTlYyazF4U196cGp2Ym1EWTc4amtOSDZDODhkbC1tM201cWZFY0luUXc2UkpSM0M2RDRPYlFBZy1TSVVUVHY3YUxXX3lhN09ManZmRmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>29/05/2026 07:00</t>
+          <t>28/05/2026 07:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Portal iG</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5076,19 +5076,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPV0FOQXhCTERTM29lQTEyZWZXUW1hSE8xNE9tQTdQRWtVYXpTdzBqcTJ4Zkp0MDczMV9MRVQ1Q1Nyc0RFem9aOUI2d18tVUhpdGZhdy14N21aS1B6eC1oaVlvU3l2RXo4Vm45VUVZTGJBMlVIMHJYUC1TM0VHOEd3OGY1NU5LTTNiSXhCbHc0S2dqRkx0STZ5cUw5SFU4dzRkOHRwYVBSY1drR3NtbFVWU9IBtgFBVV95cUxQRTU2ZnA0WERrSkVxTGtaQXRkbEF6R1MybDk1Q283b0JrYjBWWEozdUZWV0RWVjMzQ095cktCR3libXA4RkpTcXQ2NHQ4UGhieWhfNk4ydGE4WFF5NzltcVMzd3FBRlJIRHRtRWRHMWMxV1hqWlYxc2Y3TEFQbGgwVDRUdFlFNURlRVZDVVdpcnhWS3VubFNuX05wazFiaXp6a0JFNkJnbVdwY1g3MmpYdS13U3hUQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher e proíbe venda de lote de coco ralado por excesso de enxofre - ND Mais</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - MS Todo dia</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,19 +5120,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9HMUF4TXN5WUx0RTZMTUktampKOHB4MjQtTWZyR1ROQ05MOXNYQW95NHpuZjlieXJCYlNGN3U1ZjhCTzlRaEMyWlZ1eUh1TldxaFREdmktMm9IQ0VHSUpDS2U3TFJNZFNiVy1FeWZDVld1X1c2NEpqX09OVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaEFRLWlCUTNMR05sNEtuSzg5T05GVFIzdVlCUHBreS1Pa2NxU3RtSzZaQnNpYmZDRXVadVhVaFhUU0NTQV9HQ0pCUFpqQW1fczZBX3RyUGN2QXhzcldjRWVqanBseDNzTnJKMVJndmRZck9Wa1RqWWx0OXBQc3ZYZlVhUzRaRVhUQzI0SUszalJMQ1RMZTllblpHMV9oUnd4bmdVVFNWVWs2akZP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de coco ralado por excesso de enxofre - O Dia</t>
+          <t>Anvisa manda recolher e proíbe venda de lote de coco ralado por excesso de enxofre - ND Mais</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOeTZiM28xa2hiZEFUbFNlN3RreUVCTGw5RUtYVVVOVG9Fa0o1UWxHcFJLZW1sVThVcXlqT2RWbnNjLWFZTUp4enREa0dUNC0wQUdRVVI3MGRLQWt1cGZTdmNLV2RFR3BNcDJ6aUIxWFBfcGtNV3pMQVFIMnA0T19ud1dvSVVpV3c1U3V5NVJlNzBZS3NhbHFsQklVdzBYZUozV3FvdHNvZ1ViTWx4T2FzTTFYU005TDRjbWfSAb8BQVVfeXFMTnl2N3d1N1JxS2ZqWHZaOVQ2SnBQQ0xDWTRzdWxHLXBzQkxrMVhCTHpvUnBPV2xsTUFGSFRCZEdSNEpnVy1ZMXctUVdpVUM4bkppRU5tdks4dXJuczB2eTdGbXFSbHVkcDZjMW1Id1RZc05DdDBxTWVabXFiQmVndXBUNFhBZmFPUmNYclljdHNaNTlpVjQtX1hEbEhIM1BtbFI1RGZFWVJoUjF6MWVVRVhzV3Y1WDFVZ0hwa2x6N3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9HMUF4TXN5WUx0RTZMTUktampKOHB4MjQtTWZyR1ROQ05MOXNYQW95NHpuZjlieXJCYlNGN3U1ZjhCTzlRaEMyWlZ1eUh1TldxaFREdmktMm9IQ0VHSUpDS2U3TFJNZFNiVy1FeWZDVld1X1c2NEpqX09OVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de dióxido de enxofre - O POVO</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre; confira marca - Rádio Metrópole</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,19 +5186,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXFuR084YlVCYWlxRWFFZElvOXhoZGFYbXh6WXBHZzZOSm40Y3VtSUVzZjh3MVdSRGxvVVhUOWRWOHh4T1lQdUQzYVFBNXhadDhJUGpPVnBmeU1MWUo3Wk81T3JBeGkxVkUyNHlDaU11eldSckM1ZlpmQjJ0VEVFWTI4M1FtYkpxUVc0UVREUXpZZFI0clA1a1ZkS3FiNl9JMzZiVmtwN24xYWNfN0xFUUhKMlYwM1VGRm5PZ3R5cmVTNTBVRkpyb3pQM2w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQSjRVamltMjVSeTh5ZWpfTVZRQnNIRGdhc3AzNkRiQy1oSnFkQnZMczVraFl0WGNjSkhRcmRfclVoQkxtU1BROVNnaWhWaDNnd25MNHNWY28yUTVuMTNvSVpzelNBMjBvMGhCeWdXdlUtZWhwTG9HUV9kSFBDMUIwSTZxWURqQm9pc2xWd19MZ3p2bkZJdjRwUkVKS3plakJuNVdlN0FTd3BIcTdGY09PRXpoMGJtbXNuNUlqNE9zYWNqTVMwNXpXR1dtcllxUW9hM3pQODRscw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Empresas já investiram 42 mil euros em bolsas para estudantes de Engenharia de Minas e Recursos Energéticos do Técnico - Record</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmFyZTFtaDlxMU53dnBYVHctWjlaYjgxWENtckgwTGc4c3RGTXJONGJzV1ZfcVR0UkxDX25pMjRGQzVPaGd4VmhsVGt1LTU0c1h6NVpVRTdNRFRwTU9aVi1HVDh6Sl9fN2dqT1FHeVAwNzVlM2pSTE5ySFk1akxwT29HcjNxM09QcHFMeDlGWUxXQ3RIV2dsSGlKT1UzLXpBVGVTaTd2SFRuMGVLZ3JwVS13cEJyekN0RGRacVBWY21HeXNZSXlkVjRBdDQwSmRqVWFBdGVnTTVDY0xHRnRkejVJeTVQcEFEQ0dfRWlEZWxXWFQzX3VtUnlDWWVMZVlKRWfSAfwBQVVfeXFMUHk4ZkRPbFJnd21WaVVLQURqWk1WOVByTVotSmhwNHZfRThVWThRQ2Y3eWE3RHpVU2gzR0p5c1dIMzFDdkdjNXBPejF3ZWo5bnM1QWtWWEhWeXNndGNCY3VXM2UtYVFXZ1cxZlAyZ0pGd0N0ckZRNmhINW1yQS1NMzZMUzlfa1FDMksyckV2MHRXY05tcVUyLXpvNXpVbnROWjcyTTFGNHViOVVDNlVGbkk0eTZtNVprZ1Q5Tl90NWdNUTJFZGlBUzZQMDBnYzlsUEprWGRYcVZQM3hJa2U4cUhVbHA3MklRSjNCVkFMSXIwSmF3eDhrZjliTmlp?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre; confira marca - Rádio Metrópole</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de dióxido de enxofre - O POVO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,19 +5230,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQSjRVamltMjVSeTh5ZWpfTVZRQnNIRGdhc3AzNkRiQy1oSnFkQnZMczVraFl0WGNjSkhRcmRfclVoQkxtU1BROVNnaWhWaDNnd25MNHNWY28yUTVuMTNvSVpzelNBMjBvMGhCeWdXdlUtZWhwTG9HUV9kSFBDMUIwSTZxWURqQm9pc2xWd19MZ3p2bkZJdjRwUkVKS3plakJuNVdlN0FTd3BIcTdGY09PRXpoMGJtbXNuNUlqNE9zYWNqTVMwNXpXR1dtcllxUW9hM3pQODRscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXFuR084YlVCYWlxRWFFZElvOXhoZGFYbXh6WXBHZzZOSm40Y3VtSUVzZjh3MVdSRGxvVVhUOWRWOHh4T1lQdUQzYVFBNXhadDhJUGpPVnBmeU1MWUo3Wk81T3JBeGkxVkUyNHlDaU11eldSckM1ZlpmQjJ0VEVFWTI4M1FtYkpxUVc0UVREUXpZZFI0clA1a1ZkS3FiNl9JMzZiVmtwN24xYWNfN0xFUUhKMlYwM1VGRm5PZ3R5cmVTNTBVRkpyb3pQM2w?oc=5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa determina recolhimento de coco ralado por excesso de enxofre - O Dia</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOeTZiM28xa2hiZEFUbFNlN3RreUVCTGw5RUtYVVVOVG9Fa0o1UWxHcFJLZW1sVThVcXlqT2RWbnNjLWFZTUp4enREa0dUNC0wQUdRVVI3MGRLQWt1cGZTdmNLV2RFR3BNcDJ6aUIxWFBfcGtNV3pMQVFIMnA0T19ud1dvSVVpV3c1U3V5NVJlNzBZS3NhbHFsQklVdzBYZUozV3FvdHNvZ1ViTWx4T2FzTTFYU005TDRjbWfSAb8BQVVfeXFMTnl2N3d1N1JxS2ZqWHZaOVQ2SnBQQ0xDWTRzdWxHLXBzQkxrMVhCTHpvUnBPV2xsTUFGSFRCZEdSNEpnVy1ZMXctUVdpVUM4bkppRU5tdks4dXJuczB2eTdGbXFSbHVkcDZjMW1Id1RZc05DdDBxTWVabXFiQmVndXBUNFhBZmFPUmNYclljdHNaNTlpVjQtX1hEbEhIM1BtbFI1RGZFWVJoUjF6MWVVRVhzV3Y1WDFVZ0hwa2x6N3M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Portal iG</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,19 +5318,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPV0FOQXhCTERTM29lQTEyZWZXUW1hSE8xNE9tQTdQRWtVYXpTdzBqcTJ4Zkp0MDczMV9MRVQ1Q1Nyc0RFem9aOUI2d18tVUhpdGZhdy14N21aS1B6eC1oaVlvU3l2RXo4Vm45VUVZTGJBMlVIMHJYUC1TM0VHOEd3OGY1NU5LTTNiSXhCbHc0S2dqRkx0STZ5cUw5SFU4dzRkOHRwYVBSY1drR3NtbFVWU9IBtgFBVV95cUxQRTU2ZnA0WERrSkVxTGtaQXRkbEF6R1MybDk1Q283b0JrYjBWWEozdUZWV0RWVjMzQ095cktCR3libXA4RkpTcXQ2NHQ4UGhieWhfNk4ydGE4WFF5NzltcVMzd3FBRlJIRHRtRWRHMWMxV1hqWlYxc2Y3TEFQbGgwVDRUdFlFNURlRVZDVVdpcnhWS3VubFNuX05wazFiaXp6a0JFNkJnbVdwY1g3MmpYdS13U3hUQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,29 +5406,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>27/05/2026 07:00</t>
+          <t>28/05/2026 07:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,29 +5472,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>26/05/2026 07:00</t>
+          <t>27/05/2026 07:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -5506,29 +5506,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>25/05/2026 07:00</t>
+          <t>26/05/2026 07:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,19 +5560,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,19 +5582,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,19 +5604,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,63 +5648,63 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>23/05/2026 07:00</t>
+          <t>25/05/2026 07:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>22/05/2026 07:00</t>
+          <t>23/05/2026 07:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5714,19 +5714,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcG9FWW8yeVV3REc1bWxBY1I1NFh5TmJxbE5BakhjcklocVNvMDVISHNhQjE0NU43Q2tOeGdUaDktQlpFLW5ySHQ3ck5iQ3p2Y1J2aFc3UmJHeTF6cUwxemQ5ejVYQzFxY3Y2djVrQkxTdDh0TnV1NW9vRlNjS29XR1dwSTNOUVhXNVdjTzVMQ3Y3YnpZajZDRHRRUmQ0Z04tRkFUaGFURWFHM3Q3S1gza0xOZXFBMkVNei1LMGZsY3FCV3J2bHdUWUdQOElRTG4yaFltX3VCckFkaFNEZ1R3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5787,22 +5787,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>21/05/2026 07:00</t>
+          <t>22/05/2026 07:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcG9FWW8yeVV3REc1bWxBY1I1NFh5TmJxbE5BakhjcklocVNvMDVISHNhQjE0NU43Q2tOeGdUaDktQlpFLW5ySHQ3ck5iQ3p2Y1J2aFc3UmJHeTF6cUwxemQ5ejVYQzFxY3Y2djVrQkxTdDh0TnV1NW9vRlNjS29XR1dwSTNOUVhXNVdjTzVMQ3Y3YnpZajZDRHRRUmQ0Z04tRkFUaGFURWFHM3Q3S1gza0xOZXFBMkVNei1LMGZsY3FCV3J2bHdUWUdQOElRTG4yaFltX3VCckFkaFNEZ1R3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5831,34 +5831,34 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>20/05/2026 07:00</t>
+          <t>21/05/2026 07:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,19 +5868,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,19 +5890,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,19 +5912,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,29 +5934,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>19/05/2026 07:00</t>
+          <t>20/05/2026 07:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,29 +6000,29 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>18/05/2026 07:00</t>
+          <t>19/05/2026 07:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
@@ -6078,39 +6078,39 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>17/05/2026 01:15</t>
+          <t>18/05/2026 07:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWE5jYU0zdnFBT0JIbWFndHZweHBKUXBWUjJQaWxiNjMzWFRmcTJJRUJya1ktanJ0N0hOZm9KZnRvbzBjVlNXeFUtN0RvR1lXZ0p1WUI1NWd3RGpMS2xlM19TbFFXWkVSWENWME1aUjZjSzI3SDc4eFJUYU8tNDhsakROeUMwTXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>15/05/2026 07:00</t>
+          <t>17/05/2026 01:15</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWE5jYU0zdnFBT0JIbWFndHZweHBKUXBWUjJQaWxiNjMzWFRmcTJJRUJya1ktanJ0N0hOZm9KZnRvbzBjVlNXeFUtN0RvR1lXZ0p1WUI1NWd3RGpMS2xlM19TbFFXWkVSWENWME1aUjZjSzI3SDc4eFJUYU8tNDhsakROeUMwTXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -6139,100 +6139,100 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>14/05/2026 07:00</t>
+          <t>15/05/2026 07:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>13/05/2026 07:00</t>
+          <t>14/05/2026 07:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>12/05/2026 13:11</t>
+          <t>13/05/2026 07:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>12/05/2026 07:00</t>
+          <t>12/05/2026 13:11</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes tem prejuízo de US$ 422 mi com paralisações em Minas - Diário do Comércio</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,19 +6242,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1OTzdvNnBuejJSeVRQaXZRQXBnTHVzNFoxNUp6dl9JcEVDUlVoUmpEcTNpUXRlSG1nNHVKSTd4d1E0eWFTemR2UzJyWnhYZXB2SFc5RWlILXJnaGpoQjh3N0hxV0R2MVQzbU9BU2EySHpIY0VjVUJ6YWZJM1gyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
+          <t>Kaio Jorge marca, Cruzeiro suporta pressão e avança às oitavas da Copa do Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6264,19 +6264,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNajlTUWF0U2hUVWdZek85WmpHOWtqcks2OE5lNHpVczlfZEUwMmdoSm1ub25JQUk1dUIzMFQ0VG9RaExVZXdsbHk4S2ZBdmpuWmd3NEFwZ0tFalVMU1c5UktST0YwUFY4UEtpajBqVUFDV2ZmQ2ZMVW5nb1ZJX1ZmZmZyQnNtbFVUOTBVVGVFRFJoRklnZFFJdm9IUnB3NTdORkRYMTVkS3UzTWM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Kaio Jorge marca, Cruzeiro suporta pressão e avança às oitavas da Copa do Brasil - tmc.com.br</t>
+          <t>Mosaic Fertilizantes tem prejuízo de US$ 422 mi com paralisações em Minas - Diário do Comércio</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNajlTUWF0U2hUVWdZek85WmpHOWtqcks2OE5lNHpVczlfZEUwMmdoSm1ub25JQUk1dUIzMFQ0VG9RaExVZXdsbHk4S2ZBdmpuWmd3NEFwZ0tFalVMU1c5UktST0YwUFY4UEtpajBqVUFDV2ZmQ2ZMVW5nb1ZJX1ZmZmZyQnNtbFVUOTBVVGVFRFJoRklnZFFJdm9IUnB3NTdORkRYMTVkS3UzTWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1OTzdvNnBuejJSeVRQaXZRQXBnTHVzNFoxNUp6dl9JcEVDUlVoUmpEcTNpUXRlSG1nNHVKSTd4d1E0eWFTemR2UzJyWnhYZXB2SFc5RWlILXJnaGpoQjh3N0hxV0R2MVQzbU9BU2EySHpIY0VjVUJ6YWZJM1gyUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
@@ -6320,51 +6320,51 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
+          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>11/05/2026 16:42</t>
+          <t>12/05/2026 07:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>11/05/2026 07:00</t>
+          <t>11/05/2026 16:42</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,19 +6374,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>Polícia Militar apreende arma de fogo, munições e drogas no bairro Jardim Cruzeiro - Acorda Cidade</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNMkN6R0NicFFIMjViTjNQYWFwZ2xLUEhFNWw3UTJnMENJcEJKS0pmWWhsRTRRMFpObEhjU0dOdTU0Y2tyT0h5Q21MaVhhM2NkWHFtQ0RzTGZJWUVTbGNCQzFCN0RfZ19KS1ZXa2FhS2E4bHY4VG5ybVJIc3VhbnZHWlRRZEFZeXJSTG1HenJDNFZqSWRocmdDdW9JTjc0d05IRGNsWTRja09ZMkxKYW1uRWNCMFZXV3NTMmZyTlpVZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Polícia Militar apreende arma de fogo, munições e drogas no bairro Jardim Cruzeiro - Acorda Cidade</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,19 +6462,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNMkN6R0NicFFIMjViTjNQYWFwZ2xLUEhFNWw3UTJnMENJcEJKS0pmWWhsRTRRMFpObEhjU0dOdTU0Y2tyT0h5Q21MaVhhM2NkWHFtQ0RzTGZJWUVTbGNCQzFCN0RfZ19KS1ZXa2FhS2E4bHY4VG5ybVJIc3VhbnZHWlRRZEFZeXJSTG1HenJDNFZqSWRocmdDdW9JTjc0d05IRGNsWTRja09ZMkxKYW1uRWNCMFZXV3NTMmZyTlpVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6484,19 +6484,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6518,17 +6518,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>08/05/2026 07:00</t>
+          <t>11/05/2026 07:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6579,44 +6579,44 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>06/05/2026 14:23</t>
+          <t>08/05/2026 07:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>06/05/2026 07:00</t>
+          <t>06/05/2026 14:23</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,19 +6638,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,29 +6660,29 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>04/05/2026 07:00</t>
+          <t>06/05/2026 07:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6748,19 +6748,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6792,19 +6792,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6814,51 +6814,51 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Fertilidade de Potássio e Enxofre em Soja durante a estação - Tessenderlo Kerley</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>01/05/2026 10:04</t>
+          <t>04/05/2026 07:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeXZkSXBId3cwOVBBWE9XdURoZ0daUTlpZ1Y4R21PNjlYMU8yY2FLc2ZuZzhoakNxOTZnY3JFTU9JUDdvMzdibDExa0hTeWM5b0c5MHliWDFHT0VOVzVkRUFlZVlPSGdNbURpcVQxeTR6dzJnbG85YkxLb09SVXNKbG15ZmpEenZGbU9qU1pub25RTGc3U2IyMWJubW40dC0xUi1PWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Fertilidade de Potássio e Enxofre em Soja durante a estação - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>01/05/2026 07:00</t>
+          <t>01/05/2026 10:04</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeXZkSXBId3cwOVBBWE9XdURoZ0daUTlpZ1Y4R21PNjlYMU8yY2FLc2ZuZzhoakNxOTZnY3JFTU9JUDdvMzdibDExa0hTeWM5b0c5MHliWDFHT0VOVzVkRUFlZVlPSGdNbURpcVQxeTR6dzJnbG85YkxLb09SVXNKbG15ZmpEenZGbU9qU1pub25RTGc3U2IyMWJubW40dC0xUi1PWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6892,29 +6892,29 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>30/04/2026 07:00</t>
+          <t>01/05/2026 07:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6968,19 +6968,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkONIB5gFBVV95cUxORWpyQ285M1U3ekpPWWVwMER6dTNMTWlZZ3h3VFBwSmRiZ1Y0dnZvb0NtaVlXR0FSank5ZklXMkl6NUhFcG1wcWFuX3lld0VSeFktQU1PUUxESFg5VE0zRlBPaVNfb1VFZTE3ZUFsRDB4N1ZYVUo1dXMxN210RW84LU5scWp4MXppTEZLWFlEeC1mdE9hYkhOTmNoaVUzOFA2d3lvVkZ1cWxCM1A5YWxMUW0tamkxS3BqSUNxRUlWcFo1cUZ2bFVtdlIyd2xKM2FjQTBkcmJjVWdtSlI4WFNlRkxHZlBQdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkONIB5gFBVV95cUxORWpyQ285M1U3ekpPWWVwMER6dTNMTWlZZ3h3VFBwSmRiZ1Y0dnZvb0NtaVlXR0FSank5ZklXMkl6NUhFcG1wcWFuX3lld0VSeFktQU1PUUxESFg5VE0zRlBPaVNfb1VFZTE3ZUFsRDB4N1ZYVUo1dXMxN210RW84LU5scWp4MXppTEZLWFlEeC1mdE9hYkhOTmNoaVUzOFA2d3lvVkZ1cWxCM1A5YWxMUW0tamkxS3BqSUNxRUlWcFo1cUZ2bFVtdlIyd2xKM2FjQTBkcmJjVWdtSlI4WFNlRkxHZlBQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,29 +7056,29 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>28/04/2026 07:00</t>
+          <t>30/04/2026 07:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7122,29 +7122,29 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>27/04/2026 07:00</t>
+          <t>28/04/2026 07:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7217,44 +7217,44 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>24/04/2026 07:00</t>
+          <t>27/04/2026 07:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>22/04/2026 07:00</t>
+          <t>24/04/2026 07:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7305,22 +7305,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>21/04/2026 21:42</t>
+          <t>22/04/2026 07:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7332,39 +7332,39 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Cientistas criam polímero de enxofre que elimina fungos e bactérias sem afetar humanos - O Cafezinho</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>21/04/2026 07:00</t>
+          <t>21/04/2026 21:42</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZ3BJUzNVZHdWeFpabk9HUElZN1AtQWtsT2FoVmx6RHNnclJ4LWpNVlRpakhINEJzTWlUNzIwNnFQWGxWZ0RxbG9VMW9vYUN2d0xCdlBndWFqOU5oZTd3ZFZVaWwwS2xDY3prcTd6Z1phaWhhMGxVQlNrWm53X0tlOEJuRVhscmRybnRDRmctdENSajgtS2ZnRkgwNUFiV1dmUFR6ZTZiczVXbEJEdlZPQkxqY1lFdFkyZncwU1FCMWVPaFnSAcgBQVVfeXFMT2dxMVIzak5qWE41TFY1dVRXWXFTaGtFRWF0U3k1b1JtSWYtMjBZVkRGTjQtRlp2QkJQS25UeGhmMmRqTzgzd3Iza2dWcWducVB2Qjk2WGJqRF80bHZJNU5rZXBMNXpTLVd6dk1nd2Rhd0d6b2lqNlFmYWFGOW5UQmJWcUVuZW9BLWtybWNUcDFZdko3bVZSTDVyeElkZE90M3dqTFY5eTFWNi0tTUZoOEs2VDBzOHNjUlVHZGhmRmg5S3VsbjRIaXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Cientistas criam polímero de enxofre que elimina fungos e bactérias sem afetar humanos - O Cafezinho</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>20/04/2026 07:00</t>
+          <t>21/04/2026 07:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZ3BJUzNVZHdWeFpabk9HUElZN1AtQWtsT2FoVmx6RHNnclJ4LWpNVlRpakhINEJzTWlUNzIwNnFQWGxWZ0RxbG9VMW9vYUN2d0xCdlBndWFqOU5oZTd3ZFZVaWwwS2xDY3prcTd6Z1phaWhhMGxVQlNrWm53X0tlOEJuRVhscmRybnRDRmctdENSajgtS2ZnRkgwNUFiV1dmUFR6ZTZiczVXbEJEdlZPQkxqY1lFdFkyZncwU1FCMWVPaFnSAcgBQVVfeXFMT2dxMVIzak5qWE41TFY1dVRXWXFTaGtFRWF0U3k1b1JtSWYtMjBZVkRGTjQtRlp2QkJQS25UeGhmMmRqTzgzd3Iza2dWcWducVB2Qjk2WGJqRF80bHZJNU5rZXBMNXpTLVd6dk1nd2Rhd0d6b2lqNlFmYWFGOW5UQmJWcUVuZW9BLWtybWNUcDFZdko3bVZSTDVyeElkZE90M3dqTFY5eTFWNi0tTUZoOEs2VDBzOHNjUlVHZGhmRmg5S3VsbjRIaXA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7376,105 +7376,105 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>17/04/2026 07:00</t>
+          <t>20/04/2026 07:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>16/04/2026 07:00</t>
+          <t>17/04/2026 07:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
+          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>15/04/2026 22:32</t>
+          <t>16/04/2026 07:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>14/04/2026 07:00</t>
+          <t>15/04/2026 22:32</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Líder em recuperação e processamento de enxofre - Tessenderlo Kerley</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>13/04/2026 11:05</t>
+          <t>14/04/2026 07:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbUhXVzFvVVctdDZWUlE3OXNmbnJzcndpOGZ6Y2FlNGhueTB2blAtUFBGbmcwTG81eDZNN1NORzRyUktTLXo3X3RaSVRsNjA4UDF4NGFPQWlFVm9nU0Jfc25FSkNKQmlNaFFvX21NMEFWOFpzZmR2UWFBd3N2cVdmRmJER18tbmRu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,29 +7486,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Líder em recuperação e processamento de enxofre - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>13/04/2026 07:00</t>
+          <t>13/04/2026 11:05</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbUhXVzFvVVctdDZWUlE3OXNmbnJzcndpOGZ6Y2FlNGhueTB2blAtUFBGbmcwTG81eDZNN1NORzRyUktTLXo3X3RaSVRsNjA4UDF4NGFPQWlFVm9nU0Jfc25FSkNKQmlNaFFvX21NMEFWOFpzZmR2UWFBd3N2cVdmRmJER18tbmRu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7547,34 +7547,34 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>10/04/2026 07:00</t>
+          <t>13/04/2026 07:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7584,19 +7584,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - BNamericas</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>10/04/2026 07:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - BNamericas</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7706,17 +7706,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>08/04/2026 07:00</t>
+          <t>09/04/2026 07:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,51 +7914,51 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>07/04/2026 07:00</t>
+          <t>08/04/2026 07:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>06/04/2026 07:00</t>
+          <t>07/04/2026 07:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,51 +7980,51 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>02/04/2026 20:10</t>
+          <t>06/04/2026 07:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>01/04/2026 07:00</t>
+          <t>02/04/2026 20:10</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8053,34 +8053,34 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>31/03/2026 07:00</t>
+          <t>01/04/2026 07:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Caldense apresenta elenco para temporada de 2026 - onda poços</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8090,19 +8090,19 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE95MkZIWmpVeXBPdDVYRy13QnhHYnZtd3dHOUpQcnV0VmliYmNLemhIZXRZTVhVMmFqTjRBMmNJQTl2dVF0TWJTWEV6M3k1MzBQbGpJVWN5MWhVNVlxTFl3ZVNCdlFld2RyX19qUlJRLWtUTlVLdXZBRFY3RDYyLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Caldense apresenta jogadores que vão disputar o Módulo II do Mineiro de 2026 - PocosCom</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8112,19 +8112,19 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaHBlSjh0OEN5c0hhaFNud3ZtU0pacFBRUlFfQkVTWVZBczJiWE5IZklZbjQ2ODBiZ3FOeFoteG91X2NVWE00anhaTDA5dGRidTA1MUxqYkRIaEtBblZ3SkY5VWdfRmc4RUxaeHV6VW5yUmNTeWNlREp6LUpSNmg2TFYwMzNWSll1NkJMTFhtT2FXWVJDTWtTaVAtMDJnaUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Caldense apresenta elenco para temporada de 2026 - onda poços</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8134,63 +8134,63 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE95MkZIWmpVeXBPdDVYRy13QnhHYnZtd3dHOUpQcnV0VmliYmNLemhIZXRZTVhVMmFqTjRBMmNJQTl2dVF0TWJTWEV6M3k1MzBQbGpJVWN5MWhVNVlxTFl3ZVNCdlFld2RyX19qUlJRLWtUTlVLdXZBRFY3RDYyLTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Caldense apresenta jogadores que vão disputar o Módulo II do Mineiro de 2026 - PocosCom</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>30/03/2026 07:00</t>
+          <t>31/03/2026 07:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaHBlSjh0OEN5c0hhaFNud3ZtU0pacFBRUlFfQkVTWVZBczJiWE5IZklZbjQ2ODBiZ3FOeFoteG91X2NVWE00anhaTDA5dGRidTA1MUxqYkRIaEtBblZ3SkY5VWdfRmc4RUxaeHV6VW5yUmNTeWNlREp6LUpSNmg2TFYwMzNWSll1NkJMTFhtT2FXWVJDTWtTaVAtMDJnaUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>27/03/2026 07:00</t>
+          <t>30/03/2026 07:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Após anos de reclamações por barulho, pequena comunidade rural dos EUA força saída de mineradora de Bitcoin da região - Livecoins</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,19 +8200,19 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcnZsLVNQY3dYX3dtUG5pbkhwZzRTZVFhU0Q1dDEyWllPWjdsc0JKdG9VTkpRd19uOU5lYVpob1kxWS1MMVp6Xzg3VkZpYjJ1UTJ0QXBGRFZxVHY2aTFFQzVRc05SX2ZuSnFjeXdqU2dXYVlDYkNMS0hDRE9iVnBXYUsteTlKTnZYWmwyZXhtMklYVk9JZW1YQ3JPZzNlV054TkFzbnRxaTZqd0Z2dm9XbTRtakRKMXZyQVUtaXlQaTJoVFNiZjlpTFhIQmNwVnVoeDV2elFiTmFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8222,19 +8222,19 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8244,19 +8244,19 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8442,19 +8442,19 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,19 +8508,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,19 +8530,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar sulfato de amônio em 2026 - Notícias Agrícolas</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8618,51 +8618,51 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQNzYxMi1VVEdnMTlnT29ZUjhKMmN2a0RZMVR4X0o5Yk1QZkdLYU4wZVQ0RGlqYm1hUVE0UnJtcUl6MXdpYXcyYzdGdzZRaS1aMVI4UnNTeHRqa1lnSzl0eFNLWmxrSUZrRUpJU2hpWm1NSnhIRVBYZjh3NEc3UVJIT0stY2ltMWxITUZaODVtSllTd3BqYUtYMHA4eE9OSnFsZTU5MDFOQnhsa2xZRU5HY3FmUU9ILW5peko5dklXOGN1QzlPYUlJRnhPaVljTU4yQzdrMll3ZGpPVWlrUGfSAeMBQVVfeXFMTThXa1RleEtxQzR1a25yZThEUFAtajRDZEtFbFpnOFk2TWYxcUJ4UEtEYzVYdmF2YlFEZG9YTlpKam5yeUVJLWczZlRWR1pseS1CMzRENXcyUVhkM212UEhaMUhUTHJWTkZ4WkFwQWktck1ob1BwejdieXZPdjNFNzUwM1ZGUG9wamktbHhFM2FlQUhnWW92YmtQZ2IxOUoxZVU5ZDBYY1UtMW5lbTNFb3pTUjBrV3pnWlV0WWJBNGg4YWlxRzlCSDVRZF9jZzBlYzJ3S3o3WWVLRi10QzhLdFFTY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>16/03/2026 07:00</t>
+          <t>14/03/2026 07:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Archtrends - Portobello</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>14/03/2026 07:00</t>
+          <t>13/03/2026 07:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
@@ -8691,34 +8691,34 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Archtrends - Portobello</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>13/03/2026 07:00</t>
+          <t>11/03/2026 07:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário gratuito pelo programa Terra Boa; veja detalhes - JDV - Jornal do Vale</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,19 +8728,19 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBoVzBPSUx1aFltY2FyUnN2Ym1qNExJZkxKckl1bnpsdGwzT2hZdF9PaDN1SHhFV1pQRTNmTWM1TXMtakYyUERmcmRwaVpLRk5kb2JUZ1NobzJVblFVWEp2c0xvVVh2ZDg1WEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,19 +8750,19 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Agricultores de Corupá já podem solicitar calcário gratuito pelo programa Terra Boa; veja detalhes - JDV - Jornal do Vale</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,19 +8772,19 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBoVzBPSUx1aFltY2FyUnN2Ym1qNExJZkxKckl1bnpsdGwzT2hZdF9PaDN1SHhFV1pQRTNmTWM1TXMtakYyUERmcmRwaVpLRk5kb2JUZ1NobzJVblFVWEp2c0xvVVh2ZDg1WEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8794,63 +8794,63 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>11/03/2026 07:00</t>
+          <t>10/03/2026 15:14</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>10/03/2026 15:14</t>
+          <t>09/03/2026 07:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8860,19 +8860,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,19 +8882,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,19 +8904,19 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,29 +8926,29 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>09/03/2026 07:00</t>
+          <t>06/03/2026 08:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9004,39 +9004,39 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>06/03/2026 08:00</t>
+          <t>05/03/2026 08:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>05/03/2026 08:00</t>
+          <t>04/03/2026 13:02</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9048,29 +9048,29 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>04/03/2026 13:02</t>
+          <t>04/03/2026 08:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9080,19 +9080,19 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9102,19 +9102,19 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,29 +9124,29 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>04/03/2026 08:00</t>
+          <t>03/03/2026 08:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9190,19 +9190,19 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9212,95 +9212,95 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>03/03/2026 08:00</t>
+          <t>28/02/2026 08:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>28/02/2026 08:00</t>
+          <t>27/02/2026 08:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>27/02/2026 08:00</t>
+          <t>26/02/2026 08:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>26/02/2026 08:00</t>
+          <t>25/02/2026 08:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9329,34 +9329,34 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>25/02/2026 08:00</t>
+          <t>20/02/2026 08:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9366,19 +9366,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9410,19 +9410,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9498,19 +9498,19 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>CBPM barra venda de US$ 1 bi da Equinox Gold - BPMoney</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9696,19 +9696,19 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBWblRQRGhkRGVieU40amJOckdTQncyS21zQno3b0hlNmQxQU5ZTkRMTDc2clI3SEs0ckFJT3BMeFY3M09Zd0hNb0hMU2tOWjlMSldqTzJ3cmR2a1VlZHNsMHBEYUZwWWkxbnRsUFVZVWJsOURCMjZTUHdHaUJEZ0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
+          <t>CBPM barra venda de US$ 1 bi da Equinox Gold - BPMoney</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBWblRQRGhkRGVieU40amJOckdTQncyS21zQno3b0hlNmQxQU5ZTkRMTDc2clI3SEs0ckFJT3BMeFY3M09Zd0hNb0hMU2tOWjlMSldqTzJ3cmR2a1VlZHNsMHBEYUZwWWkxbnRsUFVZVWJsOURCMjZTUHdHaUJEZ0k?oc=5</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10143,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Saída de Gabigol do Cruzeiro é consenso; destino passa a ser a dúvida - DeFato.com</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNa2tNM01IRUF0a3VjME5PaDlsRWd5cW5OVW90a1J1SmxVZm5sbC1fdDZkVjZRcm1TYTdhRWs1RTJuSzJhUEhPYXpvWmhqcUExdGV5VkNPaXZLQmVvdzh0VTFraG9QbmZsZ3VlbFpXSThWWTNLLTdsZkNQNEFSLVhUcjQ5U1VIQ1BGSXZYd2tTLWV4SS1SWEl4bGdLal8tc0lz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>Saída de Gabigol do Cruzeiro é consenso; destino passa a ser a dúvida - DeFato.com</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNa2tNM01IRUF0a3VjME5PaDlsRWd5cW5OVW90a1J1SmxVZm5sbC1fdDZkVjZRcm1TYTdhRWs1RTJuSzJhUEhPYXpvWmhqcUExdGV5VkNPaXZLQmVvdzh0VTFraG9QbmZsZ3VlbFpXSThWWTNLLTdsZkNQNEFSLVhUcjQ5U1VIQ1BGSXZYd2tTLWV4SS1SWEl4bGdLal8tc0lz?oc=5</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10561,12 +10561,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>E se for para os pênaltis? Quem leva vantagem entre Hugo Souza e Cássio em Corinthians x Cruzeiro na Copa do Brasil - ESPN Brasil</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,19 +10576,19 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPOWs4S016VVRvTnBGOURieGlCNWlNZjIyX21jOV9HYjlMZGpyLS1LMUx3Nkt0Wm5rc21aMkpSZTlxdHEzLWpRV05XLTRReVFzQTVEazNEb19QSW9PemJwWjhMYWstVkYwVmhzZ1RRMjk5MWtJa2FnUzNzd096MWFHRFZTM013YlNqaXpPUWdEZjlHMGowaW92Qk5RUXZTWUdKbWtuMDg2cTU0eEVmYkNGNnctc2doX09vaFhqejNLNW9CSkt3czBFRFVSam1QdnJUMmcyd290SzgtRW9OY05hdDlacm11LVAx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Cássio iguala Dida em pênaltis defendidos; veja ranking - band.com.br</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNMFU4a0ZjNk5fVWV1eGpWbDJ2UjRTUW1rS1RZZWFVVThzMm1nQVFYbDB0dDhHblE4d2R0di1ac3dJUjhBZWlWbTI2d3FsWU15emhnbExQSU54VFprZjJKNE1mWTN3dmlEby1qTnY2dWxvdmlmak9HUU5pajVrVE5yRjRVRm5Ock5Rdnd0b0dxNnk1U2k5RnNGb29DUkhYemRsRFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Corinthians vence o Cruzeiro nos pênaltis e vai à final da Copa do Brasil - band.com.br</t>
+          <t>Corinthians elimina Cruzeiro pela 3ª vez na história da Copa do Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPV1d5dEFNd0t1ME9tQWJSWWRzLWtuckNpd25abG9vcUJ3czlmcl9xLTQxQmE4Ni1udEFTRDBFZUd3VWFMMU5McWlELUtoTG50dTZTeXY2SmtJMXdObllneDBuV1JLbXdscG1NTzhRLTJMSExGQjNxSkF3WjBuS0dkaXBYdTR0WW1DeDBQdVBvUzlmZ1JQM2pSVDhqdEFCdXlXWjZqSlhoT3ZjeVNMZGtobGdsTlBoWUpZVGlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQQ1AzUm1KNUYtMGxCaEFfQ05zUzNnemhZblotcVNfdlY2RU9Hd0M3UThGX3JEdHFoRVdFa1BncW9PanJUVHVZSEVzZk8xbmxGRkZqa2lPZWJXQjBQZjhJN04weV96TGFqS0dNNEtUZW9RQWlvNS1UUkpGYmU2ckl0S0RwaEpHR1BCaWFBeUYyeXhXdlhTQkZKRVNRUUg3OVRwTGNYUGtRbmFOVUtpQlBpWk1naHhHSTRNM2V1ZWVtV2xLQ1N3bnRnU1ZoMjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Corinthians elimina Cruzeiro pela 3ª vez na história da Copa do Brasil - CNN Brasil</t>
+          <t>Hugo Souza gigante, Corinthians elimina o Cruzeiro nos pênaltis e está na final da Copa do Brasil - capitalnews.com.br</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQQ1AzUm1KNUYtMGxCaEFfQ05zUzNnemhZblotcVNfdlY2RU9Hd0M3UThGX3JEdHFoRVdFa1BncW9PanJUVHVZSEVzZk8xbmxGRkZqa2lPZWJXQjBQZjhJN04weV96TGFqS0dNNEtUZW9RQWlvNS1UUkpGYmU2ckl0S0RwaEpHR1BCaWFBeUYyeXhXdlhTQkZKRVNRUUg3OVRwTGNYUGtRbmFOVUtpQlBpWk1naHhHSTRNM2V1ZWVtV2xLQ1N3bnRnU1ZoMjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQMlJiZVMtX3NqVlBzYzBDUnJPVk5ZWkRYcmszc2FVY2dMTWVkRG8yTDhCU1pxcl9jR0dIN0tKUHFVRVlOblVuOTdpdXlYR2lZSjhSQkpZZ25CSE5VX3Y1bThsa2dnMkpOUEtwVmF2ek5OZXFhZm1CRGF5elZQNW5SV2VjYy0wV1ZTU3hQRmswT1Z1OFRHRG5ydHlvRlEyb2oyekhBbG1uOWdpM1dIZkVXUWNMVy1Rdm9wa3dMMlZyeDZ3SENla2VjR0xqdGt0b3NnTWc2T0hQb2hWc1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>E se for para os pênaltis? Quem leva vantagem entre Hugo Souza e Cássio em Corinthians x Cruzeiro na Copa do Brasil - ESPN Brasil</t>
+          <t>Corinthians vence o Cruzeiro nos pênaltis e vai à final da Copa do Brasil - band.com.br</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPOWs4S016VVRvTnBGOURieGlCNWlNZjIyX21jOV9HYjlMZGpyLS1LMUx3Nkt0Wm5rc21aMkpSZTlxdHEzLWpRV05XLTRReVFzQTVEazNEb19QSW9PemJwWjhMYWstVkYwVmhzZ1RRMjk5MWtJa2FnUzNzd096MWFHRFZTM013YlNqaXpPUWdEZjlHMGowaW92Qk5RUXZTWUdKbWtuMDg2cTU0eEVmYkNGNnctc2doX09vaFhqejNLNW9CSkt3czBFRFVSam1QdnJUMmcyd290SzgtRW9OY05hdDlacm11LVAx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPV1d5dEFNd0t1ME9tQWJSWWRzLWtuckNpd25abG9vcUJ3czlmcl9xLTQxQmE4Ni1udEFTRDBFZUd3VWFMMU5McWlELUtoTG50dTZTeXY2SmtJMXdObllneDBuV1JLbXdscG1NTzhRLTJMSExGQjNxSkF3WjBuS0dkaXBYdTR0WW1DeDBQdVBvUzlmZ1JQM2pSVDhqdEFCdXlXWjZqSlhoT3ZjeVNMZGtobGdsTlBoWUpZVGlv?oc=5</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Hugo Souza gigante, Corinthians elimina o Cruzeiro nos pênaltis e está na final da Copa do Brasil - capitalnews.com.br</t>
+          <t>Cássio iguala Dida em pênaltis defendidos; veja ranking - band.com.br</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQMlJiZVMtX3NqVlBzYzBDUnJPVk5ZWkRYcmszc2FVY2dMTWVkRG8yTDhCU1pxcl9jR0dIN0tKUHFVRVlOblVuOTdpdXlYR2lZSjhSQkpZZ25CSE5VX3Y1bThsa2dnMkpOUEtwVmF2ek5OZXFhZm1CRGF5elZQNW5SV2VjYy0wV1ZTU3hQRmswT1Z1OFRHRG5ydHlvRlEyb2oyekhBbG1uOWdpM1dIZkVXUWNMVy1Rdm9wa3dMMlZyeDZ3SENla2VjR0xqdGt0b3NnTWc2T0hQb2hWc1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNMFU4a0ZjNk5fVWV1eGpWbDJ2UjRTUW1rS1RZZWFVVThzMm1nQVFYbDB0dDhHblE4d2R0di1ac3dJUjhBZWlWbTI2d3FsWU15emhnbExQSU54VFprZjJKNE1mWTN3dmlEby1qTnY2dWxvdmlmak9HUU5pajVrVE5yRjRVRm5Ock5Rdnd0b0dxNnk1U2k5RnNGb29DUkhYemRsRFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10825,12 +10825,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10862,19 +10862,19 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>

--- a/Noticias_Calcario_20260714.xlsx
+++ b/Noticias_Calcario_20260714.xlsx
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3162,19 +3162,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,19 +3426,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Brazilian Farmers Delay Input Purchases as They Await Debt Relief Bill, Mosaic Says - The AgriBiz</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3448,19 +3448,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQN2xNaUxQMDVWZl9tOVF1UFA3SG9QaHdTVndkU2Z3ci1Dazl6cElWRmV1NjVDMzVyY1Z1ckh1S2kydnFleVQ0YXpnOExKdlpBVkFPMk1xUWJodkpjODgyMzB3Q1lSdmN1Rm04SG1yb3hLbnhjb21fdUFoeFFoN0d6d3YzSHVfMmZWcF9WMHBKV2RRTUR6Z1VuRTRKM21CdTctOGh6VDdQSHhaQ0xhZV9xd1c0dU9wVkZIQ2U3c21weWtCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Brazilian Farmers Delay Input Purchases as They Await Debt Relief Bill, Mosaic Says - The AgriBiz</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQN2xNaUxQMDVWZl9tOVF1UFA3SG9QaHdTVndkU2Z3ci1Dazl6cElWRmV1NjVDMzVyY1Z1ckh1S2kydnFleVQ0YXpnOExKdlpBVkFPMk1xUWJodkpjODgyMzB3Q1lSdmN1Rm04SG1yb3hLbnhjb21fdUFoeFFoN0d6d3YzSHVfMmZWcF9WMHBKV2RRTUR6Z1VuRTRKM21CdTctOGh6VDdQSHhaQ0xhZV9xd1c0dU9wVkZIQ2U3c21weWtCdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Arqueólogos encontram mosaico de deus do rio na Turquia - Aventuras na História</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3514,19 +3514,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdFM4Yk1jUU5RMURVMTViQklhT2I4SW1jWUxTRVI0azJDM2lmMGtrWThNNGNKTE5HcWFabEV5MUVNU2lSc2NIYkhmbm5xcWZieXAxRmRpN1BPWXlscGtIZmZyZHREWkhQc21scEQ0d3ZobjB6eER4TVNMMHpfVUNMUGRVY3lFNnRRRGVhLUxVd0l0OXBRT3RKWjdtMENVcm5RRURBZ2EyVlNXTkc2UlpjdWozMVRXMWdyVW5j?oc=5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3536,19 +3536,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,19 +3558,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Arqueólogos encontram mosaico de deus do rio na Turquia - Aventuras na História</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3580,19 +3580,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdFM4Yk1jUU5RMURVMTViQklhT2I4SW1jWUxTRVI0azJDM2lmMGtrWThNNGNKTE5HcWFabEV5MUVNU2lSc2NIYkhmbm5xcWZieXAxRmRpN1BPWXlscGtIZmZyZHREWkhQc21scEQ0d3ZobjB6eER4TVNMMHpfVUNMUGRVY3lFNnRRRGVhLUxVd0l0OXBRT3RKWjdtMENVcm5RRURBZ2EyVlNXTkc2UlpjdWozMVRXMWdyVW5j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3690,29 +3690,29 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>23/06/2026 07:00</t>
+          <t>22/06/2026 22:10</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3724,17 +3724,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>22/06/2026 22:10</t>
+          <t>22/06/2026 12:06</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3746,39 +3746,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>22/06/2026 12:06</t>
+          <t>22/06/2026 11:41</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>22/06/2026 11:41</t>
+          <t>22/06/2026 07:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
@@ -3834,17 +3834,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>22/06/2026 07:00</t>
+          <t>21/06/2026 07:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3888,63 +3888,63 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Itamaraty faz varredura emergencial atrás de fertilizantes para o Brasil - Jornal do Comércio</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>21/06/2026 07:00</t>
+          <t>20/06/2026 20:42</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxONEFWVzJtWFhfVnFJdkpadjFtWXJaRTdYT0lUc0djdktrOEw2M0ltdnlGOFFOcWZCQ08zcXdNQU1uMkJpSV9DTnh5ajJWZDJ2NmxFaFdNMGk0VmdMbjdsWUdiNTYtSVhqNUpvWUNBbmRKNlRoTTFEOUpoQlNGX2lDUkFhQXhPVE40WldxUzhBVkhVWGdJZ2pnNk1HYVZLUXZfX1lDUnNTZndiU19rdzlTN0lOX1F2Q3EzU0JPY0h5bzBfajkycDFKOG10Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Itamaraty faz varredura emergencial atrás de fertilizantes para o Brasil - Jornal do Comércio</t>
+          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>20/06/2026 20:42</t>
+          <t>20/06/2026 07:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxONEFWVzJtWFhfVnFJdkpadjFtWXJaRTdYT0lUc0djdktrOEw2M0ltdnlGOFFOcWZCQ08zcXdNQU1uMkJpSV9DTnh5ajJWZDJ2NmxFaFdNMGk0VmdMbjdsWUdiNTYtSVhqNUpvWUNBbmRKNlRoTTFEOUpoQlNGX2lDUkFhQXhPVE40WldxUzhBVkhVWGdJZ2pnNk1HYVZLUXZfX1lDUnNTZndiU19rdzlTN0lOX1F2Q3EzU0JPY0h5bzBfajkycDFKOG10Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
@@ -3983,22 +3983,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>ProSolos: Capão Bonito do Sul distribui calcário para 25 produtores rurais - Tua Rádio</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20/06/2026 07:00</t>
+          <t>19/06/2026 07:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPczJPU19lVkVaMG8wVGZGVEpQbjQyb3pYbmY2VGhUNW1GVW9lazlCaEtONGlDR3ZpSHFxVWMwaGoyNXhzcTRBLXREWkVKZUQtNF9TRXFWY1pnYXIwS3RfNVBkaTJIbFh5blVtaEZuRWhDRzU3dW5ETDZ5RXBEZU5KZzR5NW9OMTluT0dHaGU5OC0taUI5Y2FzXzZLdlZkb2tjdnMwS2ZXTXZDMnBJT05xTEFXNFl0VXBpRTlFWVA5ZFFja2xCdGpPSExFNDJsdGVjbUVaYnNhYmFsSGZkbVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4027,34 +4027,34 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ProSolos: Capão Bonito do Sul distribui calcário para 25 produtores rurais - Tua Rádio</t>
+          <t>Compra de ativos existentes pode antecipar em dois anos o início da operação da St George em Araxá - Diário do Comércio</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>19/06/2026 07:00</t>
+          <t>18/06/2026 07:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPczJPU19lVkVaMG8wVGZGVEpQbjQyb3pYbmY2VGhUNW1GVW9lazlCaEtONGlDR3ZpSHFxVWMwaGoyNXhzcTRBLXREWkVKZUQtNF9TRXFWY1pnYXIwS3RfNVBkaTJIbFh5blVtaEZuRWhDRzU3dW5ETDZ5RXBEZU5KZzR5NW9OMTluT0dHaGU5OC0taUI5Y2FzXzZLdlZkb2tjdnMwS2ZXTXZDMnBJT05xTEFXNFl0VXBpRTlFWVA5ZFFja2xCdGpPSExFNDJsdGVjbUVaYnNhYmFsSGZkbVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE90MzZRdUdobThNWk13akRvUnVnWno1c1Q5cEU3a3EyUnExQzA2LW5MRlRPNXZIYml3dXJFYVBPRzYyeUhuMjVZTGJDWDNIYkZjRVF2XzdQank4TmMtUmdmYmhreWZfTTZQbUZaWFowNF9vNHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Compra de ativos existentes pode antecipar em dois anos o início da operação da St George em Araxá - Diário do Comércio</t>
+          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE90MzZRdUdobThNWk13akRvUnVnWno1c1Q5cEU3a3EyUnExQzA2LW5MRlRPNXZIYml3dXJFYVBPRzYyeUhuMjVZTGJDWDNIYkZjRVF2XzdQank4TmMtUmdmYmhreWZfTTZQbUZaWFowNF9vNHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4076,29 +4076,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>18/06/2026 07:00</t>
+          <t>17/06/2026 07:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,51 +4108,51 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>17/06/2026 07:00</t>
+          <t>16/06/2026 17:20</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>16/06/2026 17:20</t>
+          <t>16/06/2026 07:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4181,34 +4181,34 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>16/06/2026 07:00</t>
+          <t>15/06/2026 07:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,19 +4218,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Rio Maior organizou Gala Empresarial do concelho - O Mirante</t>
+          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYmIwcks0U205THc0UF80M2tqOTBpZWY1VWhZMFZzUUE2UEt2bmFLcTBsQ1g4YjRBRjBmRUZiN25XQVdCNDdldTdiZC10VTdBSzY3YjJiTFo5TXdaNjVVNkZUMTZSQ1g4MU1XX2s0azMwd0hNTFlDTktFVktWSWtrWUpPTjFQZEhoUzU3M3NzaXpQMVVaajZoYWhPRHNtLUhf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Rio Maior organizou Gala Empresarial do concelho - O Mirante</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYmIwcks0U205THc0UF80M2tqOTBpZWY1VWhZMFZzUUE2UEt2bmFLcTBsQ1g4YjRBRjBmRUZiN25XQVdCNDdldTdiZC10VTdBSzY3YjJiTFo5TXdaNjVVNkZUMTZSQ1g4MU1XX2s0azMwd0hNTFlDTktFVktWSWtrWUpPTjFQZEhoUzU3M3NzaXpQMVVaajZoYWhPRHNtLUhf?oc=5</t>
         </is>
       </c>
     </row>
@@ -4291,44 +4291,44 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Cruzeiro conquista o título em Imigrante - Grupo A Hora</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>15/06/2026 07:00</t>
+          <t>14/06/2026 07:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdk1rcDcyUzh6UTl2c1R0LU9JMDA0T2ozQ3h6VExIbFhUVWUzWnlWY3pnWXJmNkp1SEp2ZUtCUDNqU0FlN3NpODZtbkNramhWR2ZQaE53M1FfZFk1SnpxMTlIQjEwaUxtVTJhSGhXVWFHRkFUOHBGaS1MMDZnd2pUM2NFcnNRYWNva3JOd1VZRWxadw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Cruzeiro conquista o título em Imigrante - Grupo A Hora</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>14/06/2026 07:00</t>
+          <t>12/06/2026 07:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdk1rcDcyUzh6UTl2c1R0LU9JMDA0T2ozQ3h6VExIbFhUVWUzWnlWY3pnWXJmNkp1SEp2ZUtCUDNqU0FlN3NpODZtbkNramhWR2ZQaE53M1FfZFk1SnpxMTlIQjEwaUxtVTJhSGhXVWFHRkFUOHBGaS1MMDZnd2pUM2NFcnNRYWNva3JOd1VZRWxadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4340,73 +4340,73 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>12/06/2026 07:00</t>
+          <t>11/06/2026 07:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11/06/2026 07:00</t>
+          <t>10/06/2026 07:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>10/06/2026 07:00</t>
+          <t>09/06/2026 07:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4460,63 +4460,63 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>09/06/2026 07:00</t>
+          <t>08/06/2026 17:33</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>08/06/2026 17:33</t>
+          <t>08/06/2026 07:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Ureia cai US$ 180 por tonelada em 45 dias e relações de troca melhoram; fosfatados seguem altos - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVk1CTVNDM3VDVHFuOG03ZjN3ODk5elk3SzZpR0U4a0FGbTF3cUtCRVh3ZjJQVDYxSngxcEwwbF9xaUhfQ3dkeDdkU19jX1VqTDVDSEt3NG1VMzA1eDVZS2hsbW1ObTVLajZMeW5oanRSX1A0cnljQkZaQzQzVjE3d2VkQ2NlUkp4bzQ4S3BieUluZklQeW9Jd3Q3d1M4WnRxYldxVl92S1ppVS14MVFDQ0Zla3JTcS1iX2hVQTl3WmtkT2QyNHpYeE5OUTNrdzM2aFdkb0N5aUhmWXdJczRnWTJEajBHcENKVml30gHwAUFVX3lxTE51cVFYeVhIbkhiUXhKSlNoMnBQR0EzZzRzbmRTX0FGWkFuT055Sy1jY0tzOHBveFJxUTljd01kRmM0N1hHQ1hvV2o3c0pyNVd0TGFOQVBiejJ0WUFVX3BxR0J1QTFueVprR0VVbzFfaTgtSkVXRThQRkQ4UzJUdTZKYWdsemdDZjV3Q3pHbF96OW91c1VCQzc4Q01JLTJhVjZnVm1WSjFJMC1QUlZjeFFVcmZLbnVzQlVreEdPcW11Y0lvSzF4VTdIOGlRbVlxSmFqT0VMYmQ5SlhmR2doVGJySmMxNlQycjlHV1hFNzNrVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,19 +4548,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,19 +4592,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4790,19 +4790,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4812,19 +4812,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Votorantim compra direitos minerários da João Santos por R$ 250 milhões - Pipeline</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNN0JIVlhseElXbVBQQ0l5ZDltZnJHZXllUjk1Y2J2TUNadklUclZNWG9QQzVEQWFfVUh2SDE2VGc2YmZ6MjI2SFFFNWFBc1M4NmpKNEVVWl9iQnBWU0xLdlQxT3BQME9wQ3ZYQTl0OElZRS01WTNPVDctaGR5QWJxd2poU21oZjRRelRORUhxOHdHa3FHaEZqem9wcEptTFd0XzVaRGpWcTMzZjBKa1hMdG9aRHBVeHFGS3hLUUtxZHNmb3PSAdIBQVVfeXFMUEZFaldhc3JvYmZWM0pLV1VZNUJTMmY2eFBZQi1mS0NfX0VxNWFZbkFlWjFFMF9kSGJpLTdfbHZYeDYtRnU1UXJHbzZkb3lFY0w4WG1xcU1zUWxscFpKVmppbDJxZXNXbUl6MktMQ3VDa2txRjVvUUE2LU1fNlRpd2czWXhkcTBzY2Y3TmtGOHB5ekRybmlNcW1wWjlWY2xPMm9TSUdVNGRxTnI0X2lrakRFeUFBeUw5Wkl1TTdMMjFrY1pjckFqUkN6NkQyVEZyRGRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Votorantim compra direitos minerários da João Santos por R$ 250 milhões - Pipeline</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNN0JIVlhseElXbVBQQ0l5ZDltZnJHZXllUjk1Y2J2TUNadklUclZNWG9QQzVEQWFfVUh2SDE2VGc2YmZ6MjI2SFFFNWFBc1M4NmpKNEVVWl9iQnBWU0xLdlQxT3BQME9wQ3ZYQTl0OElZRS01WTNPVDctaGR5QWJxd2poU21oZjRRelRORUhxOHdHa3FHaEZqem9wcEptTFd0XzVaRGpWcTMzZjBKa1hMdG9aRHBVeHFGS3hLUUtxZHNmb3PSAdIBQVVfeXFMUEZFaldhc3JvYmZWM0pLV1VZNUJTMmY2eFBZQi1mS0NfX0VxNWFZbkFlWjFFMF9kSGJpLTdfbHZYeDYtRnU1UXJHbzZkb3lFY0w4WG1xcU1zUWxscFpKVmppbDJxZXNXbUl6MktMQ3VDa2txRjVvUUE2LU1fNlRpd2czWXhkcTBzY2Y3TmtGOHB5ekRybmlNcW1wWjlWY2xPMm9TSUdVNGRxTnI0X2lrakRFeUFBeUw5Wkl1TTdMMjFrY1pjckFqUkN6NkQyVEZyRGRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Com excesso de enxofre, Anvisa ordena recolhimento de coco ralado da marca ‘Casa de Mãe’ - Grafitti News</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMlJWRTAxYnh2aVNNS3N6QkQwZkMxU2lCN19hMW5FNVNPYTBZRWpPU1VVQVk3blQyMnUyNkV4X0FjcDhnNE5vMkR3dzhwSHR6ek44M2E4V3hWU0FmM3NDLUVYV0s1N1dJTlYyazF4U196cGp2Ym1EWTc4amtOSDZDODhkbC1tM201cWZFY0luUXc2UkpSM0M2RDRPYlFBZy1TSVVUVHY3YUxXX3lhN09ManZmRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Com excesso de enxofre, Anvisa ordena recolhimento de coco ralado da marca ‘Casa de Mãe’ - Grafitti News</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMlJWRTAxYnh2aVNNS3N6QkQwZkMxU2lCN19hMW5FNVNPYTBZRWpPU1VVQVk3blQyMnUyNkV4X0FjcDhnNE5vMkR3dzhwSHR6ek44M2E4V3hWU0FmM3NDLUVYV0s1N1dJTlYyazF4U196cGp2Ym1EWTc4amtOSDZDODhkbC1tM201cWZFY0luUXc2UkpSM0M2RDRPYlFBZy1TSVVUVHY3YUxXX3lhN09ManZmRmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de coco ralado por excesso de enxofre - O Dia</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOeTZiM28xa2hiZEFUbFNlN3RreUVCTGw5RUtYVVVOVG9Fa0o1UWxHcFJLZW1sVThVcXlqT2RWbnNjLWFZTUp4enREa0dUNC0wQUdRVVI3MGRLQWt1cGZTdmNLV2RFR3BNcDJ6aUIxWFBfcGtNV3pMQVFIMnA0T19ud1dvSVVpV3c1U3V5NVJlNzBZS3NhbHFsQklVdzBYZUozV3FvdHNvZ1ViTWx4T2FzTTFYU005TDRjbWfSAb8BQVVfeXFMTnl2N3d1N1JxS2ZqWHZaOVQ2SnBQQ0xDWTRzdWxHLXBzQkxrMVhCTHpvUnBPV2xsTUFGSFRCZEdSNEpnVy1ZMXctUVdpVUM4bkppRU5tdks4dXJuczB2eTdGbXFSbHVkcDZjMW1Id1RZc05DdDBxTWVabXFiQmVndXBUNFhBZmFPUmNYclljdHNaNTlpVjQtX1hEbEhIM1BtbFI1RGZFWVJoUjF6MWVVRVhzV3Y1WDFVZ0hwa2x6N3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
+          <t>Anvisa determina recolhimento de coco ralado por excesso de enxofre - O Dia</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,19 +5142,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOeTZiM28xa2hiZEFUbFNlN3RreUVCTGw5RUtYVVVOVG9Fa0o1UWxHcFJLZW1sVThVcXlqT2RWbnNjLWFZTUp4enREa0dUNC0wQUdRVVI3MGRLQWt1cGZTdmNLV2RFR3BNcDJ6aUIxWFBfcGtNV3pMQVFIMnA0T19ud1dvSVVpV3c1U3V5NVJlNzBZS3NhbHFsQklVdzBYZUozV3FvdHNvZ1ViTWx4T2FzTTFYU005TDRjbWfSAb8BQVVfeXFMTnl2N3d1N1JxS2ZqWHZaOVQ2SnBQQ0xDWTRzdWxHLXBzQkxrMVhCTHpvUnBPV2xsTUFGSFRCZEdSNEpnVy1ZMXctUVdpVUM4bkppRU5tdks4dXJuczB2eTdGbXFSbHVkcDZjMW1Id1RZc05DdDBxTWVabXFiQmVndXBUNFhBZmFPUmNYclljdHNaNTlpVjQtX1hEbEhIM1BtbFI1RGZFWVJoUjF6MWVVRVhzV3Y1WDFVZ0hwa2x6N3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Empresas já investiram 42 mil euros em bolsas para estudantes de Engenharia de Minas e Recursos Energéticos do Técnico - Record</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de dióxido de enxofre - O POVO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmFyZTFtaDlxMU53dnBYVHctWjlaYjgxWENtckgwTGc4c3RGTXJONGJzV1ZfcVR0UkxDX25pMjRGQzVPaGd4VmhsVGt1LTU0c1h6NVpVRTdNRFRwTU9aVi1HVDh6Sl9fN2dqT1FHeVAwNzVlM2pSTE5ySFk1akxwT29HcjNxM09QcHFMeDlGWUxXQ3RIV2dsSGlKT1UzLXpBVGVTaTd2SFRuMGVLZ3JwVS13cEJyekN0RGRacVBWY21HeXNZSXlkVjRBdDQwSmRqVWFBdGVnTTVDY0xHRnRkejVJeTVQcEFEQ0dfRWlEZWxXWFQzX3VtUnlDWWVMZVlKRWfSAfwBQVVfeXFMUHk4ZkRPbFJnd21WaVVLQURqWk1WOVByTVotSmhwNHZfRThVWThRQ2Y3eWE3RHpVU2gzR0p5c1dIMzFDdkdjNXBPejF3ZWo5bnM1QWtWWEhWeXNndGNCY3VXM2UtYVFXZ1cxZlAyZ0pGd0N0ckZRNmhINW1yQS1NMzZMUzlfa1FDMksyckV2MHRXY05tcVUyLXpvNXpVbnROWjcyTTFGNHViOVVDNlVGbkk0eTZtNVprZ1Q5Tl90NWdNUTJFZGlBUzZQMDBnYzlsUEprWGRYcVZQM3hJa2U4cUhVbHA3MklRSjNCVkFMSXIwSmF3eDhrZjliTmlp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXFuR084YlVCYWlxRWFFZElvOXhoZGFYbXh6WXBHZzZOSm40Y3VtSUVzZjh3MVdSRGxvVVhUOWRWOHh4T1lQdUQzYVFBNXhadDhJUGpPVnBmeU1MWUo3Wk81T3JBeGkxVkUyNHlDaU11eldSckM1ZlpmQjJ0VEVFWTI4M1FtYkpxUVc0UVREUXpZZFI0clA1a1ZkS3FiNl9JMzZiVmtwN24xYWNfN0xFUUhKMlYwM1VGRm5PZ3R5cmVTNTBVRkpyb3pQM2w?oc=5</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de dióxido de enxofre - O POVO</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre; confira marca - Rádio Metrópole</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXFuR084YlVCYWlxRWFFZElvOXhoZGFYbXh6WXBHZzZOSm40Y3VtSUVzZjh3MVdSRGxvVVhUOWRWOHh4T1lQdUQzYVFBNXhadDhJUGpPVnBmeU1MWUo3Wk81T3JBeGkxVkUyNHlDaU11eldSckM1ZlpmQjJ0VEVFWTI4M1FtYkpxUVc0UVREUXpZZFI0clA1a1ZkS3FiNl9JMzZiVmtwN24xYWNfN0xFUUhKMlYwM1VGRm5PZ3R5cmVTNTBVRkpyb3pQM2w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQSjRVamltMjVSeTh5ZWpfTVZRQnNIRGdhc3AzNkRiQy1oSnFkQnZMczVraFl0WGNjSkhRcmRfclVoQkxtU1BROVNnaWhWaDNnd25MNHNWY28yUTVuMTNvSVpzelNBMjBvMGhCeWdXdlUtZWhwTG9HUV9kSFBDMUIwSTZxWURqQm9pc2xWd19MZ3p2bkZJdjRwUkVKS3plakJuNVdlN0FTd3BIcTdGY09PRXpoMGJtbXNuNUlqNE9zYWNqTVMwNXpXR1dtcllxUW9hM3pQODRscw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Portal iG</t>
+          <t>Anvisa manda recolher e proíbe venda de lote de coco ralado por excesso de enxofre - ND Mais</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPV0FOQXhCTERTM29lQTEyZWZXUW1hSE8xNE9tQTdQRWtVYXpTdzBqcTJ4Zkp0MDczMV9MRVQ1Q1Nyc0RFem9aOUI2d18tVUhpdGZhdy14N21aS1B6eC1oaVlvU3l2RXo4Vm45VUVZTGJBMlVIMHJYUC1TM0VHOEd3OGY1NU5LTTNiSXhCbHc0S2dqRkx0STZ5cUw5SFU4dzRkOHRwYVBSY1drR3NtbFVWU9IBtgFBVV95cUxQRTU2ZnA0WERrSkVxTGtaQXRkbEF6R1MybDk1Q283b0JrYjBWWEozdUZWV0RWVjMzQ095cktCR3libXA4RkpTcXQ2NHQ4UGhieWhfNk4ydGE4WFF5NzltcVMzd3FBRlJIRHRtRWRHMWMxV1hqWlYxc2Y3TEFQbGgwVDRUdFlFNURlRVZDVVdpcnhWS3VubFNuX05wazFiaXp6a0JFNkJnbVdwY1g3MmpYdS13U3hUQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9HMUF4TXN5WUx0RTZMTUktampKOHB4MjQtTWZyR1ROQ05MOXNYQW95NHpuZjlieXJCYlNGN3U1ZjhCTzlRaEMyWlZ1eUh1TldxaFREdmktMm9IQ0VHSUpDS2U3TFJNZFNiVy1FeWZDVld1X1c2NEpqX09OVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - MS Todo dia</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaEFRLWlCUTNMR05sNEtuSzg5T05GVFIzdVlCUHBreS1Pa2NxU3RtSzZaQnNpYmZDRXVadVhVaFhUU0NTQV9HQ0pCUFpqQW1fczZBX3RyUGN2QXhzcldjRWVqanBseDNzTnJKMVJndmRZck9Wa1RqWWx0OXBQc3ZYZlVhUzRaRVhUQzI0SUszalJMQ1RMZTllblpHMV9oUnd4bmdVVFNWVWs2akZP?oc=5</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Portal iG</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPV0FOQXhCTERTM29lQTEyZWZXUW1hSE8xNE9tQTdQRWtVYXpTdzBqcTJ4Zkp0MDczMV9MRVQ1Q1Nyc0RFem9aOUI2d18tVUhpdGZhdy14N21aS1B6eC1oaVlvU3l2RXo4Vm45VUVZTGJBMlVIMHJYUC1TM0VHOEd3OGY1NU5LTTNiSXhCbHc0S2dqRkx0STZ5cUw5SFU4dzRkOHRwYVBSY1drR3NtbFVWU9IBtgFBVV95cUxQRTU2ZnA0WERrSkVxTGtaQXRkbEF6R1MybDk1Q283b0JrYjBWWEozdUZWV0RWVjMzQ095cktCR3libXA4RkpTcXQ2NHQ4UGhieWhfNk4ydGE4WFF5NzltcVMzd3FBRlJIRHRtRWRHMWMxV1hqWlYxc2Y3TEFQbGgwVDRUdFlFNURlRVZDVVdpcnhWS3VubFNuX05wazFiaXp6a0JFNkJnbVdwY1g3MmpYdS13U3hUQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre; confira marca - Rádio Metrópole</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQSjRVamltMjVSeTh5ZWpfTVZRQnNIRGdhc3AzNkRiQy1oSnFkQnZMczVraFl0WGNjSkhRcmRfclVoQkxtU1BROVNnaWhWaDNnd25MNHNWY28yUTVuMTNvSVpzelNBMjBvMGhCeWdXdlUtZWhwTG9HUV9kSFBDMUIwSTZxWURqQm9pc2xWd19MZ3p2bkZJdjRwUkVKS3plakJuNVdlN0FTd3BIcTdGY09PRXpoMGJtbXNuNUlqNE9zYWNqTVMwNXpXR1dtcllxUW9hM3pQODRscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,19 +5318,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5340,19 +5340,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5362,19 +5362,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher e proíbe venda de lote de coco ralado por excesso de enxofre - ND Mais</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9HMUF4TXN5WUx0RTZMTUktampKOHB4MjQtTWZyR1ROQ05MOXNYQW95NHpuZjlieXJCYlNGN3U1ZjhCTzlRaEMyWlZ1eUh1TldxaFREdmktMm9IQ0VHSUpDS2U3TFJNZFNiVy1FeWZDVld1X1c2NEpqX09OVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - MS Todo dia</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOaEFRLWlCUTNMR05sNEtuSzg5T05GVFIzdVlCUHBreS1Pa2NxU3RtSzZaQnNpYmZDRXVadVhVaFhUU0NTQV9HQ0pCUFpqQW1fczZBX3RyUGN2QXhzcldjRWVqanBseDNzTnJKMVJndmRZck9Wa1RqWWx0OXBQc3ZYZlVhUzRaRVhUQzI0SUszalJMQ1RMZTllblpHMV9oUnd4bmdVVFNWVWs2akZP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Empresas já investiram 42 mil euros em bolsas para estudantes de Engenharia de Minas e Recursos Energéticos do Técnico - Record</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmFyZTFtaDlxMU53dnBYVHctWjlaYjgxWENtckgwTGc4c3RGTXJONGJzV1ZfcVR0UkxDX25pMjRGQzVPaGd4VmhsVGt1LTU0c1h6NVpVRTdNRFRwTU9aVi1HVDh6Sl9fN2dqT1FHeVAwNzVlM2pSTE5ySFk1akxwT29HcjNxM09QcHFMeDlGWUxXQ3RIV2dsSGlKT1UzLXpBVGVTaTd2SFRuMGVLZ3JwVS13cEJyekN0RGRacVBWY21HeXNZSXlkVjRBdDQwSmRqVWFBdGVnTTVDY0xHRnRkejVJeTVQcEFEQ0dfRWlEZWxXWFQzX3VtUnlDWWVMZVlKRWfSAfwBQVVfeXFMUHk4ZkRPbFJnd21WaVVLQURqWk1WOVByTVotSmhwNHZfRThVWThRQ2Y3eWE3RHpVU2gzR0p5c1dIMzFDdkdjNXBPejF3ZWo5bnM1QWtWWEhWeXNndGNCY3VXM2UtYVFXZ1cxZlAyZ0pGd0N0ckZRNmhINW1yQS1NMzZMUzlfa1FDMksyckV2MHRXY05tcVUyLXpvNXpVbnROWjcyTTFGNHViOVVDNlVGbkk0eTZtNVprZ1Q5Tl90NWdNUTJFZGlBUzZQMDBnYzlsUEprWGRYcVZQM3hJa2U4cUhVbHA3MklRSjNCVkFMSXIwSmF3eDhrZjliTmlp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,19 +5472,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,19 +5494,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,19 +5626,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,19 +5648,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5670,19 +5670,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,19 +5802,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcG9FWW8yeVV3REc1bWxBY1I1NFh5TmJxbE5BakhjcklocVNvMDVISHNhQjE0NU43Q2tOeGdUaDktQlpFLW5ySHQ3ck5iQ3p2Y1J2aFc3UmJHeTF6cUwxemQ5ejVYQzFxY3Y2djVrQkxTdDh0TnV1NW9vRlNjS29XR1dwSTNOUVhXNVdjTzVMQ3Y3YnpZajZDRHRRUmQ0Z04tRkFUaGFURWFHM3Q3S1gza0xOZXFBMkVNei1LMGZsY3FCV3J2bHdUWUdQOElRTG4yaFltX3VCckFkaFNEZ1R3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcG9FWW8yeVV3REc1bWxBY1I1NFh5TmJxbE5BakhjcklocVNvMDVISHNhQjE0NU43Q2tOeGdUaDktQlpFLW5ySHQ3ck5iQ3p2Y1J2aFc3UmJHeTF6cUwxemQ5ejVYQzFxY3Y2djVrQkxTdDh0TnV1NW9vRlNjS29XR1dwSTNOUVhXNVdjTzVMQ3Y3YnpZajZDRHRRUmQ0Z04tRkFUaGFURWFHM3Q3S1gza0xOZXFBMkVNei1LMGZsY3FCV3J2bHdUWUdQOElRTG4yaFltX3VCckFkaFNEZ1R3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,19 +5846,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,19 +5868,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,19 +5890,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,19 +6000,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6022,19 +6022,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Como encontrar enxofre em Subnautica 2 - Insider Gaming</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1DeUNMSGxnbU9GRnk4Y3hGbWNzYldCMzlBd3hfM0N0R1FUcVJoeHRUMWhwYjlMUXhZRktDUU9JMHRIa2E0cTUwWl9Ld201bnF6UmZ1X1hOSl9fQ0xfbV9LVU5jNWdISk0xcE8wcERtaW4xeEZS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Como encontrar enxofre em Subnautica 2 - Insider Gaming</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1DeUNMSGxnbU9GRnk4Y3hGbWNzYldCMzlBd3hfM0N0R1FUcVJoeHRUMWhwYjlMUXhZRktDUU9JMHRIa2E0cTUwWl9Ld201bnF6UmZ1X1hOSl9fQ0xfbV9LVU5jNWdISk0xcE8wcERtaW4xeEZS?oc=5</t>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6176,19 +6176,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,19 +6374,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6572,19 +6572,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,19 +6704,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,19 +6770,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Sine Araxá inicia recebimento de currículos para recolocação de trabalhadores da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6792,19 +6792,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPWXRhQzl0UFljZ25weHRsTWo5VmlfOGlPWDBvcHZFTGVqb0pJWW9rTE1TZlVtQXo3UjI2TWhscWhCSWFfWWpJZ3JIRmwycjNWTld6UllKMFBBVjhWRU5BM1laZC01Wjd5S1pRLWxwdjhXYjVPZDRMWjBCcmtmcG1rZFlUWG5oQnFlMFdjenJwbDFWZzc1X1FKWjd6RTZhQVNOTG9Rb3JoRGhib1U2RXJyYWZiNmJPRjlTV0tEbkJmN3U3QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,19 +6858,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Sine Araxá inicia recebimento de currículos para recolocação de trabalhadores da Mosaic - Prefeitura de Araxá</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,19 +6880,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPWXRhQzl0UFljZ25weHRsTWo5VmlfOGlPWDBvcHZFTGVqb0pJWW9rTE1TZlVtQXo3UjI2TWhscWhCSWFfWWpJZ3JIRmwycjNWTld6UllKMFBBVjhWRU5BM1laZC01Wjd5S1pRLWxwdjhXYjVPZDRMWjBCcmtmcG1rZFlUWG5oQnFlMFdjenJwbDFWZzc1X1FKWjd6RTZhQVNOTG9Rb3JoRGhib1U2RXJyYWZiNmJPRjlTV0tEbkJmN3U3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6902,19 +6902,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkONIB5gFBVV95cUxORWpyQ285M1U3ekpPWWVwMER6dTNMTWlZZ3h3VFBwSmRiZ1Y0dnZvb0NtaVlXR0FSank5ZklXMkl6NUhFcG1wcWFuX3lld0VSeFktQU1PUUxESFg5VE0zRlBPaVNfb1VFZTE3ZUFsRDB4N1ZYVUo1dXMxN210RW84LU5scWp4MXppTEZLWFlEeC1mdE9hYkhOTmNoaVUzOFA2d3lvVkZ1cWxCM1A5YWxMUW0tamkxS3BqSUNxRUlWcFo1cUZ2bFVtdlIyd2xKM2FjQTBkcmJjVWdtSlI4WFNlRkxHZlBQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7078,19 +7078,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7122,19 +7122,19 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkONIB5gFBVV95cUxORWpyQ285M1U3ekpPWWVwMER6dTNMTWlZZ3h3VFBwSmRiZ1Y0dnZvb0NtaVlXR0FSank5ZklXMkl6NUhFcG1wcWFuX3lld0VSeFktQU1PUUxESFg5VE0zRlBPaVNfb1VFZTE3ZUFsRDB4N1ZYVUo1dXMxN210RW84LU5scWp4MXppTEZLWFlEeC1mdE9hYkhOTmNoaVUzOFA2d3lvVkZ1cWxCM1A5YWxMUW0tamkxS3BqSUNxRUlWcFo1cUZ2bFVtdlIyd2xKM2FjQTBkcmJjVWdtSlI4WFNlRkxHZlBQdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Para reduzir dependência externa, Petrobras volta a produzir ureia no PR - Monitor Mercantil</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNaFN6dXlpRHRuQWNMd3NybU45VF9fdkNMQnpOTmd2bGhMZ1hYem9qMmlnNTFNNWM4X0RYak56XzNpaW01NFJtalZ2TFp6STNGanpKUEhLREFkejZackdaRUN6MmRUS2FteUxpSmFpTlpfTG5oV1JncDBqZjFCaFpCRlIxeWVaR1J1blJrbkdZT1cwUVd5ZW9nRlozVlRObWR0Q1ZUMERRQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7173,22 +7173,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>28/04/2026 07:00</t>
+          <t>30/04/2026 07:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,41 +7232,41 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>27/04/2026 07:00</t>
+          <t>28/04/2026 07:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,19 +7298,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7320,63 +7320,63 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>24/04/2026 07:00</t>
+          <t>27/04/2026 07:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>22/04/2026 07:00</t>
+          <t>24/04/2026 07:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7415,22 +7415,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>21/04/2026 21:42</t>
+          <t>22/04/2026 07:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7442,39 +7442,39 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Cientistas criam polímero de enxofre que elimina fungos e bactérias sem afetar humanos - O Cafezinho</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>21/04/2026 07:00</t>
+          <t>21/04/2026 21:42</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZ3BJUzNVZHdWeFpabk9HUElZN1AtQWtsT2FoVmx6RHNnclJ4LWpNVlRpakhINEJzTWlUNzIwNnFQWGxWZ0RxbG9VMW9vYUN2d0xCdlBndWFqOU5oZTd3ZFZVaWwwS2xDY3prcTd6Z1phaWhhMGxVQlNrWm53X0tlOEJuRVhscmRybnRDRmctdENSajgtS2ZnRkgwNUFiV1dmUFR6ZTZiczVXbEJEdlZPQkxqY1lFdFkyZncwU1FCMWVPaFnSAcgBQVVfeXFMT2dxMVIzak5qWE41TFY1dVRXWXFTaGtFRWF0U3k1b1JtSWYtMjBZVkRGTjQtRlp2QkJQS25UeGhmMmRqTzgzd3Iza2dWcWducVB2Qjk2WGJqRF80bHZJNU5rZXBMNXpTLVd6dk1nd2Rhd0d6b2lqNlFmYWFGOW5UQmJWcUVuZW9BLWtybWNUcDFZdko3bVZSTDVyeElkZE90M3dqTFY5eTFWNi0tTUZoOEs2VDBzOHNjUlVHZGhmRmg5S3VsbjRIaXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Cientistas criam polímero de enxofre que elimina fungos e bactérias sem afetar humanos - O Cafezinho</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>20/04/2026 07:00</t>
+          <t>21/04/2026 07:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZ3BJUzNVZHdWeFpabk9HUElZN1AtQWtsT2FoVmx6RHNnclJ4LWpNVlRpakhINEJzTWlUNzIwNnFQWGxWZ0RxbG9VMW9vYUN2d0xCdlBndWFqOU5oZTd3ZFZVaWwwS2xDY3prcTd6Z1phaWhhMGxVQlNrWm53X0tlOEJuRVhscmRybnRDRmctdENSajgtS2ZnRkgwNUFiV1dmUFR6ZTZiczVXbEJEdlZPQkxqY1lFdFkyZncwU1FCMWVPaFnSAcgBQVVfeXFMT2dxMVIzak5qWE41TFY1dVRXWXFTaGtFRWF0U3k1b1JtSWYtMjBZVkRGTjQtRlp2QkJQS25UeGhmMmRqTzgzd3Iza2dWcWducVB2Qjk2WGJqRF80bHZJNU5rZXBMNXpTLVd6dk1nd2Rhd0d6b2lqNlFmYWFGOW5UQmJWcUVuZW9BLWtybWNUcDFZdko3bVZSTDVyeElkZE90M3dqTFY5eTFWNi0tTUZoOEs2VDBzOHNjUlVHZGhmRmg5S3VsbjRIaXA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,139 +7486,139 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>17/04/2026 07:00</t>
+          <t>20/04/2026 07:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>16/04/2026 07:00</t>
+          <t>17/04/2026 07:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
+          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>15/04/2026 22:32</t>
+          <t>16/04/2026 07:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>14/04/2026 07:00</t>
+          <t>15/04/2026 22:32</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Líder em recuperação e processamento de enxofre - Tessenderlo Kerley</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>13/04/2026 11:05</t>
+          <t>14/04/2026 07:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbUhXVzFvVVctdDZWUlE3OXNmbnJzcndpOGZ6Y2FlNGhueTB2blAtUFBGbmcwTG81eDZNN1NORzRyUktTLXo3X3RaSVRsNjA4UDF4NGFPQWlFVm9nU0Jfc25FSkNKQmlNaFFvX21NMEFWOFpzZmR2UWFBd3N2cVdmRmJER18tbmRu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
+          <t>Líder em recuperação e processamento de enxofre - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>13/04/2026 07:00</t>
+          <t>13/04/2026 11:05</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbUhXVzFvVVctdDZWUlE3OXNmbnJzcndpOGZ6Y2FlNGhueTB2blAtUFBGbmcwTG81eDZNN1NORzRyUktTLXo3X3RaSVRsNjA4UDF4NGFPQWlFVm9nU0Jfc25FSkNKQmlNaFFvX21NMEFWOFpzZmR2UWFBd3N2cVdmRmJER18tbmRu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7628,19 +7628,19 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7650,41 +7650,41 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>10/04/2026 07:00</t>
+          <t>13/04/2026 07:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7728,17 +7728,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - BNamericas</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>10/04/2026 07:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - BNamericas</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,41 +7804,41 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>08/04/2026 07:00</t>
+          <t>09/04/2026 07:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,51 +8024,51 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>07/04/2026 07:00</t>
+          <t>08/04/2026 07:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>06/04/2026 07:00</t>
+          <t>07/04/2026 07:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8090,51 +8090,51 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>02/04/2026 20:10</t>
+          <t>06/04/2026 07:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>01/04/2026 07:00</t>
+          <t>02/04/2026 20:10</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8163,34 +8163,34 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Caldense apresenta jogadores que vão disputar o Módulo II do Mineiro de 2026 - PocosCom</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>31/03/2026 07:00</t>
+          <t>01/04/2026 07:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaHBlSjh0OEN5c0hhaFNud3ZtU0pacFBRUlFfQkVTWVZBczJiWE5IZklZbjQ2ODBiZ3FOeFoteG91X2NVWE00anhaTDA5dGRidTA1MUxqYkRIaEtBblZ3SkY5VWdfRmc4RUxaeHV6VW5yUmNTeWNlREp6LUpSNmg2TFYwMzNWSll1NkJMTFhtT2FXWVJDTWtTaVAtMDJnaUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Caldense apresenta jogadores que vão disputar o Módulo II do Mineiro de 2026 - PocosCom</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaHBlSjh0OEN5c0hhaFNud3ZtU0pacFBRUlFfQkVTWVZBczJiWE5IZklZbjQ2ODBiZ3FOeFoteG91X2NVWE00anhaTDA5dGRidTA1MUxqYkRIaEtBblZ3SkY5VWdfRmc4RUxaeHV6VW5yUmNTeWNlREp6LUpSNmg2TFYwMzNWSll1NkJMTFhtT2FXWVJDTWtTaVAtMDJnaUU?oc=5</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Caldense apresenta elenco para temporada de 2026 - onda poços</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8244,63 +8244,63 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE95MkZIWmpVeXBPdDVYRy13QnhHYnZtd3dHOUpQcnV0VmliYmNLemhIZXRZTVhVMmFqTjRBMmNJQTl2dVF0TWJTWEV6M3k1MzBQbGpJVWN5MWhVNVlxTFl3ZVNCdlFld2RyX19qUlJRLWtUTlVLdXZBRFY3RDYyLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Caldense apresenta elenco para temporada de 2026 - onda poços</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>30/03/2026 07:00</t>
+          <t>31/03/2026 07:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE95MkZIWmpVeXBPdDVYRy13QnhHYnZtd3dHOUpQcnV0VmliYmNLemhIZXRZTVhVMmFqTjRBMmNJQTl2dVF0TWJTWEV6M3k1MzBQbGpJVWN5MWhVNVlxTFl3ZVNCdlFld2RyX19qUlJRLWtUTlVLdXZBRFY3RDYyLTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Após anos de reclamações por barulho, pequena comunidade rural dos EUA força saída de mineradora de Bitcoin da região - Livecoins</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>27/03/2026 07:00</t>
+          <t>30/03/2026 07:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcnZsLVNQY3dYX3dtUG5pbkhwZzRTZVFhU0Q1dDEyWllPWjdsc0JKdG9VTkpRd19uOU5lYVpob1kxWS1MMVp6Xzg3VkZpYjJ1UTJ0QXBGRFZxVHY2aTFFQzVRc05SX2ZuSnFjeXdqU2dXYVlDYkNMS0hDRE9iVnBXYUsteTlKTnZYWmwyZXhtMklYVk9JZW1YQ3JPZzNlV054TkFzbnRxaTZqd0Z2dm9XbTRtakRKMXZyQVUtaXlQaTJoVFNiZjlpTFhIQmNwVnVoeDV2elFiTmFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Preços do Enxofre Atingem Máximas Históricas, Pressionando Fortemente os Custos dos Fertilizantes Compostos - Sunsirs</t>
+          <t>Após anos de reclamações por barulho, pequena comunidade rural dos EUA força saída de mineradora de Bitcoin da região - Livecoins</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1jb0xTOTdjQ2NjUW8tMFd0ekFtRm4tbHRaaWZOZ1VnelROS2hsa1l4aDV4YWo3dVdTbGthRnF5LXFpdFE1ejdqRlBDdnhPc2ItUTAteVh4MEt4T0R1ekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcnZsLVNQY3dYX3dtUG5pbkhwZzRTZVFhU0Q1dDEyWllPWjdsc0JKdG9VTkpRd19uOU5lYVpob1kxWS1MMVp6Xzg3VkZpYjJ1UTJ0QXBGRFZxVHY2aTFFQzVRc05SX2ZuSnFjeXdqU2dXYVlDYkNMS0hDRE9iVnBXYUsteTlKTnZYWmwyZXhtMklYVk9JZW1YQ3JPZzNlV054TkFzbnRxaTZqd0Z2dm9XbTRtakRKMXZyQVUtaXlQaTJoVFNiZjlpTFhIQmNwVnVoeDV2elFiTmFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8339,22 +8339,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Preços do Enxofre Atingem Máximas Históricas, Pressionando Fortemente os Custos dos Fertilizantes Compostos - Sunsirs</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>25/03/2026 07:00</t>
+          <t>27/03/2026 07:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1jb0xTOTdjQ2NjUW8tMFd0ekFtRm4tbHRaaWZOZ1VnelROS2hsa1l4aDV4YWo3dVdTbGthRnF5LXFpdFE1ejdqRlBDdnhPc2ItUTAteVh4MEt4T0R1ekE?oc=5</t>
         </is>
       </c>
     </row>
@@ -8410,39 +8410,39 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>23/03/2026 07:00</t>
+          <t>25/03/2026 07:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - circuitomt.com.br</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>21/03/2026 07:00</t>
+          <t>23/03/2026 07:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8454,17 +8454,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - circuitomt.com.br</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>20/03/2026 21:35</t>
+          <t>21/03/2026 07:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8476,51 +8476,51 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>20/03/2026 17:42</t>
+          <t>20/03/2026 21:35</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>20/03/2026 07:00</t>
+          <t>20/03/2026 17:42</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,19 +8530,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8564,17 +8564,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>19/03/2026 07:00</t>
+          <t>20/03/2026 07:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8640,19 +8640,19 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8662,19 +8662,19 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -8684,51 +8684,51 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado Federal</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>18/03/2026 07:00</t>
+          <t>19/03/2026 07:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - Senado Federal</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>17/03/2026 07:00</t>
+          <t>18/03/2026 07:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8740,73 +8740,73 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>16/03/2026 07:00</t>
+          <t>17/03/2026 07:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>14/03/2026 07:00</t>
+          <t>16/03/2026 07:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>13/03/2026 07:00</t>
+          <t>14/03/2026 07:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Archtrends - Portobello</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8816,29 +8816,29 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Archtrends - Portobello</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>11/03/2026 07:00</t>
+          <t>13/03/2026 07:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
@@ -8938,51 +8938,51 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>10/03/2026 15:14</t>
+          <t>11/03/2026 07:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>09/03/2026 07:00</t>
+          <t>10/03/2026 15:14</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,19 +9014,19 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,19 +9036,19 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9058,41 +9058,41 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>06/03/2026 08:00</t>
+          <t>09/03/2026 07:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -9136,61 +9136,61 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>05/03/2026 08:00</t>
+          <t>06/03/2026 08:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>04/03/2026 13:02</t>
+          <t>05/03/2026 08:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>04/03/2026 08:00</t>
+          <t>04/03/2026 13:02</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9263,22 +9263,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
+          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>03/03/2026 08:00</t>
+          <t>04/03/2026 08:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
         </is>
       </c>
     </row>
@@ -9307,12 +9307,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9322,19 +9322,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia dispara com conflito no Oriente Médio - Farmnews</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -9344,95 +9344,95 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNTVFkcXZvVHN3dmdlVmU3LXI0Smh4SnJPOENuSHF6VkUxbzllQUpYOEQtQTNObEJnOHRuUFhCeDdKLWY5YzN6WGY0Uml3NUdJYmtpc3ROQVFHX3p3M1JQR3pydm5NY1pyUzFCUTYtcmpqNmt6bzRiYU44XzZOeC01ZmFrMmNOZHpxaExxTjVqdHNPcU9vTkNV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
+          <t>Preço futuro da ureia dispara com conflito no Oriente Médio - Farmnews</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>28/02/2026 08:00</t>
+          <t>03/03/2026 08:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNTVFkcXZvVHN3dmdlVmU3LXI0Smh4SnJPOENuSHF6VkUxbzllQUpYOEQtQTNObEJnOHRuUFhCeDdKLWY5YzN6WGY0Uml3NUdJYmtpc3ROQVFHX3p3M1JQR3pydm5NY1pyUzFCUTYtcmpqNmt6bzRiYU44XzZOeC01ZmFrMmNOZHpxaExxTjVqdHNPcU9vTkNV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>27/02/2026 08:00</t>
+          <t>28/02/2026 08:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>26/02/2026 08:00</t>
+          <t>27/02/2026 08:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>25/02/2026 08:00</t>
+          <t>26/02/2026 08:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9454,41 +9454,41 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>20/02/2026 08:00</t>
+          <t>25/02/2026 08:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9520,19 +9520,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9542,19 +9542,19 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>CBPM barra venda de US$ 1 bi da Equinox Gold - BPMoney</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9806,19 +9806,19 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBWblRQRGhkRGVieU40amJOckdTQncyS21zQno3b0hlNmQxQU5ZTkRMTDc2clI3SEs0ckFJT3BMeFY3M09Zd0hNb0hMU2tOWjlMSldqTzJ3cmR2a1VlZHNsMHBEYUZwWWkxbnRsUFVZVWJsOURCMjZTUHdHaUJEZ0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9828,19 +9828,19 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>CBPM barra venda de US$ 1 bi da Equinox Gold - BPMoney</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBWblRQRGhkRGVieU40amJOckdTQncyS21zQno3b0hlNmQxQU5ZTkRMTDc2clI3SEs0ckFJT3BMeFY3M09Zd0hNb0hMU2tOWjlMSldqTzJ3cmR2a1VlZHNsMHBEYUZwWWkxbnRsUFVZVWJsOURCMjZTUHdHaUJEZ0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9967,12 +9967,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -9982,19 +9982,19 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>Saída de Gabigol do Cruzeiro é consenso; destino passa a ser a dúvida - DeFato.com</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,19 +10290,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNa2tNM01IRUF0a3VjME5PaDlsRWd5cW5OVW90a1J1SmxVZm5sbC1fdDZkVjZRcm1TYTdhRWs1RTJuSzJhUEhPYXpvWmhqcUExdGV5VkNPaXZLQmVvdzh0VTFraG9QbmZsZ3VlbFpXSThWWTNLLTdsZkNQNEFSLVhUcjQ5U1VIQ1BGSXZYd2tTLWV4SS1SWEl4bGdLal8tc0lz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Saída de Gabigol do Cruzeiro é consenso; destino passa a ser a dúvida - DeFato.com</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNa2tNM01IRUF0a3VjME5PaDlsRWd5cW5OVW90a1J1SmxVZm5sbC1fdDZkVjZRcm1TYTdhRWs1RTJuSzJhUEhPYXpvWmhqcUExdGV5VkNPaXZLQmVvdzh0VTFraG9QbmZsZ3VlbFpXSThWWTNLLTdsZkNQNEFSLVhUcjQ5U1VIQ1BGSXZYd2tTLWV4SS1SWEl4bGdLal8tc0lz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Jornal Portuário</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOejlYQmU1SzhnRGtFMFJKWU9sNFZmM01temlpNFdjTVRTQzdqeFFwM0hZUzlIVlJZa2pGaGo1UVdmTXd0dGRtX041d1ptUVdvUmNfTnNlM2ppdmFEMUtlMlZVNzBvWlZyaVlGZUpOV19CR0FKeXFKU21yWEo4Q0RoMnEzdHV2Zk1ZR0prQzRnQzNzOGR1OGwwQkFYM2hwemo0emFXQ0tkUmR6a3NnYWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Jornal Portuário</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOejlYQmU1SzhnRGtFMFJKWU9sNFZmM01temlpNFdjTVRTQzdqeFFwM0hZUzlIVlJZa2pGaGo1UVdmTXd0dGRtX041d1ptUVdvUmNfTnNlM2ppdmFEMUtlMlZVNzBvWlZyaVlGZUpOV19CR0FKeXFKU21yWEo4Q0RoMnEzdHV2Zk1ZR0prQzRnQzNzOGR1OGwwQkFYM2hwemo0emFXQ0tkUmR6a3NnYWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10664,19 +10664,19 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Cássio iguala Dida em pênaltis defendidos; veja ranking - band.com.br</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10686,19 +10686,19 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNMFU4a0ZjNk5fVWV1eGpWbDJ2UjRTUW1rS1RZZWFVVThzMm1nQVFYbDB0dDhHblE4d2R0di1ac3dJUjhBZWlWbTI2d3FsWU15emhnbExQSU54VFprZjJKNE1mWTN3dmlEby1qTnY2dWxvdmlmak9HUU5pajVrVE5yRjRVRm5Ock5Rdnd0b0dxNnk1U2k5RnNGb29DUkhYemRsRFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>Corinthians vence o Cruzeiro nos pênaltis e vai à final da Copa do Brasil - band.com.br</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPV1d5dEFNd0t1ME9tQWJSWWRzLWtuckNpd25abG9vcUJ3czlmcl9xLTQxQmE4Ni1udEFTRDBFZUd3VWFMMU5McWlELUtoTG50dTZTeXY2SmtJMXdObllneDBuV1JLbXdscG1NTzhRLTJMSExGQjNxSkF3WjBuS0dkaXBYdTR0WW1DeDBQdVBvUzlmZ1JQM2pSVDhqdEFCdXlXWjZqSlhoT3ZjeVNMZGtobGdsTlBoWUpZVGlv?oc=5</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Hugo Souza gigante, Corinthians elimina o Cruzeiro nos pênaltis e está na final da Copa do Brasil - capitalnews.com.br</t>
+          <t>Cássio iguala Dida em pênaltis defendidos; veja ranking - band.com.br</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,19 +10730,19 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQMlJiZVMtX3NqVlBzYzBDUnJPVk5ZWkRYcmszc2FVY2dMTWVkRG8yTDhCU1pxcl9jR0dIN0tKUHFVRVlOblVuOTdpdXlYR2lZSjhSQkpZZ25CSE5VX3Y1bThsa2dnMkpOUEtwVmF2ek5OZXFhZm1CRGF5elZQNW5SV2VjYy0wV1ZTU3hQRmswT1Z1OFRHRG5ydHlvRlEyb2oyekhBbG1uOWdpM1dIZkVXUWNMVy1Rdm9wa3dMMlZyeDZ3SENla2VjR0xqdGt0b3NnTWc2T0hQb2hWc1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNMFU4a0ZjNk5fVWV1eGpWbDJ2UjRTUW1rS1RZZWFVVThzMm1nQVFYbDB0dDhHblE4d2R0di1ac3dJUjhBZWlWbTI2d3FsWU15emhnbExQSU54VFprZjJKNE1mWTN3dmlEby1qTnY2dWxvdmlmak9HUU5pajVrVE5yRjRVRm5Ock5Rdnd0b0dxNnk1U2k5RnNGb29DUkhYemRsRFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Cal Cruzeiro</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>Corinthians elimina Cruzeiro pela 3ª vez na história da Copa do Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQQ1AzUm1KNUYtMGxCaEFfQ05zUzNnemhZblotcVNfdlY2RU9Hd0M3UThGX3JEdHFoRVdFa1BncW9PanJUVHVZSEVzZk8xbmxGRkZqa2lPZWJXQjBQZjhJN04weV96TGFqS0dNNEtUZW9RQWlvNS1UUkpGYmU2ckl0S0RwaEpHR1BCaWFBeUYyeXhXdlhTQkZKRVNRUUg3OVRwTGNYUGtRbmFOVUtpQlBpWk1naHhHSTRNM2V1ZWVtV2xLQ1N3bnRnU1ZoMjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Corinthians elimina Cruzeiro pela 3ª vez na história da Copa do Brasil - CNN Brasil</t>
+          <t>E se for para os pênaltis? Quem leva vantagem entre Hugo Souza e Cássio em Corinthians x Cruzeiro na Copa do Brasil - ESPN Brasil</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10774,19 +10774,19 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQQ1AzUm1KNUYtMGxCaEFfQ05zUzNnemhZblotcVNfdlY2RU9Hd0M3UThGX3JEdHFoRVdFa1BncW9PanJUVHVZSEVzZk8xbmxGRkZqa2lPZWJXQjBQZjhJN04weV96TGFqS0dNNEtUZW9RQWlvNS1UUkpGYmU2ckl0S0RwaEpHR1BCaWFBeUYyeXhXdlhTQkZKRVNRUUg3OVRwTGNYUGtRbmFOVUtpQlBpWk1naHhHSTRNM2V1ZWVtV2xLQ1N3bnRnU1ZoMjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPOWs4S016VVRvTnBGOURieGlCNWlNZjIyX21jOV9HYjlMZGpyLS1LMUx3Nkt0Wm5rc21aMkpSZTlxdHEzLWpRV05XLTRReVFzQTVEazNEb19QSW9PemJwWjhMYWstVkYwVmhzZ1RRMjk5MWtJa2FnUzNzd096MWFHRFZTM013YlNqaXpPUWdEZjlHMGowaW92Qk5RUXZTWUdKbWtuMDg2cTU0eEVmYkNGNnctc2doX09vaFhqejNLNW9CSkt3czBFRFVSam1QdnJUMmcyd290SzgtRW9OY05hdDlacm11LVAx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Cal Cruzeiro</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Corinthians vence o Cruzeiro nos pênaltis e vai à final da Copa do Brasil - band.com.br</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPV1d5dEFNd0t1ME9tQWJSWWRzLWtuckNpd25abG9vcUJ3czlmcl9xLTQxQmE4Ni1udEFTRDBFZUd3VWFMMU5McWlELUtoTG50dTZTeXY2SmtJMXdObllneDBuV1JLbXdscG1NTzhRLTJMSExGQjNxSkF3WjBuS0dkaXBYdTR0WW1DeDBQdVBvUzlmZ1JQM2pSVDhqdEFCdXlXWjZqSlhoT3ZjeVNMZGtobGdsTlBoWUpZVGlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>E se for para os pênaltis? Quem leva vantagem entre Hugo Souza e Cássio em Corinthians x Cruzeiro na Copa do Brasil - ESPN Brasil</t>
+          <t>Hugo Souza gigante, Corinthians elimina o Cruzeiro nos pênaltis e está na final da Copa do Brasil - capitalnews.com.br</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPOWs4S016VVRvTnBGOURieGlCNWlNZjIyX21jOV9HYjlMZGpyLS1LMUx3Nkt0Wm5rc21aMkpSZTlxdHEzLWpRV05XLTRReVFzQTVEazNEb19QSW9PemJwWjhMYWstVkYwVmhzZ1RRMjk5MWtJa2FnUzNzd096MWFHRFZTM013YlNqaXpPUWdEZjlHMGowaW92Qk5RUXZTWUdKbWtuMDg2cTU0eEVmYkNGNnctc2doX09vaFhqejNLNW9CSkt3czBFRFVSam1QdnJUMmcyd290SzgtRW9OY05hdDlacm11LVAx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQMlJiZVMtX3NqVlBzYzBDUnJPVk5ZWkRYcmszc2FVY2dMTWVkRG8yTDhCU1pxcl9jR0dIN0tKUHFVRVlOblVuOTdpdXlYR2lZSjhSQkpZZ25CSE5VX3Y1bThsa2dnMkpOUEtwVmF2ek5OZXFhZm1CRGF5elZQNW5SV2VjYy0wV1ZTU3hQRmswT1Z1OFRHRG5ydHlvRlEyb2oyekhBbG1uOWdpM1dIZkVXUWNMVy1Rdm9wa3dMMlZyeDZ3SENla2VjR0xqdGt0b3NnTWc2T0hQb2hWc1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -10957,12 +10957,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
@@ -11001,12 +11001,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
